--- a/dataset_train_transformer-v2.xlsx
+++ b/dataset_train_transformer-v2.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2024 Foundation model\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F0EE02-4BA5-4D3E-9D37-1FD0DFCA0E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAD40C4-51C3-4F38-8CFA-486D7672990D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="2520" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="64x64" sheetId="1" r:id="rId1"/>
     <sheet name="64x64-aug" sheetId="6" r:id="rId2"/>
     <sheet name="64x64-finetune" sheetId="7" r:id="rId3"/>
+    <sheet name="readme" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'64x64'!$A$1:$X$479</definedName>
@@ -34,12 +35,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11330" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11402" uniqueCount="1103">
   <si>
     <t>path_lr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3604,6 +3608,67 @@
   </si>
   <si>
     <t>biotisr-lysosome-sr-2-256</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rcan3d-c2s-mt-dcv-mc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rcan3d-c2s-npc-dcv-mc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rcan3d-c2s-sirdna-dcv-mc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_MT\train\channel_0\confocal_p64_s64_nslice_5</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_MT\train_p64_s64_nslice_5_1.txt</t>
+  </si>
+  <si>
+    <t>SiR-DNA (red)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RCAN-C2S-SirDNA-mc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RCAN-C2S-NPC-mc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RCAN-C2S-MT-mc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_NPC\train\channel_0\confocal_p64_s64_nslice_5</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_SirDNA\train\channel_0\condition_0_p64_s64_nslice_5</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_SirDNA\train\channel_0\gt_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_NPC\train_p64_s64_nslice_5_1.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_SirDNA\train_p64_s64_nslice_5_1.txt</t>
+  </si>
+  <si>
+    <t>The index is important for generate text. The file name of the text is the index.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>in_channels</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>out_channels</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3793,7 +3858,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -3956,6 +4021,8 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -49536,7 +49603,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A163AA7F-4DF5-48A0-AE09-D011016C5669}">
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -49544,13 +49611,13 @@
     <col min="5" max="5" width="5.25" customWidth="1"/>
     <col min="6" max="6" width="5.375" customWidth="1"/>
     <col min="7" max="7" width="4.125" customWidth="1"/>
-    <col min="10" max="10" width="5.375" customWidth="1"/>
-    <col min="11" max="11" width="5.625" customWidth="1"/>
-    <col min="17" max="17" width="75" customWidth="1"/>
-    <col min="18" max="18" width="10.5" customWidth="1"/>
+    <col min="12" max="12" width="5.375" customWidth="1"/>
+    <col min="13" max="13" width="5.625" customWidth="1"/>
+    <col min="19" max="19" width="75" customWidth="1"/>
+    <col min="20" max="20" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -49578,68 +49645,74 @@
       <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="95" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K1" s="95" t="s">
+        <v>1102</v>
+      </c>
+      <c r="L1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="M1" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>930</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>931</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>0</v>
       </c>
-      <c r="O1" t="s">
-        <v>1</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R1" t="s">
         <v>932</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="28" t="s">
+      <c r="T1" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="V1" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>152</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>97</v>
       </c>
-      <c r="W1" s="112" t="s">
+      <c r="Y1" s="112" t="s">
         <v>745</v>
       </c>
-      <c r="X1" s="113" t="s">
+      <c r="Z1" s="113" t="s">
         <v>746</v>
       </c>
-      <c r="Y1" s="25" t="s">
+      <c r="AA1" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="112" t="s">
+      <c r="AC1" s="112" t="s">
         <v>756</v>
       </c>
-      <c r="AB1" s="50" t="s">
+      <c r="AD1" s="50" t="s">
         <v>819</v>
       </c>
-      <c r="AC1" s="25" t="s">
+      <c r="AE1" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="101">
         <v>0</v>
       </c>
@@ -49667,59 +49740,65 @@
       <c r="I2" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="105">
-        <v>1</v>
-      </c>
-      <c r="K2" s="106">
-        <v>1</v>
-      </c>
-      <c r="L2" s="107">
-        <v>1</v>
-      </c>
-      <c r="N2" s="107" t="s">
+      <c r="J2" s="101">
+        <v>1</v>
+      </c>
+      <c r="K2" s="101">
+        <v>1</v>
+      </c>
+      <c r="L2" s="105">
+        <v>1</v>
+      </c>
+      <c r="M2" s="106">
+        <v>1</v>
+      </c>
+      <c r="N2" s="107">
+        <v>1</v>
+      </c>
+      <c r="P2" s="107" t="s">
         <v>933</v>
       </c>
-      <c r="O2" s="96" t="s">
+      <c r="Q2" s="96" t="s">
         <v>936</v>
       </c>
-      <c r="P2" s="107" t="s">
+      <c r="R2" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="Q2" s="107" t="s">
+      <c r="S2" s="107" t="s">
         <v>938</v>
       </c>
-      <c r="R2" s="108" t="s">
+      <c r="T2" s="108" t="s">
         <v>96</v>
       </c>
-      <c r="S2" s="101" t="s">
+      <c r="U2" s="101" t="s">
         <v>915</v>
       </c>
-      <c r="T2" s="108" t="s">
+      <c r="V2" s="108" t="s">
         <v>916</v>
       </c>
-      <c r="U2" s="101" t="s">
+      <c r="W2" s="101" t="s">
         <v>909</v>
       </c>
-      <c r="W2" s="108" t="s">
+      <c r="Y2" s="108" t="s">
         <v>917</v>
       </c>
-      <c r="X2" s="104" t="s">
+      <c r="Z2" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="Y2" s="109" t="s">
+      <c r="AA2" s="109" t="s">
         <v>918</v>
       </c>
-      <c r="AA2" s="108" t="s">
+      <c r="AC2" s="108" t="s">
         <v>917</v>
       </c>
-      <c r="AB2" s="104" t="s">
+      <c r="AD2" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="AC2" s="107" t="s">
+      <c r="AE2" s="107" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" s="114">
         <v>1</v>
       </c>
@@ -49747,60 +49826,66 @@
       <c r="I3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="22">
-        <v>1</v>
-      </c>
-      <c r="K3" s="12">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="J3" s="101">
+        <v>1</v>
+      </c>
+      <c r="K3" s="101">
+        <v>1</v>
+      </c>
+      <c r="L3" s="22">
+        <v>1</v>
+      </c>
+      <c r="M3" s="12">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="P3" t="s">
         <v>934</v>
       </c>
-      <c r="O3" s="96" t="s">
+      <c r="Q3" s="96" t="s">
         <v>936</v>
       </c>
-      <c r="P3" s="96" t="s">
+      <c r="R3" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q3" s="96" t="s">
+      <c r="S3" s="96" t="s">
         <v>938</v>
       </c>
-      <c r="R3" s="115" t="s">
+      <c r="T3" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="T3" s="28" t="s">
+      <c r="V3" s="28" t="s">
         <v>921</v>
       </c>
-      <c r="U3" s="114" t="s">
+      <c r="W3" s="114" t="s">
         <v>909</v>
       </c>
-      <c r="W3" s="115" t="s">
+      <c r="Y3" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="X3" s="96" t="s">
+      <c r="Z3" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="Y3" s="115" t="s">
+      <c r="AA3" s="115" t="s">
         <v>918</v>
       </c>
-      <c r="Z3" s="96"/>
-      <c r="AA3" s="115" t="s">
+      <c r="AB3" s="96"/>
+      <c r="AC3" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="AB3" s="96" t="s">
+      <c r="AD3" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE3" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" s="114">
         <v>2</v>
       </c>
@@ -49828,60 +49913,66 @@
       <c r="I4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="22">
-        <v>1</v>
-      </c>
-      <c r="K4" s="12">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="J4" s="101">
+        <v>1</v>
+      </c>
+      <c r="K4" s="101">
+        <v>1</v>
+      </c>
+      <c r="L4" s="22">
+        <v>1</v>
+      </c>
+      <c r="M4" s="12">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="P4" t="s">
         <v>935</v>
       </c>
-      <c r="O4" s="96" t="s">
+      <c r="Q4" s="96" t="s">
         <v>936</v>
       </c>
-      <c r="P4" s="96" t="s">
+      <c r="R4" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q4" s="96" t="s">
+      <c r="S4" s="96" t="s">
         <v>938</v>
       </c>
-      <c r="R4" s="115" t="s">
+      <c r="T4" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="U4" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="T4" s="28" t="s">
+      <c r="V4" s="28" t="s">
         <v>916</v>
       </c>
-      <c r="U4" s="114" t="s">
+      <c r="W4" s="114" t="s">
         <v>909</v>
       </c>
-      <c r="W4" s="115" t="s">
+      <c r="Y4" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="X4" s="96" t="s">
+      <c r="Z4" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="Y4" s="115" t="s">
+      <c r="AA4" s="115" t="s">
         <v>918</v>
       </c>
-      <c r="Z4" s="96"/>
-      <c r="AA4" s="115" t="s">
+      <c r="AB4" s="96"/>
+      <c r="AC4" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="AB4" s="96" t="s">
+      <c r="AD4" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AE4" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="114">
         <v>3</v>
       </c>
@@ -49909,59 +50000,65 @@
       <c r="I5" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="119">
-        <v>1</v>
-      </c>
-      <c r="K5" s="120">
-        <v>1</v>
-      </c>
-      <c r="L5" s="73">
-        <v>1</v>
-      </c>
-      <c r="N5" s="73" t="s">
+      <c r="J5" s="101">
+        <v>1</v>
+      </c>
+      <c r="K5" s="101">
+        <v>1</v>
+      </c>
+      <c r="L5" s="119">
+        <v>1</v>
+      </c>
+      <c r="M5" s="120">
+        <v>1</v>
+      </c>
+      <c r="N5" s="73">
+        <v>1</v>
+      </c>
+      <c r="P5" s="73" t="s">
         <v>936</v>
       </c>
-      <c r="O5" s="73" t="s">
+      <c r="Q5" s="73" t="s">
         <v>937</v>
       </c>
-      <c r="P5" s="73" t="s">
+      <c r="R5" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="Q5" s="73" t="s">
+      <c r="S5" s="73" t="s">
         <v>938</v>
       </c>
-      <c r="R5" s="123" t="s">
+      <c r="T5" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="S5" s="74" t="s">
+      <c r="U5" s="74" t="s">
         <v>915</v>
       </c>
-      <c r="T5" s="123" t="s">
+      <c r="V5" s="123" t="s">
         <v>916</v>
       </c>
-      <c r="U5" s="74" t="s">
+      <c r="W5" s="74" t="s">
         <v>909</v>
       </c>
-      <c r="W5" s="123" t="s">
+      <c r="Y5" s="123" t="s">
         <v>917</v>
       </c>
-      <c r="X5" s="118" t="s">
+      <c r="Z5" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="Y5" s="122" t="s">
+      <c r="AA5" s="122" t="s">
         <v>918</v>
       </c>
-      <c r="AA5" s="123" t="s">
+      <c r="AC5" s="123" t="s">
         <v>917</v>
       </c>
-      <c r="AB5" s="118" t="s">
+      <c r="AD5" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="AC5" s="73" t="s">
+      <c r="AE5" s="73" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" s="101">
         <v>4</v>
       </c>
@@ -49989,70 +50086,76 @@
       <c r="I6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="101">
+        <v>1</v>
+      </c>
+      <c r="K6" s="101">
+        <v>1</v>
+      </c>
+      <c r="L6" s="22">
         <v>2</v>
       </c>
-      <c r="K6" s="12">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
+      <c r="M6" s="12">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
         <v>256</v>
       </c>
-      <c r="N6" t="s">
+      <c r="P6" t="s">
         <v>1007</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>1016</v>
       </c>
-      <c r="P6" s="96" t="s">
+      <c r="R6" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="S6" t="s">
         <v>1017</v>
       </c>
-      <c r="R6" s="20" t="s">
+      <c r="T6" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="U6" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T6" s="20" t="s">
+      <c r="V6" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="U6" s="6" t="s">
+      <c r="W6" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V6" t="s">
+      <c r="X6" t="s">
         <v>945</v>
       </c>
-      <c r="W6" s="112" t="s">
+      <c r="Y6" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X6" s="113" t="s">
+      <c r="Z6" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y6" s="27" t="s">
+      <c r="AA6" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z6" t="s">
+      <c r="AB6" t="s">
         <v>948</v>
       </c>
-      <c r="AA6" s="112" t="s">
+      <c r="AC6" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB6" s="113" t="s">
+      <c r="AD6" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC6" s="25" t="s">
+      <c r="AE6" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A7" s="101">
-        <v>4</v>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A7" s="114">
+        <v>5</v>
       </c>
       <c r="B7" s="110" t="s">
         <v>1034</v>
@@ -50078,70 +50181,76 @@
       <c r="I7" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="101">
+        <v>1</v>
+      </c>
+      <c r="K7" s="101">
+        <v>1</v>
+      </c>
+      <c r="L7" s="22">
         <v>2</v>
       </c>
-      <c r="K7" s="12">
-        <v>1</v>
-      </c>
-      <c r="L7">
+      <c r="M7" s="12">
+        <v>1</v>
+      </c>
+      <c r="N7">
         <v>2</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>512</v>
       </c>
-      <c r="N7" t="s">
+      <c r="P7" t="s">
         <v>1007</v>
       </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
         <v>1016</v>
       </c>
-      <c r="P7" s="96" t="s">
+      <c r="R7" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="S7" t="s">
         <v>1037</v>
       </c>
-      <c r="R7" s="20" t="s">
+      <c r="T7" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="U7" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T7" s="20" t="s">
+      <c r="V7" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="W7" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V7" t="s">
+      <c r="X7" t="s">
         <v>945</v>
       </c>
-      <c r="W7" s="112" t="s">
+      <c r="Y7" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X7" s="113" t="s">
+      <c r="Z7" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y7" s="27" t="s">
+      <c r="AA7" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AB7" t="s">
         <v>948</v>
       </c>
-      <c r="AA7" s="112" t="s">
+      <c r="AC7" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB7" s="113" t="s">
+      <c r="AD7" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC7" s="25" t="s">
+      <c r="AE7" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" s="114">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="110" t="s">
         <v>950</v>
@@ -50167,70 +50276,76 @@
       <c r="I8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="101">
+        <v>1</v>
+      </c>
+      <c r="K8" s="101">
+        <v>1</v>
+      </c>
+      <c r="L8" s="22">
         <v>2</v>
       </c>
-      <c r="K8" s="12">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
+      <c r="M8" s="12">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
         <v>256</v>
       </c>
-      <c r="N8" t="s">
+      <c r="P8" t="s">
         <v>1008</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>1016</v>
       </c>
-      <c r="P8" s="96" t="s">
+      <c r="R8" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="S8" t="s">
         <v>1017</v>
       </c>
-      <c r="R8" s="20" t="s">
+      <c r="T8" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="U8" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T8" s="20" t="s">
+      <c r="V8" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="W8" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V8" t="s">
+      <c r="X8" t="s">
         <v>945</v>
       </c>
-      <c r="W8" s="112" t="s">
+      <c r="Y8" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X8" s="113" t="s">
+      <c r="Z8" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y8" s="27" t="s">
+      <c r="AA8" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AB8" t="s">
         <v>948</v>
       </c>
-      <c r="AA8" s="112" t="s">
+      <c r="AC8" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB8" s="113" t="s">
+      <c r="AD8" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC8" s="25" t="s">
+      <c r="AE8" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" s="114">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" s="110" t="s">
         <v>1035</v>
@@ -50256,70 +50371,76 @@
       <c r="I9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="101">
+        <v>1</v>
+      </c>
+      <c r="K9" s="101">
+        <v>1</v>
+      </c>
+      <c r="L9" s="22">
         <v>2</v>
       </c>
-      <c r="K9" s="12">
-        <v>1</v>
-      </c>
-      <c r="L9">
+      <c r="M9" s="12">
+        <v>1</v>
+      </c>
+      <c r="N9">
         <v>2</v>
       </c>
-      <c r="M9">
+      <c r="O9">
         <v>512</v>
       </c>
-      <c r="N9" t="s">
+      <c r="P9" t="s">
         <v>1008</v>
       </c>
-      <c r="O9" t="s">
+      <c r="Q9" t="s">
         <v>1016</v>
       </c>
-      <c r="P9" s="96" t="s">
+      <c r="R9" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="S9" t="s">
         <v>1037</v>
       </c>
-      <c r="R9" s="20" t="s">
+      <c r="T9" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="U9" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T9" s="20" t="s">
+      <c r="V9" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="W9" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V9" t="s">
+      <c r="X9" t="s">
         <v>945</v>
       </c>
-      <c r="W9" s="112" t="s">
+      <c r="Y9" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X9" s="113" t="s">
+      <c r="Z9" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y9" s="27" t="s">
+      <c r="AA9" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z9" t="s">
+      <c r="AB9" t="s">
         <v>948</v>
       </c>
-      <c r="AA9" s="112" t="s">
+      <c r="AC9" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB9" s="113" t="s">
+      <c r="AD9" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC9" s="25" t="s">
+      <c r="AE9" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="73" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="114">
-        <v>6</v>
+    <row r="10" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="101">
+        <v>8</v>
       </c>
       <c r="B10" s="116" t="s">
         <v>952</v>
@@ -50345,70 +50466,76 @@
       <c r="I10" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="119">
+      <c r="J10" s="101">
+        <v>1</v>
+      </c>
+      <c r="K10" s="101">
+        <v>1</v>
+      </c>
+      <c r="L10" s="119">
         <v>2</v>
       </c>
-      <c r="K10" s="120">
-        <v>1</v>
-      </c>
-      <c r="L10" s="73">
-        <v>1</v>
-      </c>
-      <c r="M10" s="73">
+      <c r="M10" s="120">
+        <v>1</v>
+      </c>
+      <c r="N10" s="73">
+        <v>1</v>
+      </c>
+      <c r="O10" s="73">
         <v>256</v>
       </c>
-      <c r="N10" s="73" t="s">
+      <c r="P10" s="73" t="s">
         <v>1009</v>
       </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
         <v>1016</v>
       </c>
-      <c r="P10" s="73" t="s">
+      <c r="R10" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="Q10" s="73" t="s">
+      <c r="S10" s="73" t="s">
         <v>1017</v>
       </c>
-      <c r="R10" s="80" t="s">
+      <c r="T10" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="S10" s="74" t="s">
+      <c r="U10" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="T10" s="80" t="s">
+      <c r="V10" s="80" t="s">
         <v>775</v>
       </c>
-      <c r="U10" s="74" t="s">
+      <c r="W10" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="V10" s="73" t="s">
+      <c r="X10" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="W10" s="121" t="s">
+      <c r="Y10" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="X10" s="124" t="s">
+      <c r="Z10" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="Y10" s="85" t="s">
+      <c r="AA10" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="Z10" s="73" t="s">
+      <c r="AB10" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AA10" s="121" t="s">
+      <c r="AC10" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AB10" s="124" t="s">
+      <c r="AD10" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AC10" s="122" t="s">
+      <c r="AE10" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="114">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11" s="116" t="s">
         <v>1036</v>
@@ -50434,70 +50561,76 @@
       <c r="I11" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="101">
+        <v>1</v>
+      </c>
+      <c r="K11" s="101">
+        <v>1</v>
+      </c>
+      <c r="L11" s="119">
         <v>2</v>
       </c>
-      <c r="K11" s="120">
-        <v>1</v>
-      </c>
-      <c r="L11" s="73">
+      <c r="M11" s="120">
+        <v>1</v>
+      </c>
+      <c r="N11" s="73">
         <v>2</v>
       </c>
-      <c r="M11" s="73">
+      <c r="O11" s="73">
         <v>512</v>
       </c>
-      <c r="N11" s="73" t="s">
+      <c r="P11" s="73" t="s">
         <v>1009</v>
       </c>
-      <c r="O11" t="s">
+      <c r="Q11" t="s">
         <v>1016</v>
       </c>
-      <c r="P11" s="73" t="s">
+      <c r="R11" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="Q11" s="73" t="s">
+      <c r="S11" s="73" t="s">
         <v>1037</v>
       </c>
-      <c r="R11" s="80" t="s">
+      <c r="T11" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="S11" s="74" t="s">
+      <c r="U11" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="T11" s="80" t="s">
+      <c r="V11" s="80" t="s">
         <v>775</v>
       </c>
-      <c r="U11" s="74" t="s">
+      <c r="W11" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="V11" s="73" t="s">
+      <c r="X11" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="W11" s="121" t="s">
+      <c r="Y11" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="X11" s="124" t="s">
+      <c r="Z11" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="Y11" s="85" t="s">
+      <c r="AA11" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="Z11" s="73" t="s">
+      <c r="AB11" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AA11" s="121" t="s">
+      <c r="AC11" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AB11" s="124" t="s">
+      <c r="AD11" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AC11" s="122" t="s">
+      <c r="AE11" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A12" s="101">
-        <v>7</v>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A12" s="114">
+        <v>10</v>
       </c>
       <c r="B12" s="110" t="s">
         <v>954</v>
@@ -50523,70 +50656,76 @@
       <c r="I12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12" s="101">
+        <v>1</v>
+      </c>
+      <c r="K12" s="101">
+        <v>1</v>
+      </c>
+      <c r="L12" s="22">
         <v>2</v>
       </c>
-      <c r="K12" s="12">
-        <v>1</v>
-      </c>
-      <c r="L12" s="95">
-        <v>1</v>
-      </c>
-      <c r="M12" s="95">
+      <c r="M12" s="12">
+        <v>1</v>
+      </c>
+      <c r="N12" s="95">
+        <v>1</v>
+      </c>
+      <c r="O12" s="95">
         <v>576</v>
       </c>
-      <c r="N12" t="s">
+      <c r="P12" t="s">
         <v>1010</v>
       </c>
-      <c r="O12" t="s">
+      <c r="Q12" t="s">
         <v>1018</v>
       </c>
-      <c r="P12" s="96" t="s">
+      <c r="R12" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="S12" t="s">
         <v>1019</v>
       </c>
-      <c r="R12" s="20" t="s">
+      <c r="T12" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S12" s="6" t="s">
+      <c r="U12" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T12" s="20" t="s">
+      <c r="V12" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="U12" s="6" t="s">
+      <c r="W12" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V12" t="s">
+      <c r="X12" t="s">
         <v>945</v>
       </c>
-      <c r="W12" s="112" t="s">
+      <c r="Y12" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X12" s="113" t="s">
+      <c r="Z12" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y12" s="27" t="s">
+      <c r="AA12" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z12" t="s">
+      <c r="AB12" t="s">
         <v>948</v>
       </c>
-      <c r="AA12" s="112" t="s">
+      <c r="AC12" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB12" s="113" t="s">
+      <c r="AD12" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC12" s="25" t="s">
+      <c r="AE12" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A13" s="101">
-        <v>7</v>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A13" s="114">
+        <v>11</v>
       </c>
       <c r="B13" s="110" t="s">
         <v>1042</v>
@@ -50612,70 +50751,76 @@
       <c r="I13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="101">
+        <v>1</v>
+      </c>
+      <c r="K13" s="101">
+        <v>1</v>
+      </c>
+      <c r="L13" s="22">
         <v>2</v>
       </c>
-      <c r="K13" s="12">
-        <v>1</v>
-      </c>
-      <c r="L13" s="95">
-        <v>1</v>
-      </c>
-      <c r="M13" s="95">
+      <c r="M13" s="12">
+        <v>1</v>
+      </c>
+      <c r="N13" s="95">
+        <v>1</v>
+      </c>
+      <c r="O13" s="95">
         <v>576</v>
       </c>
-      <c r="N13" t="s">
+      <c r="P13" t="s">
         <v>1010</v>
       </c>
-      <c r="O13" t="s">
+      <c r="Q13" t="s">
         <v>1018</v>
       </c>
-      <c r="P13" s="96" t="s">
+      <c r="R13" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="S13" t="s">
         <v>1045</v>
       </c>
-      <c r="R13" s="20" t="s">
+      <c r="T13" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S13" s="6" t="s">
+      <c r="U13" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T13" s="20" t="s">
+      <c r="V13" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="W13" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V13" t="s">
+      <c r="X13" t="s">
         <v>945</v>
       </c>
-      <c r="W13" s="112" t="s">
+      <c r="Y13" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X13" s="113" t="s">
+      <c r="Z13" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y13" s="27" t="s">
+      <c r="AA13" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z13" t="s">
+      <c r="AB13" t="s">
         <v>948</v>
       </c>
-      <c r="AA13" s="112" t="s">
+      <c r="AC13" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB13" s="113" t="s">
+      <c r="AD13" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC13" s="25" t="s">
+      <c r="AE13" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A14" s="114">
-        <v>8</v>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A14" s="101">
+        <v>12</v>
       </c>
       <c r="B14" s="110" t="s">
         <v>957</v>
@@ -50701,70 +50846,76 @@
       <c r="I14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="101">
+        <v>1</v>
+      </c>
+      <c r="K14" s="101">
+        <v>1</v>
+      </c>
+      <c r="L14" s="22">
         <v>2</v>
       </c>
-      <c r="K14" s="12">
-        <v>1</v>
-      </c>
-      <c r="L14" s="95">
-        <v>1</v>
-      </c>
-      <c r="M14" s="95">
+      <c r="M14" s="12">
+        <v>1</v>
+      </c>
+      <c r="N14" s="95">
+        <v>1</v>
+      </c>
+      <c r="O14" s="95">
         <v>576</v>
       </c>
-      <c r="N14" t="s">
+      <c r="P14" t="s">
         <v>1011</v>
       </c>
-      <c r="O14" t="s">
+      <c r="Q14" t="s">
         <v>1018</v>
       </c>
-      <c r="P14" s="96" t="s">
+      <c r="R14" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="S14" t="s">
         <v>1019</v>
       </c>
-      <c r="R14" s="20" t="s">
+      <c r="T14" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S14" s="6" t="s">
+      <c r="U14" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T14" s="20" t="s">
+      <c r="V14" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="U14" s="6" t="s">
+      <c r="W14" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V14" t="s">
+      <c r="X14" t="s">
         <v>945</v>
       </c>
-      <c r="W14" s="112" t="s">
+      <c r="Y14" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X14" s="113" t="s">
+      <c r="Z14" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y14" s="27" t="s">
+      <c r="AA14" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z14" t="s">
+      <c r="AB14" t="s">
         <v>948</v>
       </c>
-      <c r="AA14" s="112" t="s">
+      <c r="AC14" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB14" s="113" t="s">
+      <c r="AD14" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC14" s="25" t="s">
+      <c r="AE14" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" s="114">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B15" s="110" t="s">
         <v>1043</v>
@@ -50790,70 +50941,76 @@
       <c r="I15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="101">
+        <v>1</v>
+      </c>
+      <c r="K15" s="101">
+        <v>1</v>
+      </c>
+      <c r="L15" s="22">
         <v>2</v>
       </c>
-      <c r="K15" s="12">
-        <v>1</v>
-      </c>
-      <c r="L15" s="95">
-        <v>1</v>
-      </c>
-      <c r="M15" s="95">
+      <c r="M15" s="12">
+        <v>1</v>
+      </c>
+      <c r="N15" s="95">
+        <v>1</v>
+      </c>
+      <c r="O15" s="95">
         <v>576</v>
       </c>
-      <c r="N15" t="s">
+      <c r="P15" t="s">
         <v>1011</v>
       </c>
-      <c r="O15" t="s">
+      <c r="Q15" t="s">
         <v>1018</v>
       </c>
-      <c r="P15" s="96" t="s">
+      <c r="R15" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="S15" t="s">
         <v>1045</v>
       </c>
-      <c r="R15" s="20" t="s">
+      <c r="T15" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="U15" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T15" s="20" t="s">
+      <c r="V15" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="U15" s="6" t="s">
+      <c r="W15" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="V15" t="s">
+      <c r="X15" t="s">
         <v>945</v>
       </c>
-      <c r="W15" s="112" t="s">
+      <c r="Y15" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X15" s="113" t="s">
+      <c r="Z15" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y15" s="27" t="s">
+      <c r="AA15" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z15" t="s">
+      <c r="AB15" t="s">
         <v>948</v>
       </c>
-      <c r="AA15" s="112" t="s">
+      <c r="AC15" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB15" s="113" t="s">
+      <c r="AD15" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC15" s="25" t="s">
+      <c r="AE15" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="114">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B16" s="116" t="s">
         <v>959</v>
@@ -50879,70 +51036,76 @@
       <c r="I16" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="119">
+      <c r="J16" s="101">
+        <v>1</v>
+      </c>
+      <c r="K16" s="101">
+        <v>1</v>
+      </c>
+      <c r="L16" s="119">
         <v>2</v>
       </c>
-      <c r="K16" s="120">
-        <v>1</v>
-      </c>
-      <c r="L16" s="73">
-        <v>1</v>
-      </c>
-      <c r="M16" s="73">
+      <c r="M16" s="120">
+        <v>1</v>
+      </c>
+      <c r="N16" s="73">
+        <v>1</v>
+      </c>
+      <c r="O16" s="73">
         <v>576</v>
       </c>
-      <c r="N16" s="73" t="s">
+      <c r="P16" s="73" t="s">
         <v>1012</v>
       </c>
-      <c r="O16" s="73" t="s">
+      <c r="Q16" s="73" t="s">
         <v>1018</v>
       </c>
-      <c r="P16" s="73" t="s">
+      <c r="R16" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="Q16" s="73" t="s">
+      <c r="S16" s="73" t="s">
         <v>1019</v>
       </c>
-      <c r="R16" s="80" t="s">
+      <c r="T16" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="S16" s="74" t="s">
+      <c r="U16" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="T16" s="80" t="s">
+      <c r="V16" s="80" t="s">
         <v>776</v>
       </c>
-      <c r="U16" s="74" t="s">
+      <c r="W16" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="V16" s="73" t="s">
+      <c r="X16" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="W16" s="121" t="s">
+      <c r="Y16" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="X16" s="124" t="s">
+      <c r="Z16" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="Y16" s="85" t="s">
+      <c r="AA16" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="Z16" s="73" t="s">
+      <c r="AB16" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AA16" s="121" t="s">
+      <c r="AC16" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AB16" s="124" t="s">
+      <c r="AD16" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AC16" s="122" t="s">
+      <c r="AE16" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="114">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B17" s="116" t="s">
         <v>1044</v>
@@ -50968,70 +51131,76 @@
       <c r="I17" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="119">
+      <c r="J17" s="101">
+        <v>1</v>
+      </c>
+      <c r="K17" s="101">
+        <v>1</v>
+      </c>
+      <c r="L17" s="119">
         <v>2</v>
       </c>
-      <c r="K17" s="120">
-        <v>1</v>
-      </c>
-      <c r="L17" s="73">
-        <v>1</v>
-      </c>
-      <c r="M17" s="73">
+      <c r="M17" s="120">
+        <v>1</v>
+      </c>
+      <c r="N17" s="73">
+        <v>1</v>
+      </c>
+      <c r="O17" s="73">
         <v>576</v>
       </c>
-      <c r="N17" s="73" t="s">
+      <c r="P17" s="73" t="s">
         <v>1012</v>
       </c>
-      <c r="O17" s="73" t="s">
+      <c r="Q17" s="73" t="s">
         <v>1018</v>
       </c>
-      <c r="P17" s="73" t="s">
+      <c r="R17" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="Q17" s="73" t="s">
+      <c r="S17" s="73" t="s">
         <v>1045</v>
       </c>
-      <c r="R17" s="80" t="s">
+      <c r="T17" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="S17" s="74" t="s">
+      <c r="U17" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="T17" s="80" t="s">
+      <c r="V17" s="80" t="s">
         <v>776</v>
       </c>
-      <c r="U17" s="74" t="s">
+      <c r="W17" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="V17" s="73" t="s">
+      <c r="X17" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="W17" s="121" t="s">
+      <c r="Y17" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="X17" s="124" t="s">
+      <c r="Z17" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="Y17" s="85" t="s">
+      <c r="AA17" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="Z17" s="73" t="s">
+      <c r="AB17" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AA17" s="121" t="s">
+      <c r="AC17" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AB17" s="124" t="s">
+      <c r="AD17" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AC17" s="122" t="s">
+      <c r="AE17" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="101">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B18" s="110" t="s">
         <v>961</v>
@@ -51057,70 +51226,76 @@
       <c r="I18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="22">
-        <v>1</v>
-      </c>
-      <c r="K18" s="12">
-        <v>1</v>
-      </c>
-      <c r="L18" s="96">
-        <v>1</v>
-      </c>
-      <c r="M18" s="95">
+      <c r="J18" s="101">
+        <v>1</v>
+      </c>
+      <c r="K18" s="101">
+        <v>1</v>
+      </c>
+      <c r="L18" s="22">
+        <v>1</v>
+      </c>
+      <c r="M18" s="12">
+        <v>1</v>
+      </c>
+      <c r="N18" s="96">
+        <v>1</v>
+      </c>
+      <c r="O18" s="95">
         <v>576</v>
       </c>
-      <c r="N18" t="s">
+      <c r="P18" t="s">
         <v>1013</v>
       </c>
-      <c r="O18" t="s">
+      <c r="Q18" t="s">
         <v>1020</v>
       </c>
-      <c r="P18" s="107" t="s">
+      <c r="R18" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="S18" t="s">
         <v>1021</v>
       </c>
-      <c r="R18" s="20" t="s">
+      <c r="T18" s="20" t="s">
         <v>963</v>
       </c>
-      <c r="S18" s="6" t="s">
+      <c r="U18" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T18" s="20" t="s">
+      <c r="V18" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="U18" s="6" t="s">
+      <c r="W18" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="V18" t="s">
+      <c r="X18" t="s">
         <v>965</v>
       </c>
-      <c r="W18" s="112" t="s">
+      <c r="Y18" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X18" s="113" t="s">
+      <c r="Z18" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y18" s="27" t="s">
+      <c r="AA18" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AB18" t="s">
         <v>968</v>
       </c>
-      <c r="AA18" s="112" t="s">
+      <c r="AC18" s="112" t="s">
         <v>754</v>
       </c>
-      <c r="AB18" s="113" t="s">
+      <c r="AD18" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC18" s="27" t="s">
+      <c r="AE18" s="27" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="114">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B19" s="110" t="s">
         <v>970</v>
@@ -51146,70 +51321,76 @@
       <c r="I19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="22">
-        <v>1</v>
-      </c>
-      <c r="K19" s="12">
-        <v>1</v>
-      </c>
-      <c r="L19" s="96">
-        <v>1</v>
-      </c>
-      <c r="M19" s="95">
+      <c r="J19" s="101">
+        <v>1</v>
+      </c>
+      <c r="K19" s="101">
+        <v>1</v>
+      </c>
+      <c r="L19" s="22">
+        <v>1</v>
+      </c>
+      <c r="M19" s="12">
+        <v>1</v>
+      </c>
+      <c r="N19" s="96">
+        <v>1</v>
+      </c>
+      <c r="O19" s="95">
         <v>576</v>
       </c>
-      <c r="N19" t="s">
+      <c r="P19" t="s">
         <v>1014</v>
       </c>
-      <c r="O19" t="s">
+      <c r="Q19" t="s">
         <v>1020</v>
       </c>
-      <c r="P19" s="96" t="s">
+      <c r="R19" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="S19" t="s">
         <v>1021</v>
       </c>
-      <c r="R19" s="20" t="s">
+      <c r="T19" s="20" t="s">
         <v>963</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="U19" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T19" s="20" t="s">
+      <c r="V19" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="U19" s="6" t="s">
+      <c r="W19" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="V19" t="s">
+      <c r="X19" t="s">
         <v>965</v>
       </c>
-      <c r="W19" s="112" t="s">
+      <c r="Y19" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X19" s="113" t="s">
+      <c r="Z19" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y19" s="27" t="s">
+      <c r="AA19" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AB19" t="s">
         <v>968</v>
       </c>
-      <c r="AA19" s="112" t="s">
+      <c r="AC19" s="112" t="s">
         <v>754</v>
       </c>
-      <c r="AB19" s="113" t="s">
+      <c r="AD19" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC19" s="27" t="s">
+      <c r="AE19" s="27" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="114">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B20" s="110" t="s">
         <v>972</v>
@@ -51235,70 +51416,76 @@
       <c r="I20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J20" s="22">
-        <v>1</v>
-      </c>
-      <c r="K20" s="12">
-        <v>1</v>
-      </c>
-      <c r="L20" s="96">
-        <v>1</v>
-      </c>
-      <c r="M20" s="95">
+      <c r="J20" s="101">
+        <v>1</v>
+      </c>
+      <c r="K20" s="101">
+        <v>1</v>
+      </c>
+      <c r="L20" s="22">
+        <v>1</v>
+      </c>
+      <c r="M20" s="12">
+        <v>1</v>
+      </c>
+      <c r="N20" s="96">
+        <v>1</v>
+      </c>
+      <c r="O20" s="95">
         <v>576</v>
       </c>
-      <c r="N20" t="s">
+      <c r="P20" t="s">
         <v>1015</v>
       </c>
-      <c r="O20" t="s">
+      <c r="Q20" t="s">
         <v>1020</v>
       </c>
-      <c r="P20" s="96" t="s">
+      <c r="R20" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="S20" t="s">
         <v>1021</v>
       </c>
-      <c r="R20" s="20" t="s">
+      <c r="T20" s="20" t="s">
         <v>963</v>
       </c>
-      <c r="S20" s="6" t="s">
+      <c r="U20" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T20" s="20" t="s">
+      <c r="V20" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="U20" s="6" t="s">
+      <c r="W20" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="V20" t="s">
+      <c r="X20" t="s">
         <v>965</v>
       </c>
-      <c r="W20" s="112" t="s">
+      <c r="Y20" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X20" s="113" t="s">
+      <c r="Z20" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y20" s="27" t="s">
+      <c r="AA20" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AB20" t="s">
         <v>968</v>
       </c>
-      <c r="AA20" s="112" t="s">
+      <c r="AC20" s="112" t="s">
         <v>754</v>
       </c>
-      <c r="AB20" s="113" t="s">
+      <c r="AD20" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC20" s="27" t="s">
+      <c r="AE20" s="27" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="107" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="101">
-        <v>13</v>
+    <row r="21" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="114">
+        <v>19</v>
       </c>
       <c r="B21" s="102" t="s">
         <v>974</v>
@@ -51324,70 +51511,76 @@
       <c r="I21" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="105">
+      <c r="J21" s="101">
+        <v>1</v>
+      </c>
+      <c r="K21" s="101">
+        <v>1</v>
+      </c>
+      <c r="L21" s="105">
         <v>2</v>
       </c>
-      <c r="K21" s="106">
-        <v>1</v>
-      </c>
-      <c r="L21" s="107">
-        <v>1</v>
-      </c>
-      <c r="M21" s="107">
+      <c r="M21" s="106">
+        <v>1</v>
+      </c>
+      <c r="N21" s="107">
+        <v>1</v>
+      </c>
+      <c r="O21" s="107">
         <v>256</v>
       </c>
-      <c r="N21" s="107" t="s">
+      <c r="P21" s="107" t="s">
         <v>998</v>
       </c>
-      <c r="O21" s="107" t="s">
+      <c r="Q21" s="107" t="s">
         <v>1001</v>
       </c>
-      <c r="P21" s="107" t="s">
+      <c r="R21" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="Q21" s="107" t="s">
+      <c r="S21" s="107" t="s">
         <v>1002</v>
       </c>
-      <c r="R21" s="126" t="s">
+      <c r="T21" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="S21" s="101" t="s">
+      <c r="U21" s="101" t="s">
         <v>977</v>
       </c>
-      <c r="T21" s="126" t="s">
+      <c r="V21" s="126" t="s">
         <v>773</v>
       </c>
-      <c r="U21" s="101" t="s">
+      <c r="W21" s="101" t="s">
         <v>792</v>
       </c>
-      <c r="V21" s="107" t="s">
+      <c r="X21" s="107" t="s">
         <v>965</v>
       </c>
-      <c r="W21" s="127" t="s">
+      <c r="Y21" s="127" t="s">
         <v>747</v>
       </c>
-      <c r="X21" s="128" t="s">
+      <c r="Z21" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="Y21" s="129" t="s">
+      <c r="AA21" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="Z21" s="107" t="s">
+      <c r="AB21" s="107" t="s">
         <v>978</v>
       </c>
-      <c r="AA21" s="127" t="s">
+      <c r="AC21" s="127" t="s">
         <v>753</v>
       </c>
-      <c r="AB21" s="128" t="s">
+      <c r="AD21" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="AC21" s="109" t="s">
+      <c r="AE21" s="109" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A22" s="114">
-        <v>14</v>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A22" s="101">
+        <v>20</v>
       </c>
       <c r="B22" s="110" t="s">
         <v>1003</v>
@@ -51413,70 +51606,76 @@
       <c r="I22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22" s="101">
+        <v>1</v>
+      </c>
+      <c r="K22" s="101">
+        <v>1</v>
+      </c>
+      <c r="L22" s="22">
         <v>2</v>
       </c>
-      <c r="K22" s="12">
-        <v>1</v>
-      </c>
-      <c r="L22" s="96">
+      <c r="M22" s="12">
+        <v>1</v>
+      </c>
+      <c r="N22" s="96">
         <v>2</v>
       </c>
-      <c r="M22">
+      <c r="O22">
         <v>512</v>
       </c>
-      <c r="N22" t="s">
+      <c r="P22" t="s">
         <v>998</v>
       </c>
-      <c r="O22" t="s">
+      <c r="Q22" t="s">
         <v>1001</v>
       </c>
-      <c r="P22" s="96" t="s">
+      <c r="R22" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="S22" t="s">
         <v>1006</v>
       </c>
-      <c r="R22" s="20" t="s">
+      <c r="T22" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S22" s="6" t="s">
+      <c r="U22" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T22" s="20" t="s">
+      <c r="V22" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="U22" s="6" t="s">
+      <c r="W22" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V22" t="s">
+      <c r="X22" t="s">
         <v>965</v>
       </c>
-      <c r="W22" s="112" t="s">
+      <c r="Y22" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X22" s="113" t="s">
+      <c r="Z22" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y22" s="27" t="s">
+      <c r="AA22" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AB22" t="s">
         <v>978</v>
       </c>
-      <c r="AA22" s="112" t="s">
+      <c r="AC22" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB22" s="113" t="s">
+      <c r="AD22" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC22" s="25" t="s">
+      <c r="AE22" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A23" s="114">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B23" s="110" t="s">
         <v>1046</v>
@@ -51502,70 +51701,76 @@
       <c r="I23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23" s="101">
+        <v>1</v>
+      </c>
+      <c r="K23" s="101">
+        <v>1</v>
+      </c>
+      <c r="L23" s="22">
         <v>2</v>
       </c>
-      <c r="K23" s="12">
-        <v>1</v>
-      </c>
-      <c r="L23" s="96">
+      <c r="M23" s="12">
+        <v>1</v>
+      </c>
+      <c r="N23" s="96">
         <v>2</v>
       </c>
-      <c r="M23">
+      <c r="O23">
         <v>512</v>
       </c>
-      <c r="N23" t="s">
+      <c r="P23" t="s">
         <v>998</v>
       </c>
-      <c r="O23" t="s">
+      <c r="Q23" t="s">
         <v>1001</v>
       </c>
-      <c r="P23" s="96" t="s">
+      <c r="R23" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="S23" t="s">
         <v>1052</v>
       </c>
-      <c r="R23" s="20" t="s">
+      <c r="T23" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S23" s="6" t="s">
+      <c r="U23" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T23" s="20" t="s">
+      <c r="V23" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="U23" s="6" t="s">
+      <c r="W23" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V23" t="s">
+      <c r="X23" t="s">
         <v>965</v>
       </c>
-      <c r="W23" s="112" t="s">
+      <c r="Y23" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X23" s="113" t="s">
+      <c r="Z23" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y23" s="27" t="s">
+      <c r="AA23" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="AB23" t="s">
         <v>978</v>
       </c>
-      <c r="AA23" s="112" t="s">
+      <c r="AC23" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB23" s="113" t="s">
+      <c r="AD23" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC23" s="25" t="s">
+      <c r="AE23" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A24" s="114">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B24" s="110" t="s">
         <v>1047</v>
@@ -51591,70 +51796,76 @@
       <c r="I24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24" s="101">
+        <v>1</v>
+      </c>
+      <c r="K24" s="101">
+        <v>1</v>
+      </c>
+      <c r="L24" s="22">
         <v>2</v>
       </c>
-      <c r="K24" s="12">
-        <v>1</v>
-      </c>
-      <c r="L24" s="96">
+      <c r="M24" s="12">
+        <v>1</v>
+      </c>
+      <c r="N24" s="96">
         <v>2</v>
       </c>
-      <c r="M24">
+      <c r="O24">
         <v>512</v>
       </c>
-      <c r="N24" t="s">
+      <c r="P24" t="s">
         <v>998</v>
       </c>
-      <c r="O24" t="s">
+      <c r="Q24" t="s">
         <v>1001</v>
       </c>
-      <c r="P24" s="96" t="s">
+      <c r="R24" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="S24" t="s">
         <v>1053</v>
       </c>
-      <c r="R24" s="20" t="s">
+      <c r="T24" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S24" s="6" t="s">
+      <c r="U24" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T24" s="20" t="s">
+      <c r="V24" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="U24" s="6" t="s">
+      <c r="W24" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V24" t="s">
+      <c r="X24" t="s">
         <v>965</v>
       </c>
-      <c r="W24" s="112" t="s">
+      <c r="Y24" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X24" s="113" t="s">
+      <c r="Z24" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y24" s="27" t="s">
+      <c r="AA24" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AB24" t="s">
         <v>978</v>
       </c>
-      <c r="AA24" s="112" t="s">
+      <c r="AC24" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB24" s="113" t="s">
+      <c r="AD24" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC24" s="25" t="s">
+      <c r="AE24" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A25" s="114">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B25" s="110" t="s">
         <v>1070</v>
@@ -51680,70 +51891,76 @@
       <c r="I25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="101">
+        <v>1</v>
+      </c>
+      <c r="K25" s="101">
+        <v>1</v>
+      </c>
+      <c r="L25" s="22">
         <v>2</v>
       </c>
-      <c r="K25" s="12">
-        <v>1</v>
-      </c>
-      <c r="L25" s="96">
+      <c r="M25" s="12">
+        <v>1</v>
+      </c>
+      <c r="N25" s="96">
         <v>2</v>
       </c>
-      <c r="M25">
+      <c r="O25">
         <v>512</v>
       </c>
-      <c r="N25" t="s">
+      <c r="P25" t="s">
         <v>998</v>
       </c>
-      <c r="O25" t="s">
+      <c r="Q25" t="s">
         <v>1001</v>
       </c>
-      <c r="P25" s="96" t="s">
+      <c r="R25" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="S25" t="s">
         <v>1072</v>
       </c>
-      <c r="R25" s="20" t="s">
+      <c r="T25" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S25" s="6" t="s">
+      <c r="U25" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T25" s="20" t="s">
+      <c r="V25" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="U25" s="6" t="s">
+      <c r="W25" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V25" t="s">
+      <c r="X25" t="s">
         <v>965</v>
       </c>
-      <c r="W25" s="112" t="s">
+      <c r="Y25" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X25" s="113" t="s">
+      <c r="Z25" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y25" s="27" t="s">
+      <c r="AA25" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AB25" t="s">
         <v>978</v>
       </c>
-      <c r="AA25" s="112" t="s">
+      <c r="AC25" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB25" s="113" t="s">
+      <c r="AD25" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC25" s="25" t="s">
+      <c r="AE25" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A26" s="114">
-        <v>14</v>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A26" s="101">
+        <v>24</v>
       </c>
       <c r="B26" s="110" t="s">
         <v>1071</v>
@@ -51769,70 +51986,76 @@
       <c r="I26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="22">
+      <c r="J26" s="101">
+        <v>1</v>
+      </c>
+      <c r="K26" s="101">
+        <v>1</v>
+      </c>
+      <c r="L26" s="22">
         <v>2</v>
       </c>
-      <c r="K26" s="12">
-        <v>1</v>
-      </c>
-      <c r="L26" s="96">
+      <c r="M26" s="12">
+        <v>1</v>
+      </c>
+      <c r="N26" s="96">
         <v>2</v>
       </c>
-      <c r="M26">
+      <c r="O26">
         <v>512</v>
       </c>
-      <c r="N26" t="s">
+      <c r="P26" t="s">
         <v>998</v>
       </c>
-      <c r="O26" t="s">
+      <c r="Q26" t="s">
         <v>1001</v>
       </c>
-      <c r="P26" s="96" t="s">
+      <c r="R26" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="S26" t="s">
         <v>1073</v>
       </c>
-      <c r="R26" s="20" t="s">
+      <c r="T26" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S26" s="6" t="s">
+      <c r="U26" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T26" s="20" t="s">
+      <c r="V26" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="U26" s="6" t="s">
+      <c r="W26" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V26" t="s">
+      <c r="X26" t="s">
         <v>965</v>
       </c>
-      <c r="W26" s="112" t="s">
+      <c r="Y26" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X26" s="113" t="s">
+      <c r="Z26" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y26" s="27" t="s">
+      <c r="AA26" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AB26" t="s">
         <v>978</v>
       </c>
-      <c r="AA26" s="112" t="s">
+      <c r="AC26" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB26" s="113" t="s">
+      <c r="AD26" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC26" s="25" t="s">
+      <c r="AE26" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A27" s="114">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B27" s="110" t="s">
         <v>1082</v>
@@ -51858,70 +52081,76 @@
       <c r="I27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J27" s="22">
+      <c r="J27" s="101">
+        <v>1</v>
+      </c>
+      <c r="K27" s="101">
+        <v>1</v>
+      </c>
+      <c r="L27" s="22">
         <v>2</v>
       </c>
-      <c r="K27" s="12">
-        <v>1</v>
-      </c>
-      <c r="L27" s="96">
+      <c r="M27" s="12">
+        <v>1</v>
+      </c>
+      <c r="N27" s="96">
         <v>2</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>512</v>
       </c>
-      <c r="N27" t="s">
+      <c r="P27" t="s">
         <v>998</v>
       </c>
-      <c r="O27" t="s">
+      <c r="Q27" t="s">
         <v>1001</v>
       </c>
-      <c r="P27" s="96" t="s">
+      <c r="R27" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="S27" t="s">
         <v>1081</v>
       </c>
-      <c r="R27" s="20" t="s">
+      <c r="T27" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S27" s="6" t="s">
+      <c r="U27" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T27" s="20" t="s">
+      <c r="V27" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="U27" s="6" t="s">
+      <c r="W27" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V27" t="s">
+      <c r="X27" t="s">
         <v>965</v>
       </c>
-      <c r="W27" s="112" t="s">
+      <c r="Y27" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X27" s="113" t="s">
+      <c r="Z27" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y27" s="27" t="s">
+      <c r="AA27" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z27" t="s">
+      <c r="AB27" t="s">
         <v>978</v>
       </c>
-      <c r="AA27" s="112" t="s">
+      <c r="AC27" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB27" s="113" t="s">
+      <c r="AD27" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC27" s="25" t="s">
+      <c r="AE27" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A28" s="114">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B28" s="110" t="s">
         <v>1032</v>
@@ -51947,70 +52176,76 @@
       <c r="I28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="22">
+      <c r="J28" s="101">
+        <v>1</v>
+      </c>
+      <c r="K28" s="101">
+        <v>1</v>
+      </c>
+      <c r="L28" s="22">
         <v>2</v>
       </c>
-      <c r="K28" s="12">
-        <v>1</v>
-      </c>
-      <c r="L28" s="96">
-        <v>1</v>
-      </c>
-      <c r="M28">
+      <c r="M28" s="12">
+        <v>1</v>
+      </c>
+      <c r="N28" s="96">
+        <v>1</v>
+      </c>
+      <c r="O28">
         <v>256</v>
       </c>
-      <c r="N28" t="s">
+      <c r="P28" t="s">
         <v>999</v>
       </c>
-      <c r="O28" t="s">
+      <c r="Q28" t="s">
         <v>1001</v>
       </c>
-      <c r="P28" s="96" t="s">
+      <c r="R28" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="S28" t="s">
         <v>1002</v>
       </c>
-      <c r="R28" s="20" t="s">
+      <c r="T28" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S28" s="6" t="s">
+      <c r="U28" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T28" s="28" t="s">
+      <c r="V28" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U28" s="6" t="s">
+      <c r="W28" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V28" t="s">
+      <c r="X28" t="s">
         <v>965</v>
       </c>
-      <c r="W28" s="112" t="s">
+      <c r="Y28" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X28" s="113" t="s">
+      <c r="Z28" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y28" s="27" t="s">
+      <c r="AA28" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AB28" t="s">
         <v>978</v>
       </c>
-      <c r="AA28" s="112" t="s">
+      <c r="AC28" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB28" s="113" t="s">
+      <c r="AD28" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC28" s="25" t="s">
+      <c r="AE28" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A29" s="114">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B29" s="110" t="s">
         <v>1004</v>
@@ -52036,70 +52271,76 @@
       <c r="I29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J29" s="22">
+      <c r="J29" s="101">
+        <v>1</v>
+      </c>
+      <c r="K29" s="101">
+        <v>1</v>
+      </c>
+      <c r="L29" s="22">
         <v>2</v>
       </c>
-      <c r="K29" s="12">
-        <v>1</v>
-      </c>
-      <c r="L29" s="96">
+      <c r="M29" s="12">
+        <v>1</v>
+      </c>
+      <c r="N29" s="96">
         <v>2</v>
       </c>
-      <c r="M29">
+      <c r="O29">
         <v>512</v>
       </c>
-      <c r="N29" t="s">
+      <c r="P29" t="s">
         <v>999</v>
       </c>
-      <c r="O29" t="s">
+      <c r="Q29" t="s">
         <v>1001</v>
       </c>
-      <c r="P29" s="96" t="s">
+      <c r="R29" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="S29" t="s">
         <v>1006</v>
       </c>
-      <c r="R29" s="20" t="s">
+      <c r="T29" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S29" s="6" t="s">
+      <c r="U29" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T29" s="28" t="s">
+      <c r="V29" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U29" s="6" t="s">
+      <c r="W29" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V29" t="s">
+      <c r="X29" t="s">
         <v>965</v>
       </c>
-      <c r="W29" s="112" t="s">
+      <c r="Y29" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X29" s="113" t="s">
+      <c r="Z29" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y29" s="27" t="s">
+      <c r="AA29" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AB29" t="s">
         <v>978</v>
       </c>
-      <c r="AA29" s="112" t="s">
+      <c r="AC29" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB29" s="113" t="s">
+      <c r="AD29" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC29" s="25" t="s">
+      <c r="AE29" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A30" s="114">
-        <v>16</v>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A30" s="101">
+        <v>28</v>
       </c>
       <c r="B30" s="110" t="s">
         <v>1048</v>
@@ -52125,70 +52366,76 @@
       <c r="I30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="101">
+        <v>1</v>
+      </c>
+      <c r="K30" s="101">
+        <v>1</v>
+      </c>
+      <c r="L30" s="22">
         <v>2</v>
       </c>
-      <c r="K30" s="12">
-        <v>1</v>
-      </c>
-      <c r="L30" s="96">
+      <c r="M30" s="12">
+        <v>1</v>
+      </c>
+      <c r="N30" s="96">
         <v>2</v>
       </c>
-      <c r="M30">
+      <c r="O30">
         <v>512</v>
       </c>
-      <c r="N30" t="s">
+      <c r="P30" t="s">
         <v>999</v>
       </c>
-      <c r="O30" t="s">
+      <c r="Q30" t="s">
         <v>1001</v>
       </c>
-      <c r="P30" s="96" t="s">
+      <c r="R30" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="S30" t="s">
         <v>1052</v>
       </c>
-      <c r="R30" s="20" t="s">
+      <c r="T30" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S30" s="6" t="s">
+      <c r="U30" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T30" s="28" t="s">
+      <c r="V30" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U30" s="6" t="s">
+      <c r="W30" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V30" t="s">
+      <c r="X30" t="s">
         <v>965</v>
       </c>
-      <c r="W30" s="112" t="s">
+      <c r="Y30" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X30" s="113" t="s">
+      <c r="Z30" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y30" s="27" t="s">
+      <c r="AA30" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z30" t="s">
+      <c r="AB30" t="s">
         <v>978</v>
       </c>
-      <c r="AA30" s="112" t="s">
+      <c r="AC30" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB30" s="113" t="s">
+      <c r="AD30" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC30" s="25" t="s">
+      <c r="AE30" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A31" s="114">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B31" s="110" t="s">
         <v>1049</v>
@@ -52214,70 +52461,76 @@
       <c r="I31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="101">
+        <v>1</v>
+      </c>
+      <c r="K31" s="101">
+        <v>1</v>
+      </c>
+      <c r="L31" s="22">
         <v>2</v>
       </c>
-      <c r="K31" s="12">
-        <v>1</v>
-      </c>
-      <c r="L31" s="96">
+      <c r="M31" s="12">
+        <v>1</v>
+      </c>
+      <c r="N31" s="96">
         <v>2</v>
       </c>
-      <c r="M31">
+      <c r="O31">
         <v>512</v>
       </c>
-      <c r="N31" t="s">
+      <c r="P31" t="s">
         <v>999</v>
       </c>
-      <c r="O31" t="s">
+      <c r="Q31" t="s">
         <v>1001</v>
       </c>
-      <c r="P31" s="96" t="s">
+      <c r="R31" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="S31" t="s">
         <v>1053</v>
       </c>
-      <c r="R31" s="20" t="s">
+      <c r="T31" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S31" s="6" t="s">
+      <c r="U31" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T31" s="28" t="s">
+      <c r="V31" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U31" s="6" t="s">
+      <c r="W31" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V31" t="s">
+      <c r="X31" t="s">
         <v>965</v>
       </c>
-      <c r="W31" s="112" t="s">
+      <c r="Y31" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X31" s="113" t="s">
+      <c r="Z31" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y31" s="27" t="s">
+      <c r="AA31" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AB31" t="s">
         <v>978</v>
       </c>
-      <c r="AA31" s="112" t="s">
+      <c r="AC31" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB31" s="113" t="s">
+      <c r="AD31" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC31" s="25" t="s">
+      <c r="AE31" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A32" s="114">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B32" s="110" t="s">
         <v>1074</v>
@@ -52303,70 +52556,76 @@
       <c r="I32" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J32" s="22">
+      <c r="J32" s="101">
+        <v>1</v>
+      </c>
+      <c r="K32" s="101">
+        <v>1</v>
+      </c>
+      <c r="L32" s="22">
         <v>2</v>
       </c>
-      <c r="K32" s="12">
-        <v>1</v>
-      </c>
-      <c r="L32" s="96">
+      <c r="M32" s="12">
+        <v>1</v>
+      </c>
+      <c r="N32" s="96">
         <v>2</v>
       </c>
-      <c r="M32">
+      <c r="O32">
         <v>512</v>
       </c>
-      <c r="N32" t="s">
+      <c r="P32" t="s">
         <v>999</v>
       </c>
-      <c r="O32" t="s">
+      <c r="Q32" t="s">
         <v>1001</v>
       </c>
-      <c r="P32" s="96" t="s">
+      <c r="R32" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="S32" t="s">
         <v>1072</v>
       </c>
-      <c r="R32" s="20" t="s">
+      <c r="T32" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S32" s="6" t="s">
+      <c r="U32" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T32" s="28" t="s">
+      <c r="V32" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U32" s="6" t="s">
+      <c r="W32" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V32" t="s">
+      <c r="X32" t="s">
         <v>965</v>
       </c>
-      <c r="W32" s="112" t="s">
+      <c r="Y32" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X32" s="113" t="s">
+      <c r="Z32" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y32" s="27" t="s">
+      <c r="AA32" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AB32" t="s">
         <v>978</v>
       </c>
-      <c r="AA32" s="112" t="s">
+      <c r="AC32" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB32" s="113" t="s">
+      <c r="AD32" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC32" s="25" t="s">
+      <c r="AE32" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="114">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B33" s="110" t="s">
         <v>1075</v>
@@ -52392,70 +52651,76 @@
       <c r="I33" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J33" s="22">
+      <c r="J33" s="101">
+        <v>1</v>
+      </c>
+      <c r="K33" s="101">
+        <v>1</v>
+      </c>
+      <c r="L33" s="22">
         <v>2</v>
       </c>
-      <c r="K33" s="12">
-        <v>1</v>
-      </c>
-      <c r="L33" s="96">
+      <c r="M33" s="12">
+        <v>1</v>
+      </c>
+      <c r="N33" s="96">
         <v>2</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>512</v>
       </c>
-      <c r="N33" t="s">
+      <c r="P33" t="s">
         <v>999</v>
       </c>
-      <c r="O33" t="s">
+      <c r="Q33" t="s">
         <v>1001</v>
       </c>
-      <c r="P33" s="96" t="s">
+      <c r="R33" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="S33" t="s">
         <v>1073</v>
       </c>
-      <c r="R33" s="20" t="s">
+      <c r="T33" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S33" s="6" t="s">
+      <c r="U33" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T33" s="28" t="s">
+      <c r="V33" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U33" s="6" t="s">
+      <c r="W33" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V33" t="s">
+      <c r="X33" t="s">
         <v>965</v>
       </c>
-      <c r="W33" s="112" t="s">
+      <c r="Y33" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X33" s="113" t="s">
+      <c r="Z33" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y33" s="27" t="s">
+      <c r="AA33" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z33" t="s">
+      <c r="AB33" t="s">
         <v>978</v>
       </c>
-      <c r="AA33" s="112" t="s">
+      <c r="AC33" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB33" s="113" t="s">
+      <c r="AD33" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC33" s="25" t="s">
+      <c r="AE33" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A34" s="114">
-        <v>16</v>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A34" s="101">
+        <v>32</v>
       </c>
       <c r="B34" s="110" t="s">
         <v>1083</v>
@@ -52481,70 +52746,76 @@
       <c r="I34" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J34" s="22">
+      <c r="J34" s="101">
+        <v>1</v>
+      </c>
+      <c r="K34" s="101">
+        <v>1</v>
+      </c>
+      <c r="L34" s="22">
         <v>2</v>
       </c>
-      <c r="K34" s="12">
-        <v>1</v>
-      </c>
-      <c r="L34" s="96">
+      <c r="M34" s="12">
+        <v>1</v>
+      </c>
+      <c r="N34" s="96">
         <v>2</v>
       </c>
-      <c r="M34">
+      <c r="O34">
         <v>512</v>
       </c>
-      <c r="N34" t="s">
+      <c r="P34" t="s">
         <v>999</v>
       </c>
-      <c r="O34" t="s">
+      <c r="Q34" t="s">
         <v>1001</v>
       </c>
-      <c r="P34" s="96" t="s">
+      <c r="R34" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="S34" t="s">
         <v>1081</v>
       </c>
-      <c r="R34" s="20" t="s">
+      <c r="T34" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S34" s="6" t="s">
+      <c r="U34" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T34" s="28" t="s">
+      <c r="V34" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U34" s="6" t="s">
+      <c r="W34" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V34" t="s">
+      <c r="X34" t="s">
         <v>965</v>
       </c>
-      <c r="W34" s="112" t="s">
+      <c r="Y34" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X34" s="113" t="s">
+      <c r="Z34" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y34" s="27" t="s">
+      <c r="AA34" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AB34" t="s">
         <v>978</v>
       </c>
-      <c r="AA34" s="112" t="s">
+      <c r="AC34" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB34" s="113" t="s">
+      <c r="AD34" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC34" s="25" t="s">
+      <c r="AE34" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="114">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B35" s="110" t="s">
         <v>1033</v>
@@ -52570,70 +52841,76 @@
       <c r="I35" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="101">
+        <v>1</v>
+      </c>
+      <c r="K35" s="101">
+        <v>1</v>
+      </c>
+      <c r="L35" s="22">
         <v>2</v>
       </c>
-      <c r="K35" s="12">
-        <v>1</v>
-      </c>
-      <c r="L35" s="96">
-        <v>1</v>
-      </c>
-      <c r="M35">
+      <c r="M35" s="12">
+        <v>1</v>
+      </c>
+      <c r="N35" s="96">
+        <v>1</v>
+      </c>
+      <c r="O35">
         <v>256</v>
       </c>
-      <c r="N35" t="s">
+      <c r="P35" t="s">
         <v>1000</v>
       </c>
-      <c r="O35" t="s">
+      <c r="Q35" t="s">
         <v>1001</v>
       </c>
-      <c r="P35" s="96" t="s">
+      <c r="R35" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="S35" t="s">
         <v>1002</v>
       </c>
-      <c r="R35" s="20" t="s">
+      <c r="T35" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S35" s="6" t="s">
+      <c r="U35" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T35" s="28" t="s">
+      <c r="V35" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U35" s="6" t="s">
+      <c r="W35" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V35" t="s">
+      <c r="X35" t="s">
         <v>965</v>
       </c>
-      <c r="W35" s="112" t="s">
+      <c r="Y35" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X35" s="113" t="s">
+      <c r="Z35" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y35" s="27" t="s">
+      <c r="AA35" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AB35" t="s">
         <v>978</v>
       </c>
-      <c r="AA35" s="112" t="s">
+      <c r="AC35" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB35" s="113" t="s">
+      <c r="AD35" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC35" s="25" t="s">
+      <c r="AE35" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="114">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B36" s="110" t="s">
         <v>1005</v>
@@ -52659,70 +52936,76 @@
       <c r="I36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J36" s="22">
+      <c r="J36" s="101">
+        <v>1</v>
+      </c>
+      <c r="K36" s="101">
+        <v>1</v>
+      </c>
+      <c r="L36" s="22">
         <v>2</v>
       </c>
-      <c r="K36" s="12">
-        <v>1</v>
-      </c>
-      <c r="L36" s="96">
+      <c r="M36" s="12">
+        <v>1</v>
+      </c>
+      <c r="N36" s="96">
         <v>2</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>512</v>
       </c>
-      <c r="N36" t="s">
+      <c r="P36" t="s">
         <v>1000</v>
       </c>
-      <c r="O36" t="s">
+      <c r="Q36" t="s">
         <v>1001</v>
       </c>
-      <c r="P36" s="96" t="s">
+      <c r="R36" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="S36" t="s">
         <v>1006</v>
       </c>
-      <c r="R36" s="20" t="s">
+      <c r="T36" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S36" s="6" t="s">
+      <c r="U36" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T36" s="28" t="s">
+      <c r="V36" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U36" s="6" t="s">
+      <c r="W36" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V36" t="s">
+      <c r="X36" t="s">
         <v>965</v>
       </c>
-      <c r="W36" s="112" t="s">
+      <c r="Y36" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X36" s="113" t="s">
+      <c r="Z36" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y36" s="27" t="s">
+      <c r="AA36" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AB36" t="s">
         <v>978</v>
       </c>
-      <c r="AA36" s="112" t="s">
+      <c r="AC36" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB36" s="113" t="s">
+      <c r="AD36" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC36" s="25" t="s">
+      <c r="AE36" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="114">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B37" s="110" t="s">
         <v>1050</v>
@@ -52748,70 +53031,76 @@
       <c r="I37" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J37" s="22">
+      <c r="J37" s="101">
+        <v>1</v>
+      </c>
+      <c r="K37" s="101">
+        <v>1</v>
+      </c>
+      <c r="L37" s="22">
         <v>2</v>
       </c>
-      <c r="K37" s="12">
-        <v>1</v>
-      </c>
-      <c r="L37" s="96">
+      <c r="M37" s="12">
+        <v>1</v>
+      </c>
+      <c r="N37" s="96">
         <v>2</v>
       </c>
-      <c r="M37">
+      <c r="O37">
         <v>512</v>
       </c>
-      <c r="N37" t="s">
+      <c r="P37" t="s">
         <v>1000</v>
       </c>
-      <c r="O37" t="s">
+      <c r="Q37" t="s">
         <v>1001</v>
       </c>
-      <c r="P37" s="96" t="s">
+      <c r="R37" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="S37" t="s">
         <v>1052</v>
       </c>
-      <c r="R37" s="20" t="s">
+      <c r="T37" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S37" s="6" t="s">
+      <c r="U37" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T37" s="28" t="s">
+      <c r="V37" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U37" s="6" t="s">
+      <c r="W37" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V37" t="s">
+      <c r="X37" t="s">
         <v>965</v>
       </c>
-      <c r="W37" s="112" t="s">
+      <c r="Y37" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X37" s="113" t="s">
+      <c r="Z37" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y37" s="27" t="s">
+      <c r="AA37" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AB37" t="s">
         <v>978</v>
       </c>
-      <c r="AA37" s="112" t="s">
+      <c r="AC37" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB37" s="113" t="s">
+      <c r="AD37" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC37" s="25" t="s">
+      <c r="AE37" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A38" s="114">
-        <v>18</v>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A38" s="101">
+        <v>36</v>
       </c>
       <c r="B38" s="110" t="s">
         <v>1051</v>
@@ -52837,70 +53126,76 @@
       <c r="I38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J38" s="22">
+      <c r="J38" s="101">
+        <v>1</v>
+      </c>
+      <c r="K38" s="101">
+        <v>1</v>
+      </c>
+      <c r="L38" s="22">
         <v>2</v>
       </c>
-      <c r="K38" s="12">
-        <v>1</v>
-      </c>
-      <c r="L38" s="96">
+      <c r="M38" s="12">
+        <v>1</v>
+      </c>
+      <c r="N38" s="96">
         <v>2</v>
       </c>
-      <c r="M38">
+      <c r="O38">
         <v>512</v>
       </c>
-      <c r="N38" t="s">
+      <c r="P38" t="s">
         <v>1000</v>
       </c>
-      <c r="O38" t="s">
+      <c r="Q38" t="s">
         <v>1001</v>
       </c>
-      <c r="P38" s="96" t="s">
+      <c r="R38" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="S38" t="s">
         <v>1053</v>
       </c>
-      <c r="R38" s="20" t="s">
+      <c r="T38" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S38" s="6" t="s">
+      <c r="U38" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T38" s="28" t="s">
+      <c r="V38" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U38" s="6" t="s">
+      <c r="W38" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V38" t="s">
+      <c r="X38" t="s">
         <v>965</v>
       </c>
-      <c r="W38" s="112" t="s">
+      <c r="Y38" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X38" s="113" t="s">
+      <c r="Z38" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y38" s="27" t="s">
+      <c r="AA38" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AB38" t="s">
         <v>978</v>
       </c>
-      <c r="AA38" s="112" t="s">
+      <c r="AC38" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB38" s="113" t="s">
+      <c r="AD38" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC38" s="25" t="s">
+      <c r="AE38" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A39" s="114">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B39" s="110" t="s">
         <v>1076</v>
@@ -52926,70 +53221,76 @@
       <c r="I39" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39" s="101">
+        <v>1</v>
+      </c>
+      <c r="K39" s="101">
+        <v>1</v>
+      </c>
+      <c r="L39" s="22">
         <v>2</v>
       </c>
-      <c r="K39" s="12">
-        <v>1</v>
-      </c>
-      <c r="L39" s="96">
+      <c r="M39" s="12">
+        <v>1</v>
+      </c>
+      <c r="N39" s="96">
         <v>2</v>
       </c>
-      <c r="M39">
+      <c r="O39">
         <v>512</v>
       </c>
-      <c r="N39" t="s">
+      <c r="P39" t="s">
         <v>1000</v>
       </c>
-      <c r="O39" t="s">
+      <c r="Q39" t="s">
         <v>1001</v>
       </c>
-      <c r="P39" s="96" t="s">
+      <c r="R39" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="S39" t="s">
         <v>1072</v>
       </c>
-      <c r="R39" s="20" t="s">
+      <c r="T39" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S39" s="6" t="s">
+      <c r="U39" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T39" s="28" t="s">
+      <c r="V39" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U39" s="6" t="s">
+      <c r="W39" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V39" t="s">
+      <c r="X39" t="s">
         <v>965</v>
       </c>
-      <c r="W39" s="112" t="s">
+      <c r="Y39" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X39" s="113" t="s">
+      <c r="Z39" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y39" s="27" t="s">
+      <c r="AA39" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z39" t="s">
+      <c r="AB39" t="s">
         <v>978</v>
       </c>
-      <c r="AA39" s="112" t="s">
+      <c r="AC39" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB39" s="113" t="s">
+      <c r="AD39" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC39" s="25" t="s">
+      <c r="AE39" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A40" s="114">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B40" s="110" t="s">
         <v>1077</v>
@@ -53015,70 +53316,76 @@
       <c r="I40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J40" s="22">
+      <c r="J40" s="101">
+        <v>1</v>
+      </c>
+      <c r="K40" s="101">
+        <v>1</v>
+      </c>
+      <c r="L40" s="22">
         <v>2</v>
       </c>
-      <c r="K40" s="12">
-        <v>1</v>
-      </c>
-      <c r="L40" s="96">
+      <c r="M40" s="12">
+        <v>1</v>
+      </c>
+      <c r="N40" s="96">
         <v>2</v>
       </c>
-      <c r="M40">
+      <c r="O40">
         <v>512</v>
       </c>
-      <c r="N40" t="s">
+      <c r="P40" t="s">
         <v>1000</v>
       </c>
-      <c r="O40" t="s">
+      <c r="Q40" t="s">
         <v>1001</v>
       </c>
-      <c r="P40" s="96" t="s">
+      <c r="R40" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="S40" t="s">
         <v>1073</v>
       </c>
-      <c r="R40" s="20" t="s">
+      <c r="T40" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S40" s="6" t="s">
+      <c r="U40" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T40" s="28" t="s">
+      <c r="V40" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U40" s="6" t="s">
+      <c r="W40" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V40" t="s">
+      <c r="X40" t="s">
         <v>965</v>
       </c>
-      <c r="W40" s="112" t="s">
+      <c r="Y40" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X40" s="113" t="s">
+      <c r="Z40" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y40" s="27" t="s">
+      <c r="AA40" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AB40" t="s">
         <v>978</v>
       </c>
-      <c r="AA40" s="112" t="s">
+      <c r="AC40" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB40" s="113" t="s">
+      <c r="AD40" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC40" s="25" t="s">
+      <c r="AE40" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A41" s="114">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B41" s="110" t="s">
         <v>1080</v>
@@ -53104,70 +53411,76 @@
       <c r="I41" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J41" s="22">
+      <c r="J41" s="101">
+        <v>1</v>
+      </c>
+      <c r="K41" s="101">
+        <v>1</v>
+      </c>
+      <c r="L41" s="22">
         <v>2</v>
       </c>
-      <c r="K41" s="12">
-        <v>1</v>
-      </c>
-      <c r="L41" s="96">
+      <c r="M41" s="12">
+        <v>1</v>
+      </c>
+      <c r="N41" s="96">
         <v>2</v>
       </c>
-      <c r="M41">
+      <c r="O41">
         <v>512</v>
       </c>
-      <c r="N41" t="s">
+      <c r="P41" t="s">
         <v>1000</v>
       </c>
-      <c r="O41" t="s">
+      <c r="Q41" t="s">
         <v>1001</v>
       </c>
-      <c r="P41" s="96" t="s">
+      <c r="R41" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="S41" t="s">
         <v>1081</v>
       </c>
-      <c r="R41" s="20" t="s">
+      <c r="T41" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S41" s="6" t="s">
+      <c r="U41" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="T41" s="28" t="s">
+      <c r="V41" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="U41" s="6" t="s">
+      <c r="W41" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V41" t="s">
+      <c r="X41" t="s">
         <v>965</v>
       </c>
-      <c r="W41" s="112" t="s">
+      <c r="Y41" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X41" s="113" t="s">
+      <c r="Z41" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y41" s="27" t="s">
+      <c r="AA41" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z41" t="s">
+      <c r="AB41" t="s">
         <v>978</v>
       </c>
-      <c r="AA41" s="112" t="s">
+      <c r="AC41" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB41" s="113" t="s">
+      <c r="AD41" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC41" s="25" t="s">
+      <c r="AE41" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="42" spans="1:29" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="101">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B42" s="102" t="s">
         <v>981</v>
@@ -53193,70 +53506,76 @@
       <c r="I42" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="J42" s="105">
+      <c r="J42" s="101">
+        <v>1</v>
+      </c>
+      <c r="K42" s="101">
+        <v>1</v>
+      </c>
+      <c r="L42" s="105">
         <v>2</v>
       </c>
-      <c r="K42" s="106">
-        <v>1</v>
-      </c>
-      <c r="L42" s="107">
-        <v>1</v>
-      </c>
-      <c r="M42" s="107">
+      <c r="M42" s="106">
+        <v>1</v>
+      </c>
+      <c r="N42" s="107">
+        <v>1</v>
+      </c>
+      <c r="O42" s="107">
         <v>256</v>
       </c>
-      <c r="N42" s="107" t="s">
+      <c r="P42" s="107" t="s">
         <v>1022</v>
       </c>
-      <c r="O42" s="107" t="s">
+      <c r="Q42" s="107" t="s">
         <v>1025</v>
       </c>
-      <c r="P42" s="107" t="s">
+      <c r="R42" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="Q42" s="107" t="s">
+      <c r="S42" s="107" t="s">
         <v>1026</v>
       </c>
-      <c r="R42" s="126" t="s">
+      <c r="T42" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="S42" s="101" t="s">
+      <c r="U42" s="101" t="s">
         <v>943</v>
       </c>
-      <c r="T42" s="126" t="s">
+      <c r="V42" s="126" t="s">
         <v>789</v>
       </c>
-      <c r="U42" s="101" t="s">
+      <c r="W42" s="101" t="s">
         <v>792</v>
       </c>
-      <c r="V42" s="107" t="s">
+      <c r="X42" s="107" t="s">
         <v>965</v>
       </c>
-      <c r="W42" s="127" t="s">
+      <c r="Y42" s="127" t="s">
         <v>747</v>
       </c>
-      <c r="X42" s="128" t="s">
+      <c r="Z42" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="Y42" s="129" t="s">
+      <c r="AA42" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="Z42" s="107" t="s">
+      <c r="AB42" s="107" t="s">
         <v>978</v>
       </c>
-      <c r="AA42" s="127" t="s">
+      <c r="AC42" s="127" t="s">
         <v>753</v>
       </c>
-      <c r="AB42" s="128" t="s">
+      <c r="AD42" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="AC42" s="109" t="s">
+      <c r="AE42" s="109" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A43" s="114">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B43" s="110" t="s">
         <v>983</v>
@@ -53282,70 +53601,76 @@
       <c r="I43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43" s="101">
+        <v>1</v>
+      </c>
+      <c r="K43" s="101">
+        <v>1</v>
+      </c>
+      <c r="L43" s="22">
         <v>2</v>
       </c>
-      <c r="K43" s="12">
-        <v>1</v>
-      </c>
-      <c r="L43" s="96">
-        <v>1</v>
-      </c>
-      <c r="M43" s="95">
+      <c r="M43" s="12">
+        <v>1</v>
+      </c>
+      <c r="N43" s="96">
+        <v>1</v>
+      </c>
+      <c r="O43" s="95">
         <v>256</v>
       </c>
-      <c r="N43" t="s">
+      <c r="P43" t="s">
         <v>1023</v>
       </c>
-      <c r="O43" t="s">
+      <c r="Q43" t="s">
         <v>1025</v>
       </c>
-      <c r="P43" s="96" t="s">
+      <c r="R43" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="S43" t="s">
         <v>1026</v>
       </c>
-      <c r="R43" s="20" t="s">
+      <c r="T43" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S43" s="6" t="s">
+      <c r="U43" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T43" s="20" t="s">
+      <c r="V43" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="U43" s="6" t="s">
+      <c r="W43" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V43" t="s">
+      <c r="X43" t="s">
         <v>965</v>
       </c>
-      <c r="W43" s="112" t="s">
+      <c r="Y43" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X43" s="113" t="s">
+      <c r="Z43" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y43" s="27" t="s">
+      <c r="AA43" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="AB43" t="s">
         <v>978</v>
       </c>
-      <c r="AA43" s="112" t="s">
+      <c r="AC43" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB43" s="113" t="s">
+      <c r="AD43" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC43" s="25" t="s">
+      <c r="AE43" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A44" s="114">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B44" s="110" t="s">
         <v>985</v>
@@ -53371,70 +53696,76 @@
       <c r="I44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J44" s="22">
+      <c r="J44" s="101">
+        <v>1</v>
+      </c>
+      <c r="K44" s="101">
+        <v>1</v>
+      </c>
+      <c r="L44" s="22">
         <v>2</v>
       </c>
-      <c r="K44" s="12">
-        <v>1</v>
-      </c>
-      <c r="L44" s="96">
-        <v>1</v>
-      </c>
-      <c r="M44" s="95">
+      <c r="M44" s="12">
+        <v>1</v>
+      </c>
+      <c r="N44" s="96">
+        <v>1</v>
+      </c>
+      <c r="O44" s="95">
         <v>256</v>
       </c>
-      <c r="N44" t="s">
+      <c r="P44" t="s">
         <v>1024</v>
       </c>
-      <c r="O44" t="s">
+      <c r="Q44" t="s">
         <v>1025</v>
       </c>
-      <c r="P44" s="96" t="s">
+      <c r="R44" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="S44" t="s">
         <v>1026</v>
       </c>
-      <c r="R44" s="20" t="s">
+      <c r="T44" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="S44" s="6" t="s">
+      <c r="U44" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="T44" s="20" t="s">
+      <c r="V44" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="U44" s="6" t="s">
+      <c r="W44" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="V44" t="s">
+      <c r="X44" t="s">
         <v>965</v>
       </c>
-      <c r="W44" s="112" t="s">
+      <c r="Y44" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X44" s="113" t="s">
+      <c r="Z44" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="Y44" s="27" t="s">
+      <c r="AA44" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="Z44" t="s">
+      <c r="AB44" t="s">
         <v>978</v>
       </c>
-      <c r="AA44" s="112" t="s">
+      <c r="AC44" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB44" s="113" t="s">
+      <c r="AD44" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AC44" s="25" t="s">
+      <c r="AE44" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="45" spans="1:29" s="107" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="101">
-        <v>22</v>
+    <row r="45" spans="1:31" s="107" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="114">
+        <v>43</v>
       </c>
       <c r="B45" s="102" t="s">
         <v>987</v>
@@ -53460,70 +53791,76 @@
       <c r="I45" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="J45" s="105">
+      <c r="J45" s="101">
+        <v>1</v>
+      </c>
+      <c r="K45" s="101">
+        <v>1</v>
+      </c>
+      <c r="L45" s="105">
         <v>2</v>
       </c>
-      <c r="K45" s="106">
-        <v>1</v>
-      </c>
-      <c r="L45" s="107">
-        <v>1</v>
-      </c>
-      <c r="M45" s="107">
+      <c r="M45" s="106">
+        <v>1</v>
+      </c>
+      <c r="N45" s="107">
+        <v>1</v>
+      </c>
+      <c r="O45" s="107">
         <v>256</v>
       </c>
-      <c r="N45" s="107" t="s">
+      <c r="P45" s="107" t="s">
         <v>1027</v>
       </c>
-      <c r="O45" s="107" t="s">
+      <c r="Q45" s="107" t="s">
         <v>1030</v>
       </c>
-      <c r="P45" s="107" t="s">
+      <c r="R45" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="Q45" s="107" t="s">
+      <c r="S45" s="107" t="s">
         <v>1031</v>
       </c>
-      <c r="R45" s="126" t="s">
+      <c r="T45" s="126" t="s">
         <v>92</v>
       </c>
-      <c r="S45" s="101" t="s">
+      <c r="U45" s="101" t="s">
         <v>943</v>
       </c>
-      <c r="T45" s="126" t="s">
+      <c r="V45" s="126" t="s">
         <v>772</v>
       </c>
-      <c r="U45" s="101" t="s">
+      <c r="W45" s="101" t="s">
         <v>989</v>
       </c>
-      <c r="V45" s="107" t="s">
+      <c r="X45" s="107" t="s">
         <v>990</v>
       </c>
-      <c r="W45" s="127" t="s">
+      <c r="Y45" s="127" t="s">
         <v>747</v>
       </c>
-      <c r="X45" s="128" t="s">
+      <c r="Z45" s="128" t="s">
         <v>946</v>
       </c>
-      <c r="Y45" s="129" t="s">
+      <c r="AA45" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="Z45" s="107" t="s">
+      <c r="AB45" s="107" t="s">
         <v>991</v>
       </c>
-      <c r="AA45" s="127" t="s">
+      <c r="AC45" s="127" t="s">
         <v>753</v>
       </c>
-      <c r="AB45" s="128" t="s">
+      <c r="AD45" s="128" t="s">
         <v>946</v>
       </c>
-      <c r="AC45" s="109" t="s">
+      <c r="AE45" s="109" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="46" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="114">
-        <v>22</v>
+    <row r="46" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="101">
+        <v>44</v>
       </c>
       <c r="B46" s="130" t="s">
         <v>1038</v>
@@ -53549,70 +53886,76 @@
       <c r="I46" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J46" s="131">
+      <c r="J46" s="101">
+        <v>1</v>
+      </c>
+      <c r="K46" s="101">
+        <v>1</v>
+      </c>
+      <c r="L46" s="131">
         <v>2</v>
       </c>
-      <c r="K46" s="132">
-        <v>1</v>
-      </c>
-      <c r="L46" s="96">
-        <v>1</v>
-      </c>
-      <c r="M46" s="96">
+      <c r="M46" s="132">
+        <v>1</v>
+      </c>
+      <c r="N46" s="96">
+        <v>1</v>
+      </c>
+      <c r="O46" s="96">
         <v>256</v>
       </c>
-      <c r="N46" s="96" t="s">
+      <c r="P46" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="O46" s="96" t="s">
+      <c r="Q46" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P46" s="96" t="s">
+      <c r="R46" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q46" s="96" t="s">
+      <c r="S46" s="96" t="s">
         <v>1041</v>
       </c>
-      <c r="R46" s="133" t="s">
+      <c r="T46" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S46" s="114" t="s">
+      <c r="U46" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T46" s="133" t="s">
+      <c r="V46" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U46" s="114" t="s">
+      <c r="W46" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V46" s="96" t="s">
+      <c r="X46" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W46" s="134" t="s">
+      <c r="Y46" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X46" s="135" t="s">
+      <c r="Z46" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y46" s="133" t="s">
+      <c r="AA46" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z46" s="96" t="s">
+      <c r="AB46" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA46" s="134" t="s">
+      <c r="AC46" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB46" s="135" t="s">
+      <c r="AD46" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC46" s="115" t="s">
+      <c r="AE46" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="47" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="114">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B47" s="130" t="s">
         <v>1054</v>
@@ -53638,70 +53981,76 @@
       <c r="I47" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J47" s="131">
+      <c r="J47" s="101">
+        <v>1</v>
+      </c>
+      <c r="K47" s="101">
+        <v>1</v>
+      </c>
+      <c r="L47" s="131">
         <v>2</v>
       </c>
-      <c r="K47" s="132">
-        <v>1</v>
-      </c>
-      <c r="L47" s="96">
-        <v>1</v>
-      </c>
-      <c r="M47" s="96">
+      <c r="M47" s="132">
+        <v>1</v>
+      </c>
+      <c r="N47" s="96">
+        <v>1</v>
+      </c>
+      <c r="O47" s="96">
         <v>256</v>
       </c>
-      <c r="N47" s="96" t="s">
+      <c r="P47" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="O47" s="96" t="s">
+      <c r="Q47" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P47" s="96" t="s">
+      <c r="R47" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q47" s="96" t="s">
+      <c r="S47" s="96" t="s">
         <v>1060</v>
       </c>
-      <c r="R47" s="133" t="s">
+      <c r="T47" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S47" s="114" t="s">
+      <c r="U47" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T47" s="133" t="s">
+      <c r="V47" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U47" s="114" t="s">
+      <c r="W47" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V47" s="96" t="s">
+      <c r="X47" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W47" s="134" t="s">
+      <c r="Y47" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X47" s="135" t="s">
+      <c r="Z47" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y47" s="133" t="s">
+      <c r="AA47" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z47" s="96" t="s">
+      <c r="AB47" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA47" s="134" t="s">
+      <c r="AC47" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB47" s="135" t="s">
+      <c r="AD47" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC47" s="115" t="s">
+      <c r="AE47" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="114">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B48" s="130" t="s">
         <v>1055</v>
@@ -53727,70 +54076,76 @@
       <c r="I48" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J48" s="131">
+      <c r="J48" s="101">
+        <v>1</v>
+      </c>
+      <c r="K48" s="101">
+        <v>1</v>
+      </c>
+      <c r="L48" s="131">
         <v>2</v>
       </c>
-      <c r="K48" s="132">
-        <v>1</v>
-      </c>
-      <c r="L48" s="96">
-        <v>1</v>
-      </c>
-      <c r="M48" s="96">
+      <c r="M48" s="132">
+        <v>1</v>
+      </c>
+      <c r="N48" s="96">
+        <v>1</v>
+      </c>
+      <c r="O48" s="96">
         <v>256</v>
       </c>
-      <c r="N48" s="96" t="s">
+      <c r="P48" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="O48" s="96" t="s">
+      <c r="Q48" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P48" s="96" t="s">
+      <c r="R48" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q48" s="96" t="s">
+      <c r="S48" s="96" t="s">
         <v>1061</v>
       </c>
-      <c r="R48" s="133" t="s">
+      <c r="T48" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S48" s="114" t="s">
+      <c r="U48" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T48" s="133" t="s">
+      <c r="V48" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U48" s="114" t="s">
+      <c r="W48" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V48" s="96" t="s">
+      <c r="X48" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W48" s="134" t="s">
+      <c r="Y48" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X48" s="135" t="s">
+      <c r="Z48" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y48" s="133" t="s">
+      <c r="AA48" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z48" s="96" t="s">
+      <c r="AB48" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA48" s="134" t="s">
+      <c r="AC48" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB48" s="135" t="s">
+      <c r="AD48" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC48" s="115" t="s">
+      <c r="AE48" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="49" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="114">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B49" s="130" t="s">
         <v>1062</v>
@@ -53816,70 +54171,76 @@
       <c r="I49" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J49" s="131">
+      <c r="J49" s="101">
+        <v>1</v>
+      </c>
+      <c r="K49" s="101">
+        <v>1</v>
+      </c>
+      <c r="L49" s="131">
         <v>2</v>
       </c>
-      <c r="K49" s="132">
-        <v>1</v>
-      </c>
-      <c r="L49" s="96">
-        <v>1</v>
-      </c>
-      <c r="M49" s="96">
+      <c r="M49" s="132">
+        <v>1</v>
+      </c>
+      <c r="N49" s="96">
+        <v>1</v>
+      </c>
+      <c r="O49" s="96">
         <v>256</v>
       </c>
-      <c r="N49" s="96" t="s">
+      <c r="P49" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="O49" s="96" t="s">
+      <c r="Q49" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P49" s="96" t="s">
+      <c r="R49" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q49" s="96" t="s">
+      <c r="S49" s="96" t="s">
         <v>1064</v>
       </c>
-      <c r="R49" s="133" t="s">
+      <c r="T49" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S49" s="114" t="s">
+      <c r="U49" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T49" s="133" t="s">
+      <c r="V49" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U49" s="114" t="s">
+      <c r="W49" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V49" s="96" t="s">
+      <c r="X49" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W49" s="134" t="s">
+      <c r="Y49" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X49" s="135" t="s">
+      <c r="Z49" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y49" s="133" t="s">
+      <c r="AA49" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z49" s="96" t="s">
+      <c r="AB49" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA49" s="134" t="s">
+      <c r="AC49" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB49" s="135" t="s">
+      <c r="AD49" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC49" s="115" t="s">
+      <c r="AE49" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="50" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="114">
-        <v>22</v>
+    <row r="50" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="101">
+        <v>48</v>
       </c>
       <c r="B50" s="130" t="s">
         <v>1063</v>
@@ -53905,70 +54266,76 @@
       <c r="I50" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J50" s="131">
+      <c r="J50" s="101">
+        <v>1</v>
+      </c>
+      <c r="K50" s="101">
+        <v>1</v>
+      </c>
+      <c r="L50" s="131">
         <v>2</v>
       </c>
-      <c r="K50" s="132">
-        <v>1</v>
-      </c>
-      <c r="L50" s="96">
-        <v>1</v>
-      </c>
-      <c r="M50" s="96">
+      <c r="M50" s="132">
+        <v>1</v>
+      </c>
+      <c r="N50" s="96">
+        <v>1</v>
+      </c>
+      <c r="O50" s="96">
         <v>256</v>
       </c>
-      <c r="N50" s="96" t="s">
+      <c r="P50" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="O50" s="96" t="s">
+      <c r="Q50" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P50" s="96" t="s">
+      <c r="R50" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q50" s="96" t="s">
+      <c r="S50" s="96" t="s">
         <v>1065</v>
       </c>
-      <c r="R50" s="133" t="s">
+      <c r="T50" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S50" s="114" t="s">
+      <c r="U50" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T50" s="133" t="s">
+      <c r="V50" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U50" s="114" t="s">
+      <c r="W50" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V50" s="96" t="s">
+      <c r="X50" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W50" s="134" t="s">
+      <c r="Y50" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X50" s="135" t="s">
+      <c r="Z50" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y50" s="133" t="s">
+      <c r="AA50" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z50" s="96" t="s">
+      <c r="AB50" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA50" s="134" t="s">
+      <c r="AC50" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB50" s="135" t="s">
+      <c r="AD50" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC50" s="115" t="s">
+      <c r="AE50" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="51" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="114">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="B51" s="130" t="s">
         <v>1084</v>
@@ -53994,70 +54361,76 @@
       <c r="I51" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J51" s="131">
+      <c r="J51" s="101">
+        <v>1</v>
+      </c>
+      <c r="K51" s="101">
+        <v>1</v>
+      </c>
+      <c r="L51" s="131">
         <v>2</v>
       </c>
-      <c r="K51" s="132">
-        <v>1</v>
-      </c>
-      <c r="L51" s="96">
-        <v>1</v>
-      </c>
-      <c r="M51" s="96">
+      <c r="M51" s="132">
+        <v>1</v>
+      </c>
+      <c r="N51" s="96">
+        <v>1</v>
+      </c>
+      <c r="O51" s="96">
         <v>256</v>
       </c>
-      <c r="N51" s="96" t="s">
+      <c r="P51" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="O51" s="96" t="s">
+      <c r="Q51" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P51" s="96" t="s">
+      <c r="R51" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q51" s="96" t="s">
+      <c r="S51" s="96" t="s">
         <v>1079</v>
       </c>
-      <c r="R51" s="133" t="s">
+      <c r="T51" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S51" s="114" t="s">
+      <c r="U51" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T51" s="133" t="s">
+      <c r="V51" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U51" s="114" t="s">
+      <c r="W51" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V51" s="96" t="s">
+      <c r="X51" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W51" s="134" t="s">
+      <c r="Y51" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X51" s="135" t="s">
+      <c r="Z51" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y51" s="133" t="s">
+      <c r="AA51" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z51" s="96" t="s">
+      <c r="AB51" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA51" s="134" t="s">
+      <c r="AC51" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB51" s="135" t="s">
+      <c r="AD51" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC51" s="115" t="s">
+      <c r="AE51" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="52" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="114">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B52" s="130" t="s">
         <v>992</v>
@@ -54083,70 +54456,76 @@
       <c r="I52" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J52" s="131">
+      <c r="J52" s="101">
+        <v>1</v>
+      </c>
+      <c r="K52" s="101">
+        <v>1</v>
+      </c>
+      <c r="L52" s="131">
         <v>2</v>
       </c>
-      <c r="K52" s="132">
-        <v>1</v>
-      </c>
-      <c r="L52" s="96">
-        <v>1</v>
-      </c>
-      <c r="M52" s="95">
+      <c r="M52" s="132">
+        <v>1</v>
+      </c>
+      <c r="N52" s="96">
+        <v>1</v>
+      </c>
+      <c r="O52" s="95">
         <v>256</v>
       </c>
-      <c r="N52" s="96" t="s">
+      <c r="P52" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="O52" s="96" t="s">
+      <c r="Q52" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P52" s="96" t="s">
+      <c r="R52" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q52" s="96" t="s">
+      <c r="S52" s="96" t="s">
         <v>1031</v>
       </c>
-      <c r="R52" s="133" t="s">
+      <c r="T52" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S52" s="114" t="s">
+      <c r="U52" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T52" s="133" t="s">
+      <c r="V52" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U52" s="114" t="s">
+      <c r="W52" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V52" s="96" t="s">
+      <c r="X52" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W52" s="134" t="s">
+      <c r="Y52" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X52" s="135" t="s">
+      <c r="Z52" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y52" s="133" t="s">
+      <c r="AA52" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z52" s="96" t="s">
+      <c r="AB52" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA52" s="134" t="s">
+      <c r="AC52" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB52" s="135" t="s">
+      <c r="AD52" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC52" s="115" t="s">
+      <c r="AE52" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="53" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="114">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B53" s="130" t="s">
         <v>1039</v>
@@ -54172,70 +54551,76 @@
       <c r="I53" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J53" s="131">
+      <c r="J53" s="101">
+        <v>1</v>
+      </c>
+      <c r="K53" s="101">
+        <v>1</v>
+      </c>
+      <c r="L53" s="131">
         <v>2</v>
       </c>
-      <c r="K53" s="132">
-        <v>1</v>
-      </c>
-      <c r="L53" s="96">
-        <v>1</v>
-      </c>
-      <c r="M53" s="95">
+      <c r="M53" s="132">
+        <v>1</v>
+      </c>
+      <c r="N53" s="96">
+        <v>1</v>
+      </c>
+      <c r="O53" s="95">
         <v>256</v>
       </c>
-      <c r="N53" s="96" t="s">
+      <c r="P53" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="O53" s="96" t="s">
+      <c r="Q53" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P53" s="96" t="s">
+      <c r="R53" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q53" s="96" t="s">
+      <c r="S53" s="96" t="s">
         <v>1041</v>
       </c>
-      <c r="R53" s="133" t="s">
+      <c r="T53" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S53" s="114" t="s">
+      <c r="U53" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T53" s="133" t="s">
+      <c r="V53" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U53" s="114" t="s">
+      <c r="W53" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V53" s="96" t="s">
+      <c r="X53" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W53" s="134" t="s">
+      <c r="Y53" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X53" s="135" t="s">
+      <c r="Z53" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y53" s="133" t="s">
+      <c r="AA53" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z53" s="96" t="s">
+      <c r="AB53" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA53" s="134" t="s">
+      <c r="AC53" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB53" s="135" t="s">
+      <c r="AD53" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC53" s="115" t="s">
+      <c r="AE53" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="54" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="114">
-        <v>23</v>
+    <row r="54" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="101">
+        <v>52</v>
       </c>
       <c r="B54" s="130" t="s">
         <v>1056</v>
@@ -54261,70 +54646,76 @@
       <c r="I54" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J54" s="131">
+      <c r="J54" s="101">
+        <v>1</v>
+      </c>
+      <c r="K54" s="101">
+        <v>1</v>
+      </c>
+      <c r="L54" s="131">
         <v>2</v>
       </c>
-      <c r="K54" s="132">
-        <v>1</v>
-      </c>
-      <c r="L54" s="96">
-        <v>1</v>
-      </c>
-      <c r="M54" s="95">
+      <c r="M54" s="132">
+        <v>1</v>
+      </c>
+      <c r="N54" s="96">
+        <v>1</v>
+      </c>
+      <c r="O54" s="95">
         <v>256</v>
       </c>
-      <c r="N54" s="96" t="s">
+      <c r="P54" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="O54" s="96" t="s">
+      <c r="Q54" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P54" s="96" t="s">
+      <c r="R54" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q54" s="96" t="s">
+      <c r="S54" s="96" t="s">
         <v>1060</v>
       </c>
-      <c r="R54" s="133" t="s">
+      <c r="T54" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S54" s="114" t="s">
+      <c r="U54" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T54" s="133" t="s">
+      <c r="V54" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U54" s="114" t="s">
+      <c r="W54" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V54" s="96" t="s">
+      <c r="X54" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W54" s="134" t="s">
+      <c r="Y54" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X54" s="135" t="s">
+      <c r="Z54" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y54" s="133" t="s">
+      <c r="AA54" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z54" s="96" t="s">
+      <c r="AB54" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA54" s="134" t="s">
+      <c r="AC54" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB54" s="135" t="s">
+      <c r="AD54" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC54" s="115" t="s">
+      <c r="AE54" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="55" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="114">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="B55" s="130" t="s">
         <v>1057</v>
@@ -54350,70 +54741,76 @@
       <c r="I55" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J55" s="131">
+      <c r="J55" s="101">
+        <v>1</v>
+      </c>
+      <c r="K55" s="101">
+        <v>1</v>
+      </c>
+      <c r="L55" s="131">
         <v>2</v>
       </c>
-      <c r="K55" s="132">
-        <v>1</v>
-      </c>
-      <c r="L55" s="96">
-        <v>1</v>
-      </c>
-      <c r="M55" s="95">
+      <c r="M55" s="132">
+        <v>1</v>
+      </c>
+      <c r="N55" s="96">
+        <v>1</v>
+      </c>
+      <c r="O55" s="95">
         <v>256</v>
       </c>
-      <c r="N55" s="96" t="s">
+      <c r="P55" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="O55" s="96" t="s">
+      <c r="Q55" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P55" s="96" t="s">
+      <c r="R55" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q55" s="96" t="s">
+      <c r="S55" s="96" t="s">
         <v>1061</v>
       </c>
-      <c r="R55" s="133" t="s">
+      <c r="T55" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S55" s="114" t="s">
+      <c r="U55" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T55" s="133" t="s">
+      <c r="V55" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U55" s="114" t="s">
+      <c r="W55" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V55" s="96" t="s">
+      <c r="X55" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W55" s="134" t="s">
+      <c r="Y55" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X55" s="135" t="s">
+      <c r="Z55" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y55" s="133" t="s">
+      <c r="AA55" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z55" s="96" t="s">
+      <c r="AB55" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA55" s="134" t="s">
+      <c r="AC55" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB55" s="135" t="s">
+      <c r="AD55" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC55" s="115" t="s">
+      <c r="AE55" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="56" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="114">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B56" s="130" t="s">
         <v>1066</v>
@@ -54439,70 +54836,76 @@
       <c r="I56" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J56" s="131">
+      <c r="J56" s="101">
+        <v>1</v>
+      </c>
+      <c r="K56" s="101">
+        <v>1</v>
+      </c>
+      <c r="L56" s="131">
         <v>2</v>
       </c>
-      <c r="K56" s="132">
-        <v>1</v>
-      </c>
-      <c r="L56" s="96">
-        <v>1</v>
-      </c>
-      <c r="M56" s="95">
+      <c r="M56" s="132">
+        <v>1</v>
+      </c>
+      <c r="N56" s="96">
+        <v>1</v>
+      </c>
+      <c r="O56" s="95">
         <v>256</v>
       </c>
-      <c r="N56" s="96" t="s">
+      <c r="P56" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="O56" s="96" t="s">
+      <c r="Q56" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P56" s="96" t="s">
+      <c r="R56" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q56" s="96" t="s">
+      <c r="S56" s="96" t="s">
         <v>1064</v>
       </c>
-      <c r="R56" s="133" t="s">
+      <c r="T56" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S56" s="114" t="s">
+      <c r="U56" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T56" s="133" t="s">
+      <c r="V56" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U56" s="114" t="s">
+      <c r="W56" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V56" s="96" t="s">
+      <c r="X56" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W56" s="134" t="s">
+      <c r="Y56" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X56" s="135" t="s">
+      <c r="Z56" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y56" s="133" t="s">
+      <c r="AA56" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z56" s="96" t="s">
+      <c r="AB56" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA56" s="134" t="s">
+      <c r="AC56" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB56" s="135" t="s">
+      <c r="AD56" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC56" s="115" t="s">
+      <c r="AE56" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="57" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="114">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="B57" s="130" t="s">
         <v>1067</v>
@@ -54528,70 +54931,76 @@
       <c r="I57" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J57" s="131">
+      <c r="J57" s="101">
+        <v>1</v>
+      </c>
+      <c r="K57" s="101">
+        <v>1</v>
+      </c>
+      <c r="L57" s="131">
         <v>2</v>
       </c>
-      <c r="K57" s="132">
-        <v>1</v>
-      </c>
-      <c r="L57" s="96">
-        <v>1</v>
-      </c>
-      <c r="M57" s="95">
+      <c r="M57" s="132">
+        <v>1</v>
+      </c>
+      <c r="N57" s="96">
+        <v>1</v>
+      </c>
+      <c r="O57" s="95">
         <v>256</v>
       </c>
-      <c r="N57" s="96" t="s">
+      <c r="P57" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="O57" s="96" t="s">
+      <c r="Q57" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P57" s="96" t="s">
+      <c r="R57" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q57" s="96" t="s">
+      <c r="S57" s="96" t="s">
         <v>1065</v>
       </c>
-      <c r="R57" s="133" t="s">
+      <c r="T57" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S57" s="114" t="s">
+      <c r="U57" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T57" s="133" t="s">
+      <c r="V57" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U57" s="114" t="s">
+      <c r="W57" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V57" s="96" t="s">
+      <c r="X57" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W57" s="134" t="s">
+      <c r="Y57" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X57" s="135" t="s">
+      <c r="Z57" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y57" s="133" t="s">
+      <c r="AA57" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z57" s="96" t="s">
+      <c r="AB57" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA57" s="134" t="s">
+      <c r="AC57" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB57" s="135" t="s">
+      <c r="AD57" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC57" s="115" t="s">
+      <c r="AE57" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="58" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="114">
-        <v>23</v>
+    <row r="58" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="101">
+        <v>56</v>
       </c>
       <c r="B58" s="130" t="s">
         <v>1085</v>
@@ -54617,70 +55026,76 @@
       <c r="I58" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J58" s="131">
+      <c r="J58" s="101">
+        <v>1</v>
+      </c>
+      <c r="K58" s="101">
+        <v>1</v>
+      </c>
+      <c r="L58" s="131">
         <v>2</v>
       </c>
-      <c r="K58" s="132">
-        <v>1</v>
-      </c>
-      <c r="L58" s="96">
-        <v>1</v>
-      </c>
-      <c r="M58" s="95">
+      <c r="M58" s="132">
+        <v>1</v>
+      </c>
+      <c r="N58" s="96">
+        <v>1</v>
+      </c>
+      <c r="O58" s="95">
         <v>256</v>
       </c>
-      <c r="N58" s="96" t="s">
+      <c r="P58" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="O58" s="96" t="s">
+      <c r="Q58" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P58" s="96" t="s">
+      <c r="R58" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q58" s="96" t="s">
+      <c r="S58" s="96" t="s">
         <v>1079</v>
       </c>
-      <c r="R58" s="133" t="s">
+      <c r="T58" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S58" s="114" t="s">
+      <c r="U58" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T58" s="133" t="s">
+      <c r="V58" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U58" s="114" t="s">
+      <c r="W58" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V58" s="96" t="s">
+      <c r="X58" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W58" s="134" t="s">
+      <c r="Y58" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X58" s="135" t="s">
+      <c r="Z58" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y58" s="133" t="s">
+      <c r="AA58" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z58" s="96" t="s">
+      <c r="AB58" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA58" s="134" t="s">
+      <c r="AC58" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB58" s="135" t="s">
+      <c r="AD58" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC58" s="115" t="s">
+      <c r="AE58" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="59" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="114">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="B59" s="130" t="s">
         <v>994</v>
@@ -54706,70 +55121,76 @@
       <c r="I59" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J59" s="131">
+      <c r="J59" s="101">
+        <v>1</v>
+      </c>
+      <c r="K59" s="101">
+        <v>1</v>
+      </c>
+      <c r="L59" s="131">
         <v>2</v>
       </c>
-      <c r="K59" s="132">
-        <v>1</v>
-      </c>
-      <c r="L59" s="96">
-        <v>1</v>
-      </c>
-      <c r="M59" s="96">
+      <c r="M59" s="132">
+        <v>1</v>
+      </c>
+      <c r="N59" s="96">
+        <v>1</v>
+      </c>
+      <c r="O59" s="96">
         <v>256</v>
       </c>
-      <c r="N59" s="96" t="s">
+      <c r="P59" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="O59" s="96" t="s">
+      <c r="Q59" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P59" s="96" t="s">
+      <c r="R59" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q59" s="96" t="s">
+      <c r="S59" s="96" t="s">
         <v>1031</v>
       </c>
-      <c r="R59" s="133" t="s">
+      <c r="T59" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S59" s="114" t="s">
+      <c r="U59" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T59" s="133" t="s">
+      <c r="V59" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U59" s="114" t="s">
+      <c r="W59" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V59" s="96" t="s">
+      <c r="X59" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W59" s="134" t="s">
+      <c r="Y59" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X59" s="135" t="s">
+      <c r="Z59" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y59" s="133" t="s">
+      <c r="AA59" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z59" s="96" t="s">
+      <c r="AB59" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA59" s="134" t="s">
+      <c r="AC59" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB59" s="135" t="s">
+      <c r="AD59" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC59" s="115" t="s">
+      <c r="AE59" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="60" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="114">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B60" s="130" t="s">
         <v>1040</v>
@@ -54795,70 +55216,76 @@
       <c r="I60" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J60" s="131">
+      <c r="J60" s="101">
+        <v>1</v>
+      </c>
+      <c r="K60" s="101">
+        <v>1</v>
+      </c>
+      <c r="L60" s="131">
         <v>2</v>
       </c>
-      <c r="K60" s="132">
-        <v>1</v>
-      </c>
-      <c r="L60" s="96">
-        <v>1</v>
-      </c>
-      <c r="M60" s="96">
+      <c r="M60" s="132">
+        <v>1</v>
+      </c>
+      <c r="N60" s="96">
+        <v>1</v>
+      </c>
+      <c r="O60" s="96">
         <v>256</v>
       </c>
-      <c r="N60" s="96" t="s">
+      <c r="P60" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="O60" s="96" t="s">
+      <c r="Q60" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P60" s="96" t="s">
+      <c r="R60" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q60" s="96" t="s">
+      <c r="S60" s="96" t="s">
         <v>1041</v>
       </c>
-      <c r="R60" s="20" t="s">
+      <c r="T60" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S60" s="114" t="s">
+      <c r="U60" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T60" s="20" t="s">
+      <c r="V60" s="20" t="s">
         <v>772</v>
       </c>
-      <c r="U60" s="114" t="s">
+      <c r="W60" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V60" s="96" t="s">
+      <c r="X60" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W60" s="112" t="s">
+      <c r="Y60" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X60" s="113" t="s">
+      <c r="Z60" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y60" s="133" t="s">
+      <c r="AA60" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z60" s="96" t="s">
+      <c r="AB60" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA60" s="112" t="s">
+      <c r="AC60" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB60" s="113" t="s">
+      <c r="AD60" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC60" s="115" t="s">
+      <c r="AE60" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="61" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="114">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B61" s="130" t="s">
         <v>1058</v>
@@ -54884,70 +55311,76 @@
       <c r="I61" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J61" s="131">
+      <c r="J61" s="101">
+        <v>1</v>
+      </c>
+      <c r="K61" s="101">
+        <v>1</v>
+      </c>
+      <c r="L61" s="131">
         <v>2</v>
       </c>
-      <c r="K61" s="132">
-        <v>1</v>
-      </c>
-      <c r="L61" s="96">
-        <v>1</v>
-      </c>
-      <c r="M61" s="96">
+      <c r="M61" s="132">
+        <v>1</v>
+      </c>
+      <c r="N61" s="96">
+        <v>1</v>
+      </c>
+      <c r="O61" s="96">
         <v>256</v>
       </c>
-      <c r="N61" s="96" t="s">
+      <c r="P61" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="O61" s="96" t="s">
+      <c r="Q61" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P61" s="96" t="s">
+      <c r="R61" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q61" s="96" t="s">
+      <c r="S61" s="96" t="s">
         <v>1060</v>
       </c>
-      <c r="R61" s="133" t="s">
+      <c r="T61" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S61" s="114" t="s">
+      <c r="U61" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T61" s="133" t="s">
+      <c r="V61" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U61" s="114" t="s">
+      <c r="W61" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V61" s="96" t="s">
+      <c r="X61" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W61" s="134" t="s">
+      <c r="Y61" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X61" s="135" t="s">
+      <c r="Z61" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y61" s="133" t="s">
+      <c r="AA61" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z61" s="96" t="s">
+      <c r="AB61" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA61" s="134" t="s">
+      <c r="AC61" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB61" s="135" t="s">
+      <c r="AD61" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC61" s="115" t="s">
+      <c r="AE61" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="62" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="114">
-        <v>24</v>
+    <row r="62" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="101">
+        <v>60</v>
       </c>
       <c r="B62" s="130" t="s">
         <v>1059</v>
@@ -54973,70 +55406,76 @@
       <c r="I62" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J62" s="131">
+      <c r="J62" s="101">
+        <v>1</v>
+      </c>
+      <c r="K62" s="101">
+        <v>1</v>
+      </c>
+      <c r="L62" s="131">
         <v>2</v>
       </c>
-      <c r="K62" s="132">
-        <v>1</v>
-      </c>
-      <c r="L62" s="96">
-        <v>1</v>
-      </c>
-      <c r="M62" s="96">
+      <c r="M62" s="132">
+        <v>1</v>
+      </c>
+      <c r="N62" s="96">
+        <v>1</v>
+      </c>
+      <c r="O62" s="96">
         <v>256</v>
       </c>
-      <c r="N62" s="96" t="s">
+      <c r="P62" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="O62" s="96" t="s">
+      <c r="Q62" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P62" s="96" t="s">
+      <c r="R62" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q62" s="96" t="s">
+      <c r="S62" s="96" t="s">
         <v>1061</v>
       </c>
-      <c r="R62" s="20" t="s">
+      <c r="T62" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="S62" s="114" t="s">
+      <c r="U62" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T62" s="20" t="s">
+      <c r="V62" s="20" t="s">
         <v>772</v>
       </c>
-      <c r="U62" s="114" t="s">
+      <c r="W62" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V62" s="96" t="s">
+      <c r="X62" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W62" s="112" t="s">
+      <c r="Y62" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="X62" s="113" t="s">
+      <c r="Z62" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="Y62" s="133" t="s">
+      <c r="AA62" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z62" s="96" t="s">
+      <c r="AB62" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA62" s="112" t="s">
+      <c r="AC62" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AB62" s="113" t="s">
+      <c r="AD62" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AC62" s="115" t="s">
+      <c r="AE62" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="63" spans="1:29" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="114">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B63" s="130" t="s">
         <v>1068</v>
@@ -55062,70 +55501,76 @@
       <c r="I63" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J63" s="131">
+      <c r="J63" s="101">
+        <v>1</v>
+      </c>
+      <c r="K63" s="101">
+        <v>1</v>
+      </c>
+      <c r="L63" s="131">
         <v>2</v>
       </c>
-      <c r="K63" s="132">
-        <v>1</v>
-      </c>
-      <c r="L63" s="96">
-        <v>1</v>
-      </c>
-      <c r="M63" s="96">
+      <c r="M63" s="132">
+        <v>1</v>
+      </c>
+      <c r="N63" s="96">
+        <v>1</v>
+      </c>
+      <c r="O63" s="96">
         <v>256</v>
       </c>
-      <c r="N63" s="96" t="s">
+      <c r="P63" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="O63" s="96" t="s">
+      <c r="Q63" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="P63" s="96" t="s">
+      <c r="R63" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="Q63" s="96" t="s">
+      <c r="S63" s="96" t="s">
         <v>1064</v>
       </c>
-      <c r="R63" s="133" t="s">
+      <c r="T63" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="S63" s="114" t="s">
+      <c r="U63" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="T63" s="133" t="s">
+      <c r="V63" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="U63" s="114" t="s">
+      <c r="W63" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="V63" s="96" t="s">
+      <c r="X63" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="W63" s="134" t="s">
+      <c r="Y63" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="X63" s="135" t="s">
+      <c r="Z63" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="Y63" s="133" t="s">
+      <c r="AA63" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="Z63" s="96" t="s">
+      <c r="AB63" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AA63" s="134" t="s">
+      <c r="AC63" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AB63" s="135" t="s">
+      <c r="AD63" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AC63" s="115" t="s">
+      <c r="AE63" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="64" spans="1:29" s="73" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="74">
-        <v>24</v>
+    <row r="64" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="114">
+        <v>62</v>
       </c>
       <c r="B64" s="116" t="s">
         <v>1069</v>
@@ -55151,70 +55596,76 @@
       <c r="I64" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="J64" s="119">
+      <c r="J64" s="101">
+        <v>1</v>
+      </c>
+      <c r="K64" s="101">
+        <v>1</v>
+      </c>
+      <c r="L64" s="119">
         <v>2</v>
       </c>
-      <c r="K64" s="120">
-        <v>1</v>
-      </c>
-      <c r="L64" s="73">
-        <v>1</v>
-      </c>
-      <c r="M64" s="73">
+      <c r="M64" s="120">
+        <v>1</v>
+      </c>
+      <c r="N64" s="73">
+        <v>1</v>
+      </c>
+      <c r="O64" s="73">
         <v>256</v>
       </c>
-      <c r="N64" s="73" t="s">
+      <c r="P64" s="73" t="s">
         <v>1029</v>
       </c>
-      <c r="O64" s="73" t="s">
+      <c r="Q64" s="73" t="s">
         <v>1030</v>
       </c>
-      <c r="P64" s="73" t="s">
+      <c r="R64" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="Q64" s="73" t="s">
+      <c r="S64" s="73" t="s">
         <v>1065</v>
       </c>
-      <c r="R64" s="80" t="s">
+      <c r="T64" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="S64" s="74" t="s">
+      <c r="U64" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="T64" s="80" t="s">
+      <c r="V64" s="80" t="s">
         <v>772</v>
       </c>
-      <c r="U64" s="74" t="s">
+      <c r="W64" s="74" t="s">
         <v>989</v>
       </c>
-      <c r="V64" s="73" t="s">
+      <c r="X64" s="73" t="s">
         <v>990</v>
       </c>
-      <c r="W64" s="121" t="s">
+      <c r="Y64" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="X64" s="124" t="s">
+      <c r="Z64" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="Y64" s="85" t="s">
+      <c r="AA64" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="Z64" s="73" t="s">
+      <c r="AB64" s="73" t="s">
         <v>991</v>
       </c>
-      <c r="AA64" s="121" t="s">
+      <c r="AC64" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AB64" s="124" t="s">
+      <c r="AD64" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AC64" s="122" t="s">
+      <c r="AE64" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="65" spans="1:29" s="73" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="74">
-        <v>24</v>
+    <row r="65" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="114">
+        <v>63</v>
       </c>
       <c r="B65" s="116" t="s">
         <v>1078</v>
@@ -55240,70 +55691,352 @@
       <c r="I65" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="J65" s="119">
+      <c r="J65" s="101">
+        <v>1</v>
+      </c>
+      <c r="K65" s="101">
+        <v>1</v>
+      </c>
+      <c r="L65" s="119">
         <v>2</v>
       </c>
-      <c r="K65" s="120">
-        <v>1</v>
-      </c>
-      <c r="L65" s="73">
-        <v>1</v>
-      </c>
-      <c r="M65" s="73">
+      <c r="M65" s="120">
+        <v>1</v>
+      </c>
+      <c r="N65" s="73">
+        <v>1</v>
+      </c>
+      <c r="O65" s="73">
         <v>256</v>
       </c>
-      <c r="N65" s="73" t="s">
+      <c r="P65" s="73" t="s">
         <v>1029</v>
       </c>
-      <c r="O65" s="73" t="s">
+      <c r="Q65" s="73" t="s">
         <v>1030</v>
       </c>
-      <c r="P65" s="73" t="s">
+      <c r="R65" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="Q65" s="73" t="s">
+      <c r="S65" s="73" t="s">
         <v>1079</v>
       </c>
-      <c r="R65" s="80" t="s">
+      <c r="T65" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="S65" s="74" t="s">
+      <c r="U65" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="T65" s="80" t="s">
+      <c r="V65" s="80" t="s">
         <v>772</v>
       </c>
-      <c r="U65" s="74" t="s">
+      <c r="W65" s="74" t="s">
         <v>989</v>
       </c>
-      <c r="V65" s="73" t="s">
+      <c r="X65" s="73" t="s">
         <v>990</v>
       </c>
-      <c r="W65" s="121" t="s">
+      <c r="Y65" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="X65" s="124" t="s">
+      <c r="Z65" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="Y65" s="85" t="s">
+      <c r="AA65" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="Z65" s="73" t="s">
+      <c r="AB65" s="73" t="s">
         <v>991</v>
       </c>
-      <c r="AA65" s="121" t="s">
+      <c r="AC65" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AB65" s="124" t="s">
+      <c r="AD65" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AC65" s="122" t="s">
+      <c r="AE65" s="122" t="s">
         <v>949</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A66" s="101">
+        <v>64</v>
+      </c>
+      <c r="B66" s="102" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C66" s="102" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D66" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E66" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F66" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G66" s="95">
+        <v>2</v>
+      </c>
+      <c r="H66" s="114" t="s">
+        <v>105</v>
+      </c>
+      <c r="I66" s="130" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="101">
+        <v>5</v>
+      </c>
+      <c r="K66" s="101">
+        <v>1</v>
+      </c>
+      <c r="L66" s="131">
+        <v>1</v>
+      </c>
+      <c r="M66" s="132">
+        <v>1</v>
+      </c>
+      <c r="N66" s="95">
+        <v>1</v>
+      </c>
+      <c r="P66" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>868</v>
+      </c>
+      <c r="R66" s="73" t="s">
+        <v>914</v>
+      </c>
+      <c r="S66" t="s">
+        <v>1090</v>
+      </c>
+      <c r="T66" s="133" t="s">
+        <v>95</v>
+      </c>
+      <c r="U66" s="101" t="s">
+        <v>840</v>
+      </c>
+      <c r="V66" s="126" t="s">
+        <v>775</v>
+      </c>
+      <c r="W66" s="107" t="s">
+        <v>841</v>
+      </c>
+      <c r="X66" s="101" t="s">
+        <v>842</v>
+      </c>
+      <c r="Y66" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="Z66" s="137" t="s">
+        <v>901</v>
+      </c>
+      <c r="AA66" s="129" t="s">
+        <v>843</v>
+      </c>
+      <c r="AB66" s="101" t="s">
+        <v>844</v>
+      </c>
+      <c r="AC66" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AD66" s="137" t="s">
+        <v>901</v>
+      </c>
+      <c r="AE66" s="129" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A67" s="114">
+        <v>65</v>
+      </c>
+      <c r="B67" s="110" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C67" s="110" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D67" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E67" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F67" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67" s="114" t="s">
+        <v>847</v>
+      </c>
+      <c r="I67" s="130" t="s">
+        <v>13</v>
+      </c>
+      <c r="J67" s="101">
+        <v>5</v>
+      </c>
+      <c r="K67" s="101">
+        <v>1</v>
+      </c>
+      <c r="L67" s="131">
+        <v>1</v>
+      </c>
+      <c r="M67" s="132">
+        <v>1</v>
+      </c>
+      <c r="N67" s="95">
+        <v>1</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1095</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>873</v>
+      </c>
+      <c r="R67" s="73" t="s">
+        <v>914</v>
+      </c>
+      <c r="S67" t="s">
+        <v>1098</v>
+      </c>
+      <c r="T67" s="133" t="s">
+        <v>95</v>
+      </c>
+      <c r="U67" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="V67" s="28" t="s">
+        <v>848</v>
+      </c>
+      <c r="W67" t="s">
+        <v>849</v>
+      </c>
+      <c r="X67" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="Y67" s="23" t="s">
+        <v>765</v>
+      </c>
+      <c r="Z67" s="24" t="s">
+        <v>901</v>
+      </c>
+      <c r="AA67" s="27" t="s">
+        <v>851</v>
+      </c>
+      <c r="AB67" s="6" t="s">
+        <v>844</v>
+      </c>
+      <c r="AC67" s="23" t="s">
+        <v>845</v>
+      </c>
+      <c r="AD67" s="24" t="s">
+        <v>901</v>
+      </c>
+      <c r="AE67" s="27" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A68" s="114">
+        <v>66</v>
+      </c>
+      <c r="B68" s="110" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C68" s="110" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D68" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E68" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F68" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68" s="114" t="s">
+        <v>108</v>
+      </c>
+      <c r="I68" s="130" t="s">
+        <v>13</v>
+      </c>
+      <c r="J68" s="101">
+        <v>5</v>
+      </c>
+      <c r="K68" s="101">
+        <v>1</v>
+      </c>
+      <c r="L68" s="131">
+        <v>1</v>
+      </c>
+      <c r="M68" s="132">
+        <v>1</v>
+      </c>
+      <c r="N68" s="95">
+        <v>1</v>
+      </c>
+      <c r="P68" t="s">
+        <v>1096</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>1097</v>
+      </c>
+      <c r="R68" s="73" t="s">
+        <v>914</v>
+      </c>
+      <c r="S68" t="s">
+        <v>1099</v>
+      </c>
+      <c r="T68" s="133" t="s">
+        <v>95</v>
+      </c>
+      <c r="U68" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="V68" s="133" t="s">
+        <v>108</v>
+      </c>
+      <c r="W68" s="114" t="s">
+        <v>1091</v>
+      </c>
+      <c r="X68" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="Y68" s="23" t="s">
+        <v>765</v>
+      </c>
+      <c r="Z68" s="24" t="s">
+        <v>901</v>
+      </c>
+      <c r="AA68" s="27" t="s">
+        <v>851</v>
+      </c>
+      <c r="AB68" s="95" t="s">
+        <v>996</v>
+      </c>
+      <c r="AC68" s="23" t="s">
+        <v>845</v>
+      </c>
+      <c r="AD68" s="24" t="s">
+        <v>901</v>
+      </c>
+      <c r="AE68" s="27" t="s">
+        <v>851</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="I2:I5 I21 I28 I35 I42:I45 I52 I59">
+  <conditionalFormatting sqref="I21 I28 I35 I42:I45 I52 I59 I2:K2 I3:I5 J3:K68">
     <cfRule type="containsText" dxfId="388" priority="464" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I2)))</formula>
     </cfRule>
@@ -55325,7 +56058,7 @@
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I1">
+  <conditionalFormatting sqref="I1:K1">
     <cfRule type="containsText" dxfId="382" priority="458" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I1)))</formula>
     </cfRule>
@@ -56811,4 +57544,23 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC72B34-3F4F-4FFB-B9F1-CADAF091BA12}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="61.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dataset_train_transformer-v2.xlsx
+++ b/dataset_train_transformer-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2024 Foundation model\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAD40C4-51C3-4F38-8CFA-486D7672990D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375F894E-A497-4DE7-B9C1-F5B177A7C187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="2520" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13815" yWindow="2595" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="64x64" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11402" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11678" uniqueCount="1136">
   <si>
     <t>path_lr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3670,6 +3670,119 @@
   <si>
     <t>out_channels</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-projection-flywing-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-projection-flywing-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-projection-flywing-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-projection-flywing-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CARE-PROJ-FLYWING-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CARE-PROJ-FLYWING-1</t>
+  </si>
+  <si>
+    <t>CARE-PROJ-FLYWING-2</t>
+  </si>
+  <si>
+    <t>CARE-PROJ-FLYWING-3</t>
+  </si>
+  <si>
+    <t>proj</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_0_p64_s64</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_1_p64_s64</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_2_p64_s64</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_3_p64_s64</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_2_proj_premosa_p64_s64</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test_p64_s64_1.txt</t>
+  </si>
+  <si>
+    <t>surface projection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drosophila wing</t>
+  </si>
+  <si>
+    <t>Ecad::GFP (GFP)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>with a Zeiss AxioObserver  stand, Zeiss LCI Plan-Neofluar 63x, 1.3 NA Imm Corr objective, Zeiss AxioCam MR3 camera  (2x2 binning) and a Yokogawa CSU-X1 spinning disk unit.</t>
+  </si>
+  <si>
+    <t>Images were acquired with a spinning disk microscope equipped with a Zeiss AxioObserver  stand, Zeiss LCI Plan-Neofluar 63x, 1.3 NA Imm Corr objective, Zeiss AxioCam MR3 camera  (2x2 binning) and a Yokogawa CSU-X1 spinning disk unit.</t>
+  </si>
+  <si>
+    <t>265 x 265 nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-denoising-flywing-0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-denoising-flywing-1</t>
+  </si>
+  <si>
+    <t>care-denoising-flywing-2</t>
+  </si>
+  <si>
+    <t>care-denoising-flywing-3</t>
+  </si>
+  <si>
+    <t>care-projection-flywing-0-dn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-projection-flywing-1-dn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-projection-flywing-2-dn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-projection-flywing-3-dn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_0_proj_max_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_1_proj_max_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_2_proj_max_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_3_proj_max_p64_s64_2d</t>
   </si>
 </sst>
 </file>
@@ -49603,16 +49716,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A163AA7F-4DF5-48A0-AE09-D011016C5669}">
-  <dimension ref="A1:AE68"/>
+  <dimension ref="A1:AE80"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="20.75" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
     <col min="5" max="5" width="5.25" customWidth="1"/>
     <col min="6" max="6" width="5.375" customWidth="1"/>
     <col min="7" max="7" width="4.125" customWidth="1"/>
-    <col min="12" max="12" width="5.375" customWidth="1"/>
-    <col min="13" max="13" width="5.625" customWidth="1"/>
+    <col min="8" max="8" width="10.375" customWidth="1"/>
+    <col min="9" max="9" width="5.375" customWidth="1"/>
+    <col min="10" max="11" width="3.625" customWidth="1"/>
+    <col min="12" max="12" width="3.75" customWidth="1"/>
+    <col min="13" max="13" width="3.5" customWidth="1"/>
+    <col min="14" max="14" width="3.375" customWidth="1"/>
+    <col min="15" max="15" width="4" customWidth="1"/>
     <col min="19" max="19" width="75" customWidth="1"/>
     <col min="20" max="20" width="10.5" customWidth="1"/>
   </cols>
@@ -55991,7 +56109,7 @@
       <c r="Q68" t="s">
         <v>1097</v>
       </c>
-      <c r="R68" s="73" t="s">
+      <c r="R68" s="96" t="s">
         <v>914</v>
       </c>
       <c r="S68" t="s">
@@ -56032,6 +56150,1110 @@
       </c>
       <c r="AE68" s="27" t="s">
         <v>851</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="107">
+        <v>67</v>
+      </c>
+      <c r="B69" s="107" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C69" s="107" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D69" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E69" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F69" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G69">
+        <v>2</v>
+      </c>
+      <c r="H69" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I69" s="107" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J69" s="107">
+        <v>50</v>
+      </c>
+      <c r="K69" s="107">
+        <v>1</v>
+      </c>
+      <c r="L69" s="107">
+        <v>1</v>
+      </c>
+      <c r="M69" s="107">
+        <v>1</v>
+      </c>
+      <c r="N69" s="107">
+        <v>1</v>
+      </c>
+      <c r="P69" s="107" t="s">
+        <v>1112</v>
+      </c>
+      <c r="Q69" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R69" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S69" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T69" s="107" t="s">
+        <v>1118</v>
+      </c>
+      <c r="U69" s="107" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V69" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W69" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X69" s="107" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y69" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z69" s="107" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA69" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB69" s="107" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC69" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD69" s="107" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE69" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A70" s="107">
+        <v>68</v>
+      </c>
+      <c r="B70" s="110" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C70" s="107" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D70" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E70" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F70" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G70">
+        <v>2</v>
+      </c>
+      <c r="H70" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I70" s="107" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J70" s="107">
+        <v>50</v>
+      </c>
+      <c r="K70" s="107">
+        <v>1</v>
+      </c>
+      <c r="L70" s="107">
+        <v>1</v>
+      </c>
+      <c r="M70" s="107">
+        <v>1</v>
+      </c>
+      <c r="N70" s="107">
+        <v>1</v>
+      </c>
+      <c r="P70" t="s">
+        <v>1113</v>
+      </c>
+      <c r="Q70" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R70" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S70" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T70" s="133" t="s">
+        <v>1118</v>
+      </c>
+      <c r="U70" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V70" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W70" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X70" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y70" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA70" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC70" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE70" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A71" s="107">
+        <v>69</v>
+      </c>
+      <c r="B71" s="110" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C71" s="107" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D71" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E71" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F71" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G71">
+        <v>2</v>
+      </c>
+      <c r="H71" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I71" s="107" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J71" s="107">
+        <v>50</v>
+      </c>
+      <c r="K71" s="107">
+        <v>1</v>
+      </c>
+      <c r="L71" s="107">
+        <v>1</v>
+      </c>
+      <c r="M71" s="107">
+        <v>1</v>
+      </c>
+      <c r="N71" s="107">
+        <v>1</v>
+      </c>
+      <c r="P71" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q71" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R71" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S71" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T71" s="133" t="s">
+        <v>1118</v>
+      </c>
+      <c r="U71" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V71" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W71" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X71" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y71" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA71" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC71" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE71" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A72" s="107">
+        <v>70</v>
+      </c>
+      <c r="B72" s="110" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C72" s="107" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D72" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E72" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F72" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I72" s="107" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J72" s="107">
+        <v>50</v>
+      </c>
+      <c r="K72" s="107">
+        <v>1</v>
+      </c>
+      <c r="L72" s="107">
+        <v>1</v>
+      </c>
+      <c r="M72" s="107">
+        <v>1</v>
+      </c>
+      <c r="N72" s="107">
+        <v>1</v>
+      </c>
+      <c r="P72" t="s">
+        <v>1115</v>
+      </c>
+      <c r="Q72" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R72" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S72" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T72" s="133" t="s">
+        <v>1118</v>
+      </c>
+      <c r="U72" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V72" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W72" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X72" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y72" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA72" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC72" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE72" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="107">
+        <v>71</v>
+      </c>
+      <c r="B73" s="107" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C73" s="107" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D73" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E73" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F73" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G73">
+        <v>2</v>
+      </c>
+      <c r="H73" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I73" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J73" s="107">
+        <v>1</v>
+      </c>
+      <c r="K73" s="107">
+        <v>1</v>
+      </c>
+      <c r="L73" s="107">
+        <v>1</v>
+      </c>
+      <c r="M73" s="107">
+        <v>1</v>
+      </c>
+      <c r="N73" s="107">
+        <v>1</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1132</v>
+      </c>
+      <c r="Q73" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R73" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S73" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T73" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U73" s="107" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V73" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W73" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X73" s="107" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y73" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z73" s="107" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA73" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB73" s="107" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC73" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD73" s="107" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE73" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A74" s="107">
+        <v>72</v>
+      </c>
+      <c r="B74" s="107" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C74" s="107" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D74" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E74" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F74" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G74">
+        <v>2</v>
+      </c>
+      <c r="H74" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I74" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J74" s="107">
+        <v>1</v>
+      </c>
+      <c r="K74" s="107">
+        <v>1</v>
+      </c>
+      <c r="L74" s="107">
+        <v>1</v>
+      </c>
+      <c r="M74" s="107">
+        <v>1</v>
+      </c>
+      <c r="N74" s="107">
+        <v>1</v>
+      </c>
+      <c r="P74" t="s">
+        <v>1133</v>
+      </c>
+      <c r="Q74" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R74" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S74" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T74" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U74" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V74" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W74" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X74" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y74" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA74" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC74" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE74" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A75" s="107">
+        <v>73</v>
+      </c>
+      <c r="B75" s="107" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C75" s="107" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D75" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E75" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F75" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+      <c r="H75" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I75" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J75" s="107">
+        <v>1</v>
+      </c>
+      <c r="K75" s="107">
+        <v>1</v>
+      </c>
+      <c r="L75" s="107">
+        <v>1</v>
+      </c>
+      <c r="M75" s="107">
+        <v>1</v>
+      </c>
+      <c r="N75" s="107">
+        <v>1</v>
+      </c>
+      <c r="P75" t="s">
+        <v>1134</v>
+      </c>
+      <c r="Q75" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R75" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S75" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T75" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U75" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V75" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W75" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X75" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y75" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA75" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC75" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE75" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A76" s="107">
+        <v>74</v>
+      </c>
+      <c r="B76" s="107" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C76" s="107" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D76" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E76" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F76" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I76" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J76" s="107">
+        <v>1</v>
+      </c>
+      <c r="K76" s="107">
+        <v>1</v>
+      </c>
+      <c r="L76" s="107">
+        <v>1</v>
+      </c>
+      <c r="M76" s="107">
+        <v>1</v>
+      </c>
+      <c r="N76" s="107">
+        <v>1</v>
+      </c>
+      <c r="P76" t="s">
+        <v>1135</v>
+      </c>
+      <c r="Q76" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R76" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S76" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T76" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U76" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V76" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W76" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X76" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y76" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA76" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC76" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE76" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="107">
+        <v>75</v>
+      </c>
+      <c r="B77" s="107" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C77" s="107" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D77" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E77" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F77" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I77" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J77" s="107">
+        <v>50</v>
+      </c>
+      <c r="K77" s="107">
+        <v>1</v>
+      </c>
+      <c r="L77" s="107">
+        <v>1</v>
+      </c>
+      <c r="M77" s="107">
+        <v>1</v>
+      </c>
+      <c r="N77" s="107">
+        <v>1</v>
+      </c>
+      <c r="P77" s="107" t="s">
+        <v>1112</v>
+      </c>
+      <c r="Q77" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R77" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S77" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T77" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U77" s="107" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V77" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W77" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X77" s="107" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y77" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z77" s="107" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA77" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB77" s="107" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC77" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD77" s="107" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE77" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A78" s="107">
+        <v>76</v>
+      </c>
+      <c r="B78" s="110" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C78" s="107" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D78" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E78" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F78" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+      <c r="H78" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I78" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J78" s="107">
+        <v>50</v>
+      </c>
+      <c r="K78" s="107">
+        <v>1</v>
+      </c>
+      <c r="L78" s="107">
+        <v>1</v>
+      </c>
+      <c r="M78" s="107">
+        <v>1</v>
+      </c>
+      <c r="N78" s="107">
+        <v>1</v>
+      </c>
+      <c r="P78" t="s">
+        <v>1113</v>
+      </c>
+      <c r="Q78" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R78" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S78" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T78" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U78" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V78" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W78" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X78" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y78" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA78" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC78" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE78" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A79" s="107">
+        <v>77</v>
+      </c>
+      <c r="B79" s="110" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C79" s="107" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D79" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E79" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F79" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G79">
+        <v>2</v>
+      </c>
+      <c r="H79" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I79" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J79" s="107">
+        <v>50</v>
+      </c>
+      <c r="K79" s="107">
+        <v>1</v>
+      </c>
+      <c r="L79" s="107">
+        <v>1</v>
+      </c>
+      <c r="M79" s="107">
+        <v>1</v>
+      </c>
+      <c r="N79" s="107">
+        <v>1</v>
+      </c>
+      <c r="P79" t="s">
+        <v>1114</v>
+      </c>
+      <c r="Q79" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R79" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S79" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T79" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U79" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V79" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W79" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X79" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y79" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA79" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC79" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE79" s="107" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A80" s="107">
+        <v>78</v>
+      </c>
+      <c r="B80" s="110" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C80" s="107" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D80" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E80" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F80" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G80">
+        <v>2</v>
+      </c>
+      <c r="H80" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="I80" s="107" t="s">
+        <v>12</v>
+      </c>
+      <c r="J80" s="107">
+        <v>50</v>
+      </c>
+      <c r="K80" s="107">
+        <v>1</v>
+      </c>
+      <c r="L80" s="107">
+        <v>1</v>
+      </c>
+      <c r="M80" s="107">
+        <v>1</v>
+      </c>
+      <c r="N80" s="107">
+        <v>1</v>
+      </c>
+      <c r="P80" t="s">
+        <v>1115</v>
+      </c>
+      <c r="Q80" s="107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="R80" s="96" t="s">
+        <v>914</v>
+      </c>
+      <c r="S80" s="107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="T80" s="107" t="s">
+        <v>96</v>
+      </c>
+      <c r="U80" t="s">
+        <v>1119</v>
+      </c>
+      <c r="V80" s="107" t="s">
+        <v>116</v>
+      </c>
+      <c r="W80" s="107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="X80" t="s">
+        <v>1122</v>
+      </c>
+      <c r="Y80" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AA80" s="107" t="s">
+        <v>1123</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AC80" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>1121</v>
+      </c>
+      <c r="AE80" s="107" t="s">
+        <v>1123</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_train_transformer-v2.xlsx
+++ b/dataset_train_transformer-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2024 Foundation model\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375F894E-A497-4DE7-B9C1-F5B177A7C187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADDD848-CA56-49D1-A755-34CED7C49CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13815" yWindow="2595" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18375" yWindow="2625" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="64x64" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11678" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12093" uniqueCount="1203">
   <si>
     <t>path_lr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3783,6 +3783,244 @@
   </si>
   <si>
     <t>E:\qiqilu\datasets\CARE_Projection_Flywing\transformed\test\channel_0\condition_3_proj_max_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20.9 x 20.9 nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train_sr_p64_s64_2d_1.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\SIM_nonlinear_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_1_up3_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-2</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-3</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-4</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-5</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-6</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-7</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-8</t>
+  </si>
+  <si>
+    <t>BioSR-F-actin-SR-9</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_2_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_3_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_4_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_5_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_6_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_7_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_8_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\BioSR\transformed\F_actin_nonlinear\train\channel_0\WF_noise_level_9_up3_p64_s64_2d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-2</t>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-3</t>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-4</t>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-5</t>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-6</t>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-7</t>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-8</t>
+  </si>
+  <si>
+    <t>biosr-factinnl-sr3-9</t>
+  </si>
+  <si>
+    <t>62.6 x 62.6 nm. Nearest interpolation with a factor of 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>62.6 x 62.6 nm. Nearest interpolation with a factor of 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\CARE_Isotropic_Drosophila\transformed\train_p64_2d_1.txt</t>
+  </si>
+  <si>
+    <t>CARE-drosophila</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>care-iso-drosophila-3d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-0-64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-0-128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-1-64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-1-128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SynProt-0-64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SynProt-0-128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SynProt-1-64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synaptic protein PSD95</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synaptic protein Bassoon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>super-resolution with a scale factor of 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fixed hippocampal neurons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STAR 635P (red)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>with a 100x 1.4NA oil objective in confocal mode, confocal detection pinhole was set around 1 Airy unit.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60 x 60 nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>with a 4 color Abberior ExpertLine STED system equipped with a 100x 1.4NA oil objective.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15 x 15 nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SynProt-1-128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\confocal_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\confocal_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\STED_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\STED_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\confocal_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\confocal_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\STED_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\STED_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test_p64_s64_2d_1.txt</t>
+  </si>
+  <si>
+    <t>num of patches</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test_p128_s128_2d_1.txt</t>
+  </si>
+  <si>
+    <t>synprot-channe-0-128-granule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-1-128-granule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-0-64-granule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-1-64-granule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8341,18 +8579,18 @@
     <col min="10" max="10" width="16.375" customWidth="1"/>
     <col min="11" max="11" width="12.875" customWidth="1"/>
     <col min="12" max="12" width="11.375" customWidth="1"/>
-    <col min="13" max="13" width="9.875" style="31" customWidth="1"/>
+    <col min="13" max="13" width="37.625" style="31" customWidth="1"/>
     <col min="14" max="14" width="19.5" customWidth="1"/>
     <col min="15" max="15" width="23.375" style="28" customWidth="1"/>
     <col min="16" max="16" width="18.875" style="50" customWidth="1"/>
     <col min="17" max="17" width="17" style="3" customWidth="1"/>
     <col min="18" max="18" width="22.5" style="21" customWidth="1"/>
     <col min="19" max="19" width="25.125" style="55" customWidth="1"/>
-    <col min="20" max="20" width="14.5" style="25" customWidth="1"/>
+    <col min="20" max="20" width="35.125" style="25" customWidth="1"/>
     <col min="21" max="21" width="22.125" style="1" customWidth="1"/>
     <col min="22" max="22" width="25.75" style="19" customWidth="1"/>
     <col min="23" max="23" width="23.75" style="16" customWidth="1"/>
-    <col min="24" max="24" width="15.25" style="25" customWidth="1"/>
+    <col min="24" max="24" width="34" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="4" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -14151,7 +14389,7 @@
         <v>882</v>
       </c>
       <c r="T81" s="27" t="s">
-        <v>770</v>
+        <v>1166</v>
       </c>
       <c r="U81" s="6" t="s">
         <v>140</v>
@@ -49716,7 +49954,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A163AA7F-4DF5-48A0-AE09-D011016C5669}">
-  <dimension ref="A1:AE80"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -49731,11 +49969,12 @@
     <col min="13" max="13" width="3.5" customWidth="1"/>
     <col min="14" max="14" width="3.375" customWidth="1"/>
     <col min="15" max="15" width="4" customWidth="1"/>
-    <col min="19" max="19" width="75" customWidth="1"/>
-    <col min="20" max="20" width="10.5" customWidth="1"/>
+    <col min="16" max="16" width="6.375" customWidth="1"/>
+    <col min="20" max="20" width="75" customWidth="1"/>
+    <col min="21" max="21" width="45.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -49782,55 +50021,58 @@
         <v>931</v>
       </c>
       <c r="P1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="Q1" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" t="s">
-        <v>1</v>
-      </c>
       <c r="R1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S1" t="s">
         <v>932</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>2</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="U1" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>90</v>
       </c>
-      <c r="V1" s="28" t="s">
+      <c r="W1" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>152</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>97</v>
       </c>
-      <c r="Y1" s="112" t="s">
+      <c r="Z1" s="112" t="s">
         <v>745</v>
       </c>
-      <c r="Z1" s="113" t="s">
+      <c r="AA1" s="113" t="s">
         <v>746</v>
       </c>
-      <c r="AA1" s="25" t="s">
+      <c r="AB1" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>99</v>
       </c>
-      <c r="AC1" s="112" t="s">
+      <c r="AD1" s="112" t="s">
         <v>756</v>
       </c>
-      <c r="AD1" s="50" t="s">
+      <c r="AE1" s="50" t="s">
         <v>819</v>
       </c>
-      <c r="AE1" s="25" t="s">
+      <c r="AF1" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="101">
         <v>0</v>
       </c>
@@ -49873,50 +50115,50 @@
       <c r="N2" s="107">
         <v>1</v>
       </c>
-      <c r="P2" s="107" t="s">
+      <c r="Q2" s="107" t="s">
         <v>933</v>
       </c>
-      <c r="Q2" s="96" t="s">
+      <c r="R2" s="96" t="s">
         <v>936</v>
       </c>
-      <c r="R2" s="107" t="s">
+      <c r="S2" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="S2" s="107" t="s">
+      <c r="T2" s="107" t="s">
         <v>938</v>
       </c>
-      <c r="T2" s="108" t="s">
+      <c r="U2" s="108" t="s">
         <v>96</v>
       </c>
-      <c r="U2" s="101" t="s">
+      <c r="V2" s="101" t="s">
         <v>915</v>
       </c>
-      <c r="V2" s="108" t="s">
+      <c r="W2" s="108" t="s">
         <v>916</v>
       </c>
-      <c r="W2" s="101" t="s">
+      <c r="X2" s="101" t="s">
         <v>909</v>
       </c>
-      <c r="Y2" s="108" t="s">
+      <c r="Z2" s="108" t="s">
         <v>917</v>
       </c>
-      <c r="Z2" s="104" t="s">
+      <c r="AA2" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="AA2" s="109" t="s">
+      <c r="AB2" s="109" t="s">
         <v>918</v>
       </c>
-      <c r="AC2" s="108" t="s">
+      <c r="AD2" s="108" t="s">
         <v>917</v>
       </c>
-      <c r="AD2" s="104" t="s">
+      <c r="AE2" s="104" t="s">
         <v>120</v>
       </c>
-      <c r="AE2" s="107" t="s">
+      <c r="AF2" s="107" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="114">
         <v>1</v>
       </c>
@@ -49959,51 +50201,51 @@
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>934</v>
       </c>
-      <c r="Q3" s="96" t="s">
+      <c r="R3" s="96" t="s">
         <v>936</v>
       </c>
-      <c r="R3" s="96" t="s">
+      <c r="S3" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S3" s="96" t="s">
+      <c r="T3" s="96" t="s">
         <v>938</v>
       </c>
-      <c r="T3" s="115" t="s">
+      <c r="U3" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="V3" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="V3" s="28" t="s">
+      <c r="W3" s="28" t="s">
         <v>921</v>
       </c>
-      <c r="W3" s="114" t="s">
+      <c r="X3" s="114" t="s">
         <v>909</v>
       </c>
-      <c r="Y3" s="115" t="s">
+      <c r="Z3" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="Z3" s="96" t="s">
+      <c r="AA3" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="AA3" s="115" t="s">
+      <c r="AB3" s="115" t="s">
         <v>918</v>
       </c>
-      <c r="AB3" s="96"/>
-      <c r="AC3" s="115" t="s">
+      <c r="AC3" s="96"/>
+      <c r="AD3" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="AD3" s="96" t="s">
+      <c r="AE3" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="114">
         <v>2</v>
       </c>
@@ -50046,51 +50288,51 @@
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>935</v>
       </c>
-      <c r="Q4" s="96" t="s">
+      <c r="R4" s="96" t="s">
         <v>936</v>
       </c>
-      <c r="R4" s="96" t="s">
+      <c r="S4" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S4" s="96" t="s">
+      <c r="T4" s="96" t="s">
         <v>938</v>
       </c>
-      <c r="T4" s="115" t="s">
+      <c r="U4" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="V4" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="V4" s="28" t="s">
+      <c r="W4" s="28" t="s">
         <v>916</v>
       </c>
-      <c r="W4" s="114" t="s">
+      <c r="X4" s="114" t="s">
         <v>909</v>
       </c>
-      <c r="Y4" s="115" t="s">
+      <c r="Z4" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="Z4" s="96" t="s">
+      <c r="AA4" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="AA4" s="115" t="s">
+      <c r="AB4" s="115" t="s">
         <v>918</v>
       </c>
-      <c r="AB4" s="96"/>
-      <c r="AC4" s="115" t="s">
+      <c r="AC4" s="96"/>
+      <c r="AD4" s="115" t="s">
         <v>917</v>
       </c>
-      <c r="AD4" s="96" t="s">
+      <c r="AE4" s="96" t="s">
         <v>120</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="114">
         <v>3</v>
       </c>
@@ -50133,50 +50375,50 @@
       <c r="N5" s="73">
         <v>1</v>
       </c>
-      <c r="P5" s="73" t="s">
+      <c r="Q5" s="73" t="s">
         <v>936</v>
       </c>
-      <c r="Q5" s="73" t="s">
+      <c r="R5" s="73" t="s">
         <v>937</v>
       </c>
-      <c r="R5" s="73" t="s">
+      <c r="S5" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S5" s="73" t="s">
+      <c r="T5" s="73" t="s">
         <v>938</v>
       </c>
-      <c r="T5" s="123" t="s">
+      <c r="U5" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="U5" s="74" t="s">
+      <c r="V5" s="74" t="s">
         <v>915</v>
       </c>
-      <c r="V5" s="123" t="s">
+      <c r="W5" s="123" t="s">
         <v>916</v>
       </c>
-      <c r="W5" s="74" t="s">
+      <c r="X5" s="74" t="s">
         <v>909</v>
       </c>
-      <c r="Y5" s="123" t="s">
+      <c r="Z5" s="123" t="s">
         <v>917</v>
       </c>
-      <c r="Z5" s="118" t="s">
+      <c r="AA5" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="AA5" s="122" t="s">
+      <c r="AB5" s="122" t="s">
         <v>918</v>
       </c>
-      <c r="AC5" s="123" t="s">
+      <c r="AD5" s="123" t="s">
         <v>917</v>
       </c>
-      <c r="AD5" s="118" t="s">
+      <c r="AE5" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="AE5" s="73" t="s">
+      <c r="AF5" s="73" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="101">
         <v>4</v>
       </c>
@@ -50222,56 +50464,56 @@
       <c r="O6">
         <v>256</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>1007</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>1016</v>
       </c>
-      <c r="R6" s="96" t="s">
+      <c r="S6" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S6" t="s">
+      <c r="T6" t="s">
         <v>1017</v>
       </c>
-      <c r="T6" s="20" t="s">
+      <c r="U6" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U6" s="6" t="s">
+      <c r="V6" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V6" s="20" t="s">
+      <c r="W6" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="W6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>945</v>
       </c>
-      <c r="Y6" s="112" t="s">
+      <c r="Z6" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z6" s="113" t="s">
+      <c r="AA6" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA6" s="27" t="s">
+      <c r="AB6" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB6" t="s">
+      <c r="AC6" t="s">
         <v>948</v>
       </c>
-      <c r="AC6" s="112" t="s">
+      <c r="AD6" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD6" s="113" t="s">
+      <c r="AE6" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE6" s="25" t="s">
+      <c r="AF6" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="114">
         <v>5</v>
       </c>
@@ -50317,56 +50559,56 @@
       <c r="O7">
         <v>512</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>1007</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="R7" t="s">
         <v>1016</v>
       </c>
-      <c r="R7" s="96" t="s">
+      <c r="S7" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S7" t="s">
+      <c r="T7" t="s">
         <v>1037</v>
       </c>
-      <c r="T7" s="20" t="s">
+      <c r="U7" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U7" s="6" t="s">
+      <c r="V7" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V7" s="20" t="s">
+      <c r="W7" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="W7" s="6" t="s">
+      <c r="X7" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
         <v>945</v>
       </c>
-      <c r="Y7" s="112" t="s">
+      <c r="Z7" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z7" s="113" t="s">
+      <c r="AA7" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA7" s="27" t="s">
+      <c r="AB7" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AC7" t="s">
         <v>948</v>
       </c>
-      <c r="AC7" s="112" t="s">
+      <c r="AD7" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD7" s="113" t="s">
+      <c r="AE7" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE7" s="25" t="s">
+      <c r="AF7" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="114">
         <v>6</v>
       </c>
@@ -50412,56 +50654,56 @@
       <c r="O8">
         <v>256</v>
       </c>
-      <c r="P8" t="s">
+      <c r="Q8" t="s">
         <v>1008</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="R8" t="s">
         <v>1016</v>
       </c>
-      <c r="R8" s="96" t="s">
+      <c r="S8" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>1017</v>
       </c>
-      <c r="T8" s="20" t="s">
+      <c r="U8" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U8" s="6" t="s">
+      <c r="V8" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V8" s="20" t="s">
+      <c r="W8" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="W8" s="6" t="s">
+      <c r="X8" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X8" t="s">
+      <c r="Y8" t="s">
         <v>945</v>
       </c>
-      <c r="Y8" s="112" t="s">
+      <c r="Z8" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z8" s="113" t="s">
+      <c r="AA8" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA8" s="27" t="s">
+      <c r="AB8" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AC8" t="s">
         <v>948</v>
       </c>
-      <c r="AC8" s="112" t="s">
+      <c r="AD8" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD8" s="113" t="s">
+      <c r="AE8" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE8" s="25" t="s">
+      <c r="AF8" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="114">
         <v>7</v>
       </c>
@@ -50507,56 +50749,56 @@
       <c r="O9">
         <v>512</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>1008</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="R9" t="s">
         <v>1016</v>
       </c>
-      <c r="R9" s="96" t="s">
+      <c r="S9" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>1037</v>
       </c>
-      <c r="T9" s="20" t="s">
+      <c r="U9" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="V9" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V9" s="20" t="s">
+      <c r="W9" s="20" t="s">
         <v>775</v>
       </c>
-      <c r="W9" s="6" t="s">
+      <c r="X9" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X9" t="s">
+      <c r="Y9" t="s">
         <v>945</v>
       </c>
-      <c r="Y9" s="112" t="s">
+      <c r="Z9" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z9" s="113" t="s">
+      <c r="AA9" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA9" s="27" t="s">
+      <c r="AB9" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>948</v>
       </c>
-      <c r="AC9" s="112" t="s">
+      <c r="AD9" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD9" s="113" t="s">
+      <c r="AE9" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE9" s="25" t="s">
+      <c r="AF9" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="101">
         <v>8</v>
       </c>
@@ -50602,56 +50844,56 @@
       <c r="O10" s="73">
         <v>256</v>
       </c>
-      <c r="P10" s="73" t="s">
+      <c r="Q10" s="73" t="s">
         <v>1009</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="R10" t="s">
         <v>1016</v>
       </c>
-      <c r="R10" s="73" t="s">
+      <c r="S10" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S10" s="73" t="s">
+      <c r="T10" s="73" t="s">
         <v>1017</v>
       </c>
-      <c r="T10" s="80" t="s">
+      <c r="U10" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="U10" s="74" t="s">
+      <c r="V10" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="V10" s="80" t="s">
+      <c r="W10" s="80" t="s">
         <v>775</v>
       </c>
-      <c r="W10" s="74" t="s">
+      <c r="X10" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="X10" s="73" t="s">
+      <c r="Y10" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="Y10" s="121" t="s">
+      <c r="Z10" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="Z10" s="124" t="s">
+      <c r="AA10" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AA10" s="85" t="s">
+      <c r="AB10" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="AB10" s="73" t="s">
+      <c r="AC10" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AC10" s="121" t="s">
+      <c r="AD10" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AD10" s="124" t="s">
+      <c r="AE10" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AE10" s="122" t="s">
+      <c r="AF10" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="114">
         <v>9</v>
       </c>
@@ -50697,56 +50939,56 @@
       <c r="O11" s="73">
         <v>512</v>
       </c>
-      <c r="P11" s="73" t="s">
+      <c r="Q11" s="73" t="s">
         <v>1009</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="R11" t="s">
         <v>1016</v>
       </c>
-      <c r="R11" s="73" t="s">
+      <c r="S11" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S11" s="73" t="s">
+      <c r="T11" s="73" t="s">
         <v>1037</v>
       </c>
-      <c r="T11" s="80" t="s">
+      <c r="U11" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="U11" s="74" t="s">
+      <c r="V11" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="V11" s="80" t="s">
+      <c r="W11" s="80" t="s">
         <v>775</v>
       </c>
-      <c r="W11" s="74" t="s">
+      <c r="X11" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="X11" s="73" t="s">
+      <c r="Y11" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="Y11" s="121" t="s">
+      <c r="Z11" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="Z11" s="124" t="s">
+      <c r="AA11" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AA11" s="85" t="s">
+      <c r="AB11" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="AB11" s="73" t="s">
+      <c r="AC11" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AC11" s="121" t="s">
+      <c r="AD11" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AD11" s="124" t="s">
+      <c r="AE11" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AE11" s="122" t="s">
+      <c r="AF11" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" s="114">
         <v>10</v>
       </c>
@@ -50792,56 +51034,57 @@
       <c r="O12" s="95">
         <v>576</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="95"/>
+      <c r="Q12" t="s">
         <v>1010</v>
       </c>
-      <c r="Q12" t="s">
+      <c r="R12" t="s">
         <v>1018</v>
       </c>
-      <c r="R12" s="96" t="s">
+      <c r="S12" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S12" t="s">
+      <c r="T12" t="s">
         <v>1019</v>
       </c>
-      <c r="T12" s="20" t="s">
+      <c r="U12" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U12" s="6" t="s">
+      <c r="V12" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V12" s="20" t="s">
+      <c r="W12" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="W12" s="6" t="s">
+      <c r="X12" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Y12" t="s">
         <v>945</v>
       </c>
-      <c r="Y12" s="112" t="s">
+      <c r="Z12" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z12" s="113" t="s">
+      <c r="AA12" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA12" s="27" t="s">
+      <c r="AB12" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB12" t="s">
+      <c r="AC12" t="s">
         <v>948</v>
       </c>
-      <c r="AC12" s="112" t="s">
+      <c r="AD12" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD12" s="113" t="s">
+      <c r="AE12" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE12" s="25" t="s">
+      <c r="AF12" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" s="114">
         <v>11</v>
       </c>
@@ -50887,56 +51130,57 @@
       <c r="O13" s="95">
         <v>576</v>
       </c>
-      <c r="P13" t="s">
+      <c r="P13" s="95"/>
+      <c r="Q13" t="s">
         <v>1010</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>1018</v>
       </c>
-      <c r="R13" s="96" t="s">
+      <c r="S13" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S13" t="s">
+      <c r="T13" t="s">
         <v>1045</v>
       </c>
-      <c r="T13" s="20" t="s">
+      <c r="U13" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U13" s="6" t="s">
+      <c r="V13" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V13" s="20" t="s">
+      <c r="W13" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="W13" s="6" t="s">
+      <c r="X13" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X13" t="s">
+      <c r="Y13" t="s">
         <v>945</v>
       </c>
-      <c r="Y13" s="112" t="s">
+      <c r="Z13" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z13" s="113" t="s">
+      <c r="AA13" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA13" s="27" t="s">
+      <c r="AB13" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB13" t="s">
+      <c r="AC13" t="s">
         <v>948</v>
       </c>
-      <c r="AC13" s="112" t="s">
+      <c r="AD13" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD13" s="113" t="s">
+      <c r="AE13" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE13" s="25" t="s">
+      <c r="AF13" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" s="101">
         <v>12</v>
       </c>
@@ -50982,56 +51226,57 @@
       <c r="O14" s="95">
         <v>576</v>
       </c>
-      <c r="P14" t="s">
+      <c r="P14" s="95"/>
+      <c r="Q14" t="s">
         <v>1011</v>
       </c>
-      <c r="Q14" t="s">
+      <c r="R14" t="s">
         <v>1018</v>
       </c>
-      <c r="R14" s="96" t="s">
+      <c r="S14" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
         <v>1019</v>
       </c>
-      <c r="T14" s="20" t="s">
+      <c r="U14" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U14" s="6" t="s">
+      <c r="V14" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V14" s="20" t="s">
+      <c r="W14" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="W14" s="6" t="s">
+      <c r="X14" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Y14" t="s">
         <v>945</v>
       </c>
-      <c r="Y14" s="112" t="s">
+      <c r="Z14" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z14" s="113" t="s">
+      <c r="AA14" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA14" s="27" t="s">
+      <c r="AB14" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB14" t="s">
+      <c r="AC14" t="s">
         <v>948</v>
       </c>
-      <c r="AC14" s="112" t="s">
+      <c r="AD14" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD14" s="113" t="s">
+      <c r="AE14" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE14" s="25" t="s">
+      <c r="AF14" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" s="114">
         <v>13</v>
       </c>
@@ -51077,56 +51322,57 @@
       <c r="O15" s="95">
         <v>576</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="95"/>
+      <c r="Q15" t="s">
         <v>1011</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="R15" t="s">
         <v>1018</v>
       </c>
-      <c r="R15" s="96" t="s">
+      <c r="S15" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>1045</v>
       </c>
-      <c r="T15" s="20" t="s">
+      <c r="U15" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U15" s="6" t="s">
+      <c r="V15" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V15" s="20" t="s">
+      <c r="W15" s="20" t="s">
         <v>776</v>
       </c>
-      <c r="W15" s="6" t="s">
+      <c r="X15" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="X15" t="s">
+      <c r="Y15" t="s">
         <v>945</v>
       </c>
-      <c r="Y15" s="112" t="s">
+      <c r="Z15" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z15" s="113" t="s">
+      <c r="AA15" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA15" s="27" t="s">
+      <c r="AB15" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB15" t="s">
+      <c r="AC15" t="s">
         <v>948</v>
       </c>
-      <c r="AC15" s="112" t="s">
+      <c r="AD15" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD15" s="113" t="s">
+      <c r="AE15" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE15" s="25" t="s">
+      <c r="AF15" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="16" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="114">
         <v>14</v>
       </c>
@@ -51172,56 +51418,56 @@
       <c r="O16" s="73">
         <v>576</v>
       </c>
-      <c r="P16" s="73" t="s">
+      <c r="Q16" s="73" t="s">
         <v>1012</v>
       </c>
-      <c r="Q16" s="73" t="s">
+      <c r="R16" s="73" t="s">
         <v>1018</v>
       </c>
-      <c r="R16" s="73" t="s">
+      <c r="S16" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S16" s="73" t="s">
+      <c r="T16" s="73" t="s">
         <v>1019</v>
       </c>
-      <c r="T16" s="80" t="s">
+      <c r="U16" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="U16" s="74" t="s">
+      <c r="V16" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="V16" s="80" t="s">
+      <c r="W16" s="80" t="s">
         <v>776</v>
       </c>
-      <c r="W16" s="74" t="s">
+      <c r="X16" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="X16" s="73" t="s">
+      <c r="Y16" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="Y16" s="121" t="s">
+      <c r="Z16" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="Z16" s="124" t="s">
+      <c r="AA16" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AA16" s="85" t="s">
+      <c r="AB16" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="AB16" s="73" t="s">
+      <c r="AC16" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AC16" s="121" t="s">
+      <c r="AD16" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AD16" s="124" t="s">
+      <c r="AE16" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AE16" s="122" t="s">
+      <c r="AF16" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="17" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="114">
         <v>15</v>
       </c>
@@ -51267,56 +51513,56 @@
       <c r="O17" s="73">
         <v>576</v>
       </c>
-      <c r="P17" s="73" t="s">
+      <c r="Q17" s="73" t="s">
         <v>1012</v>
       </c>
-      <c r="Q17" s="73" t="s">
+      <c r="R17" s="73" t="s">
         <v>1018</v>
       </c>
-      <c r="R17" s="73" t="s">
+      <c r="S17" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S17" s="73" t="s">
+      <c r="T17" s="73" t="s">
         <v>1045</v>
       </c>
-      <c r="T17" s="80" t="s">
+      <c r="U17" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="U17" s="74" t="s">
+      <c r="V17" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="V17" s="80" t="s">
+      <c r="W17" s="80" t="s">
         <v>776</v>
       </c>
-      <c r="W17" s="74" t="s">
+      <c r="X17" s="74" t="s">
         <v>944</v>
       </c>
-      <c r="X17" s="73" t="s">
+      <c r="Y17" s="73" t="s">
         <v>945</v>
       </c>
-      <c r="Y17" s="121" t="s">
+      <c r="Z17" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="Z17" s="124" t="s">
+      <c r="AA17" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AA17" s="85" t="s">
+      <c r="AB17" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="AB17" s="73" t="s">
+      <c r="AC17" s="73" t="s">
         <v>948</v>
       </c>
-      <c r="AC17" s="121" t="s">
+      <c r="AD17" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AD17" s="124" t="s">
+      <c r="AE17" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AE17" s="122" t="s">
+      <c r="AF17" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" s="101">
         <v>16</v>
       </c>
@@ -51362,56 +51608,57 @@
       <c r="O18" s="95">
         <v>576</v>
       </c>
-      <c r="P18" t="s">
+      <c r="P18" s="95"/>
+      <c r="Q18" t="s">
         <v>1013</v>
       </c>
-      <c r="Q18" t="s">
+      <c r="R18" t="s">
         <v>1020</v>
       </c>
-      <c r="R18" s="107" t="s">
+      <c r="S18" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
         <v>1021</v>
       </c>
-      <c r="T18" s="20" t="s">
+      <c r="U18" s="20" t="s">
         <v>963</v>
       </c>
-      <c r="U18" s="6" t="s">
+      <c r="V18" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V18" s="20" t="s">
+      <c r="W18" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="W18" s="6" t="s">
+      <c r="X18" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Y18" t="s">
         <v>965</v>
       </c>
-      <c r="Y18" s="112" t="s">
+      <c r="Z18" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z18" s="113" t="s">
+      <c r="AA18" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA18" s="27" t="s">
+      <c r="AB18" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AC18" t="s">
         <v>968</v>
       </c>
-      <c r="AC18" s="112" t="s">
+      <c r="AD18" s="112" t="s">
         <v>754</v>
       </c>
-      <c r="AD18" s="113" t="s">
+      <c r="AE18" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE18" s="27" t="s">
+      <c r="AF18" s="27" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" s="114">
         <v>17</v>
       </c>
@@ -51457,56 +51704,57 @@
       <c r="O19" s="95">
         <v>576</v>
       </c>
-      <c r="P19" t="s">
+      <c r="P19" s="95"/>
+      <c r="Q19" t="s">
         <v>1014</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="R19" t="s">
         <v>1020</v>
       </c>
-      <c r="R19" s="96" t="s">
+      <c r="S19" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
         <v>1021</v>
       </c>
-      <c r="T19" s="20" t="s">
+      <c r="U19" s="20" t="s">
         <v>963</v>
       </c>
-      <c r="U19" s="6" t="s">
+      <c r="V19" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V19" s="20" t="s">
+      <c r="W19" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="W19" s="6" t="s">
+      <c r="X19" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Y19" t="s">
         <v>965</v>
       </c>
-      <c r="Y19" s="112" t="s">
+      <c r="Z19" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z19" s="113" t="s">
+      <c r="AA19" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA19" s="27" t="s">
+      <c r="AB19" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AC19" t="s">
         <v>968</v>
       </c>
-      <c r="AC19" s="112" t="s">
+      <c r="AD19" s="112" t="s">
         <v>754</v>
       </c>
-      <c r="AD19" s="113" t="s">
+      <c r="AE19" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE19" s="27" t="s">
+      <c r="AF19" s="27" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" s="114">
         <v>18</v>
       </c>
@@ -51552,56 +51800,57 @@
       <c r="O20" s="95">
         <v>576</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20" s="95"/>
+      <c r="Q20" t="s">
         <v>1015</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="R20" t="s">
         <v>1020</v>
       </c>
-      <c r="R20" s="96" t="s">
+      <c r="S20" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
         <v>1021</v>
       </c>
-      <c r="T20" s="20" t="s">
+      <c r="U20" s="20" t="s">
         <v>963</v>
       </c>
-      <c r="U20" s="6" t="s">
+      <c r="V20" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V20" s="20" t="s">
+      <c r="W20" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="W20" s="6" t="s">
+      <c r="X20" s="6" t="s">
         <v>964</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Y20" t="s">
         <v>965</v>
       </c>
-      <c r="Y20" s="112" t="s">
+      <c r="Z20" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z20" s="113" t="s">
+      <c r="AA20" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA20" s="27" t="s">
+      <c r="AB20" s="27" t="s">
         <v>967</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AC20" t="s">
         <v>968</v>
       </c>
-      <c r="AC20" s="112" t="s">
+      <c r="AD20" s="112" t="s">
         <v>754</v>
       </c>
-      <c r="AD20" s="113" t="s">
+      <c r="AE20" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE20" s="27" t="s">
+      <c r="AF20" s="27" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="21" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="114">
         <v>19</v>
       </c>
@@ -51647,56 +51896,56 @@
       <c r="O21" s="107">
         <v>256</v>
       </c>
-      <c r="P21" s="107" t="s">
+      <c r="Q21" s="107" t="s">
         <v>998</v>
       </c>
-      <c r="Q21" s="107" t="s">
+      <c r="R21" s="107" t="s">
         <v>1001</v>
       </c>
-      <c r="R21" s="107" t="s">
+      <c r="S21" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="S21" s="107" t="s">
+      <c r="T21" s="107" t="s">
         <v>1002</v>
       </c>
-      <c r="T21" s="126" t="s">
+      <c r="U21" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="U21" s="101" t="s">
+      <c r="V21" s="101" t="s">
         <v>977</v>
       </c>
-      <c r="V21" s="126" t="s">
+      <c r="W21" s="126" t="s">
         <v>773</v>
       </c>
-      <c r="W21" s="101" t="s">
+      <c r="X21" s="101" t="s">
         <v>792</v>
       </c>
-      <c r="X21" s="107" t="s">
+      <c r="Y21" s="107" t="s">
         <v>965</v>
       </c>
-      <c r="Y21" s="127" t="s">
+      <c r="Z21" s="127" t="s">
         <v>747</v>
       </c>
-      <c r="Z21" s="128" t="s">
+      <c r="AA21" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="AA21" s="129" t="s">
+      <c r="AB21" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="AB21" s="107" t="s">
+      <c r="AC21" s="107" t="s">
         <v>978</v>
       </c>
-      <c r="AC21" s="127" t="s">
+      <c r="AD21" s="127" t="s">
         <v>753</v>
       </c>
-      <c r="AD21" s="128" t="s">
+      <c r="AE21" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="AE21" s="109" t="s">
+      <c r="AF21" s="109" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" s="101">
         <v>20</v>
       </c>
@@ -51742,56 +51991,56 @@
       <c r="O22">
         <v>512</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>998</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>1001</v>
       </c>
-      <c r="R22" s="96" t="s">
+      <c r="S22" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S22" t="s">
+      <c r="T22" t="s">
         <v>1006</v>
       </c>
-      <c r="T22" s="20" t="s">
+      <c r="U22" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U22" s="6" t="s">
+      <c r="V22" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V22" s="20" t="s">
+      <c r="W22" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="W22" s="6" t="s">
+      <c r="X22" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Y22" t="s">
         <v>965</v>
       </c>
-      <c r="Y22" s="112" t="s">
+      <c r="Z22" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z22" s="113" t="s">
+      <c r="AA22" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA22" s="27" t="s">
+      <c r="AB22" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AC22" t="s">
         <v>978</v>
       </c>
-      <c r="AC22" s="112" t="s">
+      <c r="AD22" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD22" s="113" t="s">
+      <c r="AE22" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE22" s="25" t="s">
+      <c r="AF22" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" s="114">
         <v>21</v>
       </c>
@@ -51837,56 +52086,56 @@
       <c r="O23">
         <v>512</v>
       </c>
-      <c r="P23" t="s">
+      <c r="Q23" t="s">
         <v>998</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="R23" t="s">
         <v>1001</v>
       </c>
-      <c r="R23" s="96" t="s">
+      <c r="S23" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S23" t="s">
+      <c r="T23" t="s">
         <v>1052</v>
       </c>
-      <c r="T23" s="20" t="s">
+      <c r="U23" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U23" s="6" t="s">
+      <c r="V23" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V23" s="20" t="s">
+      <c r="W23" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="W23" s="6" t="s">
+      <c r="X23" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X23" t="s">
+      <c r="Y23" t="s">
         <v>965</v>
       </c>
-      <c r="Y23" s="112" t="s">
+      <c r="Z23" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z23" s="113" t="s">
+      <c r="AA23" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA23" s="27" t="s">
+      <c r="AB23" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AC23" t="s">
         <v>978</v>
       </c>
-      <c r="AC23" s="112" t="s">
+      <c r="AD23" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD23" s="113" t="s">
+      <c r="AE23" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE23" s="25" t="s">
+      <c r="AF23" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" s="114">
         <v>22</v>
       </c>
@@ -51932,56 +52181,56 @@
       <c r="O24">
         <v>512</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>998</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>1001</v>
       </c>
-      <c r="R24" s="96" t="s">
+      <c r="S24" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S24" t="s">
+      <c r="T24" t="s">
         <v>1053</v>
       </c>
-      <c r="T24" s="20" t="s">
+      <c r="U24" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U24" s="6" t="s">
+      <c r="V24" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V24" s="20" t="s">
+      <c r="W24" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="W24" s="6" t="s">
+      <c r="X24" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Y24" t="s">
         <v>965</v>
       </c>
-      <c r="Y24" s="112" t="s">
+      <c r="Z24" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z24" s="113" t="s">
+      <c r="AA24" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA24" s="27" t="s">
+      <c r="AB24" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AC24" t="s">
         <v>978</v>
       </c>
-      <c r="AC24" s="112" t="s">
+      <c r="AD24" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD24" s="113" t="s">
+      <c r="AE24" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE24" s="25" t="s">
+      <c r="AF24" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" s="114">
         <v>23</v>
       </c>
@@ -52027,56 +52276,56 @@
       <c r="O25">
         <v>512</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>998</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>1001</v>
       </c>
-      <c r="R25" s="96" t="s">
+      <c r="S25" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
         <v>1072</v>
       </c>
-      <c r="T25" s="20" t="s">
+      <c r="U25" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U25" s="6" t="s">
+      <c r="V25" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V25" s="20" t="s">
+      <c r="W25" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="W25" s="6" t="s">
+      <c r="X25" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Y25" t="s">
         <v>965</v>
       </c>
-      <c r="Y25" s="112" t="s">
+      <c r="Z25" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z25" s="113" t="s">
+      <c r="AA25" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA25" s="27" t="s">
+      <c r="AB25" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AC25" t="s">
         <v>978</v>
       </c>
-      <c r="AC25" s="112" t="s">
+      <c r="AD25" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD25" s="113" t="s">
+      <c r="AE25" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE25" s="25" t="s">
+      <c r="AF25" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" s="101">
         <v>24</v>
       </c>
@@ -52122,56 +52371,56 @@
       <c r="O26">
         <v>512</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>998</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>1001</v>
       </c>
-      <c r="R26" s="96" t="s">
+      <c r="S26" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>1073</v>
       </c>
-      <c r="T26" s="20" t="s">
+      <c r="U26" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U26" s="6" t="s">
+      <c r="V26" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V26" s="20" t="s">
+      <c r="W26" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="W26" s="6" t="s">
+      <c r="X26" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Y26" t="s">
         <v>965</v>
       </c>
-      <c r="Y26" s="112" t="s">
+      <c r="Z26" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z26" s="113" t="s">
+      <c r="AA26" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA26" s="27" t="s">
+      <c r="AB26" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AC26" t="s">
         <v>978</v>
       </c>
-      <c r="AC26" s="112" t="s">
+      <c r="AD26" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD26" s="113" t="s">
+      <c r="AE26" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE26" s="25" t="s">
+      <c r="AF26" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" s="114">
         <v>25</v>
       </c>
@@ -52217,56 +52466,56 @@
       <c r="O27">
         <v>512</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>998</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>1001</v>
       </c>
-      <c r="R27" s="96" t="s">
+      <c r="S27" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S27" t="s">
+      <c r="T27" t="s">
         <v>1081</v>
       </c>
-      <c r="T27" s="20" t="s">
+      <c r="U27" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U27" s="6" t="s">
+      <c r="V27" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V27" s="20" t="s">
+      <c r="W27" s="20" t="s">
         <v>773</v>
       </c>
-      <c r="W27" s="6" t="s">
+      <c r="X27" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Y27" t="s">
         <v>965</v>
       </c>
-      <c r="Y27" s="112" t="s">
+      <c r="Z27" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z27" s="113" t="s">
+      <c r="AA27" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA27" s="27" t="s">
+      <c r="AB27" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AC27" t="s">
         <v>978</v>
       </c>
-      <c r="AC27" s="112" t="s">
+      <c r="AD27" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD27" s="113" t="s">
+      <c r="AE27" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE27" s="25" t="s">
+      <c r="AF27" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" s="114">
         <v>26</v>
       </c>
@@ -52312,56 +52561,56 @@
       <c r="O28">
         <v>256</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>999</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>1001</v>
       </c>
-      <c r="R28" s="96" t="s">
+      <c r="S28" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S28" t="s">
+      <c r="T28" t="s">
         <v>1002</v>
       </c>
-      <c r="T28" s="20" t="s">
+      <c r="U28" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U28" s="6" t="s">
+      <c r="V28" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V28" s="28" t="s">
+      <c r="W28" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W28" s="6" t="s">
+      <c r="X28" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X28" t="s">
+      <c r="Y28" t="s">
         <v>965</v>
       </c>
-      <c r="Y28" s="112" t="s">
+      <c r="Z28" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z28" s="113" t="s">
+      <c r="AA28" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA28" s="27" t="s">
+      <c r="AB28" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AC28" t="s">
         <v>978</v>
       </c>
-      <c r="AC28" s="112" t="s">
+      <c r="AD28" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD28" s="113" t="s">
+      <c r="AE28" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE28" s="25" t="s">
+      <c r="AF28" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" s="114">
         <v>27</v>
       </c>
@@ -52407,56 +52656,56 @@
       <c r="O29">
         <v>512</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>999</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>1001</v>
       </c>
-      <c r="R29" s="96" t="s">
+      <c r="S29" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S29" t="s">
+      <c r="T29" t="s">
         <v>1006</v>
       </c>
-      <c r="T29" s="20" t="s">
+      <c r="U29" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U29" s="6" t="s">
+      <c r="V29" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V29" s="28" t="s">
+      <c r="W29" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W29" s="6" t="s">
+      <c r="X29" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Y29" t="s">
         <v>965</v>
       </c>
-      <c r="Y29" s="112" t="s">
+      <c r="Z29" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z29" s="113" t="s">
+      <c r="AA29" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA29" s="27" t="s">
+      <c r="AB29" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
         <v>978</v>
       </c>
-      <c r="AC29" s="112" t="s">
+      <c r="AD29" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD29" s="113" t="s">
+      <c r="AE29" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE29" s="25" t="s">
+      <c r="AF29" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" s="101">
         <v>28</v>
       </c>
@@ -52502,56 +52751,56 @@
       <c r="O30">
         <v>512</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>999</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>1001</v>
       </c>
-      <c r="R30" s="96" t="s">
+      <c r="S30" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>1052</v>
       </c>
-      <c r="T30" s="20" t="s">
+      <c r="U30" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U30" s="6" t="s">
+      <c r="V30" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V30" s="28" t="s">
+      <c r="W30" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W30" s="6" t="s">
+      <c r="X30" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X30" t="s">
+      <c r="Y30" t="s">
         <v>965</v>
       </c>
-      <c r="Y30" s="112" t="s">
+      <c r="Z30" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z30" s="113" t="s">
+      <c r="AA30" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA30" s="27" t="s">
+      <c r="AB30" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
         <v>978</v>
       </c>
-      <c r="AC30" s="112" t="s">
+      <c r="AD30" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD30" s="113" t="s">
+      <c r="AE30" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE30" s="25" t="s">
+      <c r="AF30" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" s="114">
         <v>29</v>
       </c>
@@ -52597,56 +52846,56 @@
       <c r="O31">
         <v>512</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>999</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>1001</v>
       </c>
-      <c r="R31" s="96" t="s">
+      <c r="S31" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S31" t="s">
+      <c r="T31" t="s">
         <v>1053</v>
       </c>
-      <c r="T31" s="20" t="s">
+      <c r="U31" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U31" s="6" t="s">
+      <c r="V31" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V31" s="28" t="s">
+      <c r="W31" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W31" s="6" t="s">
+      <c r="X31" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Y31" t="s">
         <v>965</v>
       </c>
-      <c r="Y31" s="112" t="s">
+      <c r="Z31" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z31" s="113" t="s">
+      <c r="AA31" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA31" s="27" t="s">
+      <c r="AB31" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AC31" t="s">
         <v>978</v>
       </c>
-      <c r="AC31" s="112" t="s">
+      <c r="AD31" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD31" s="113" t="s">
+      <c r="AE31" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE31" s="25" t="s">
+      <c r="AF31" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" s="114">
         <v>30</v>
       </c>
@@ -52692,56 +52941,56 @@
       <c r="O32">
         <v>512</v>
       </c>
-      <c r="P32" t="s">
+      <c r="Q32" t="s">
         <v>999</v>
       </c>
-      <c r="Q32" t="s">
+      <c r="R32" t="s">
         <v>1001</v>
       </c>
-      <c r="R32" s="96" t="s">
+      <c r="S32" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S32" t="s">
+      <c r="T32" t="s">
         <v>1072</v>
       </c>
-      <c r="T32" s="20" t="s">
+      <c r="U32" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U32" s="6" t="s">
+      <c r="V32" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V32" s="28" t="s">
+      <c r="W32" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W32" s="6" t="s">
+      <c r="X32" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X32" t="s">
+      <c r="Y32" t="s">
         <v>965</v>
       </c>
-      <c r="Y32" s="112" t="s">
+      <c r="Z32" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z32" s="113" t="s">
+      <c r="AA32" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA32" s="27" t="s">
+      <c r="AB32" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>978</v>
       </c>
-      <c r="AC32" s="112" t="s">
+      <c r="AD32" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD32" s="113" t="s">
+      <c r="AE32" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE32" s="25" t="s">
+      <c r="AF32" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="114">
         <v>31</v>
       </c>
@@ -52787,56 +53036,56 @@
       <c r="O33">
         <v>512</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>999</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>1001</v>
       </c>
-      <c r="R33" s="96" t="s">
+      <c r="S33" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S33" t="s">
+      <c r="T33" t="s">
         <v>1073</v>
       </c>
-      <c r="T33" s="20" t="s">
+      <c r="U33" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U33" s="6" t="s">
+      <c r="V33" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V33" s="28" t="s">
+      <c r="W33" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W33" s="6" t="s">
+      <c r="X33" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X33" t="s">
+      <c r="Y33" t="s">
         <v>965</v>
       </c>
-      <c r="Y33" s="112" t="s">
+      <c r="Z33" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z33" s="113" t="s">
+      <c r="AA33" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA33" s="27" t="s">
+      <c r="AB33" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB33" t="s">
+      <c r="AC33" t="s">
         <v>978</v>
       </c>
-      <c r="AC33" s="112" t="s">
+      <c r="AD33" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD33" s="113" t="s">
+      <c r="AE33" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE33" s="25" t="s">
+      <c r="AF33" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" s="101">
         <v>32</v>
       </c>
@@ -52882,56 +53131,56 @@
       <c r="O34">
         <v>512</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>999</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>1001</v>
       </c>
-      <c r="R34" s="96" t="s">
+      <c r="S34" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S34" t="s">
+      <c r="T34" t="s">
         <v>1081</v>
       </c>
-      <c r="T34" s="20" t="s">
+      <c r="U34" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U34" s="6" t="s">
+      <c r="V34" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V34" s="28" t="s">
+      <c r="W34" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W34" s="6" t="s">
+      <c r="X34" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X34" t="s">
+      <c r="Y34" t="s">
         <v>965</v>
       </c>
-      <c r="Y34" s="112" t="s">
+      <c r="Z34" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z34" s="113" t="s">
+      <c r="AA34" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA34" s="27" t="s">
+      <c r="AB34" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB34" t="s">
+      <c r="AC34" t="s">
         <v>978</v>
       </c>
-      <c r="AC34" s="112" t="s">
+      <c r="AD34" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD34" s="113" t="s">
+      <c r="AE34" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE34" s="25" t="s">
+      <c r="AF34" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" s="114">
         <v>33</v>
       </c>
@@ -52977,56 +53226,56 @@
       <c r="O35">
         <v>256</v>
       </c>
-      <c r="P35" t="s">
+      <c r="Q35" t="s">
         <v>1000</v>
       </c>
-      <c r="Q35" t="s">
+      <c r="R35" t="s">
         <v>1001</v>
       </c>
-      <c r="R35" s="96" t="s">
+      <c r="S35" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S35" t="s">
+      <c r="T35" t="s">
         <v>1002</v>
       </c>
-      <c r="T35" s="20" t="s">
+      <c r="U35" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U35" s="6" t="s">
+      <c r="V35" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V35" s="28" t="s">
+      <c r="W35" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W35" s="6" t="s">
+      <c r="X35" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X35" t="s">
+      <c r="Y35" t="s">
         <v>965</v>
       </c>
-      <c r="Y35" s="112" t="s">
+      <c r="Z35" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z35" s="113" t="s">
+      <c r="AA35" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA35" s="27" t="s">
+      <c r="AB35" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB35" t="s">
+      <c r="AC35" t="s">
         <v>978</v>
       </c>
-      <c r="AC35" s="112" t="s">
+      <c r="AD35" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD35" s="113" t="s">
+      <c r="AE35" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE35" s="25" t="s">
+      <c r="AF35" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" s="114">
         <v>34</v>
       </c>
@@ -53072,56 +53321,56 @@
       <c r="O36">
         <v>512</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>1000</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>1001</v>
       </c>
-      <c r="R36" s="96" t="s">
+      <c r="S36" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S36" t="s">
+      <c r="T36" t="s">
         <v>1006</v>
       </c>
-      <c r="T36" s="20" t="s">
+      <c r="U36" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U36" s="6" t="s">
+      <c r="V36" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V36" s="28" t="s">
+      <c r="W36" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W36" s="6" t="s">
+      <c r="X36" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X36" t="s">
+      <c r="Y36" t="s">
         <v>965</v>
       </c>
-      <c r="Y36" s="112" t="s">
+      <c r="Z36" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z36" s="113" t="s">
+      <c r="AA36" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA36" s="27" t="s">
+      <c r="AB36" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB36" t="s">
+      <c r="AC36" t="s">
         <v>978</v>
       </c>
-      <c r="AC36" s="112" t="s">
+      <c r="AD36" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD36" s="113" t="s">
+      <c r="AE36" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE36" s="25" t="s">
+      <c r="AF36" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" s="114">
         <v>35</v>
       </c>
@@ -53167,56 +53416,56 @@
       <c r="O37">
         <v>512</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>1000</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>1001</v>
       </c>
-      <c r="R37" s="96" t="s">
+      <c r="S37" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S37" t="s">
+      <c r="T37" t="s">
         <v>1052</v>
       </c>
-      <c r="T37" s="20" t="s">
+      <c r="U37" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U37" s="6" t="s">
+      <c r="V37" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V37" s="28" t="s">
+      <c r="W37" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W37" s="6" t="s">
+      <c r="X37" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X37" t="s">
+      <c r="Y37" t="s">
         <v>965</v>
       </c>
-      <c r="Y37" s="112" t="s">
+      <c r="Z37" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z37" s="113" t="s">
+      <c r="AA37" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA37" s="27" t="s">
+      <c r="AB37" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB37" t="s">
+      <c r="AC37" t="s">
         <v>978</v>
       </c>
-      <c r="AC37" s="112" t="s">
+      <c r="AD37" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD37" s="113" t="s">
+      <c r="AE37" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE37" s="25" t="s">
+      <c r="AF37" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" s="101">
         <v>36</v>
       </c>
@@ -53262,56 +53511,56 @@
       <c r="O38">
         <v>512</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>1000</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>1001</v>
       </c>
-      <c r="R38" s="96" t="s">
+      <c r="S38" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S38" t="s">
+      <c r="T38" t="s">
         <v>1053</v>
       </c>
-      <c r="T38" s="20" t="s">
+      <c r="U38" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U38" s="6" t="s">
+      <c r="V38" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V38" s="28" t="s">
+      <c r="W38" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W38" s="6" t="s">
+      <c r="X38" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X38" t="s">
+      <c r="Y38" t="s">
         <v>965</v>
       </c>
-      <c r="Y38" s="112" t="s">
+      <c r="Z38" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z38" s="113" t="s">
+      <c r="AA38" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA38" s="27" t="s">
+      <c r="AB38" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB38" t="s">
+      <c r="AC38" t="s">
         <v>978</v>
       </c>
-      <c r="AC38" s="112" t="s">
+      <c r="AD38" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD38" s="113" t="s">
+      <c r="AE38" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE38" s="25" t="s">
+      <c r="AF38" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" s="114">
         <v>37</v>
       </c>
@@ -53357,56 +53606,56 @@
       <c r="O39">
         <v>512</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>1000</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>1001</v>
       </c>
-      <c r="R39" s="96" t="s">
+      <c r="S39" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S39" t="s">
+      <c r="T39" t="s">
         <v>1072</v>
       </c>
-      <c r="T39" s="20" t="s">
+      <c r="U39" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U39" s="6" t="s">
+      <c r="V39" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V39" s="28" t="s">
+      <c r="W39" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W39" s="6" t="s">
+      <c r="X39" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X39" t="s">
+      <c r="Y39" t="s">
         <v>965</v>
       </c>
-      <c r="Y39" s="112" t="s">
+      <c r="Z39" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z39" s="113" t="s">
+      <c r="AA39" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA39" s="27" t="s">
+      <c r="AB39" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB39" t="s">
+      <c r="AC39" t="s">
         <v>978</v>
       </c>
-      <c r="AC39" s="112" t="s">
+      <c r="AD39" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD39" s="113" t="s">
+      <c r="AE39" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE39" s="25" t="s">
+      <c r="AF39" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40" s="114">
         <v>38</v>
       </c>
@@ -53452,56 +53701,56 @@
       <c r="O40">
         <v>512</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>1000</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>1001</v>
       </c>
-      <c r="R40" s="96" t="s">
+      <c r="S40" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S40" t="s">
+      <c r="T40" t="s">
         <v>1073</v>
       </c>
-      <c r="T40" s="20" t="s">
+      <c r="U40" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U40" s="6" t="s">
+      <c r="V40" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V40" s="28" t="s">
+      <c r="W40" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W40" s="6" t="s">
+      <c r="X40" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X40" t="s">
+      <c r="Y40" t="s">
         <v>965</v>
       </c>
-      <c r="Y40" s="112" t="s">
+      <c r="Z40" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z40" s="113" t="s">
+      <c r="AA40" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA40" s="27" t="s">
+      <c r="AB40" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB40" t="s">
+      <c r="AC40" t="s">
         <v>978</v>
       </c>
-      <c r="AC40" s="112" t="s">
+      <c r="AD40" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD40" s="113" t="s">
+      <c r="AE40" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE40" s="25" t="s">
+      <c r="AF40" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41" s="114">
         <v>39</v>
       </c>
@@ -53547,56 +53796,56 @@
       <c r="O41">
         <v>512</v>
       </c>
-      <c r="P41" t="s">
+      <c r="Q41" t="s">
         <v>1000</v>
       </c>
-      <c r="Q41" t="s">
+      <c r="R41" t="s">
         <v>1001</v>
       </c>
-      <c r="R41" s="96" t="s">
+      <c r="S41" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S41" t="s">
+      <c r="T41" t="s">
         <v>1081</v>
       </c>
-      <c r="T41" s="20" t="s">
+      <c r="U41" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U41" s="6" t="s">
+      <c r="V41" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="V41" s="28" t="s">
+      <c r="W41" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="W41" s="6" t="s">
+      <c r="X41" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X41" t="s">
+      <c r="Y41" t="s">
         <v>965</v>
       </c>
-      <c r="Y41" s="112" t="s">
+      <c r="Z41" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z41" s="113" t="s">
+      <c r="AA41" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA41" s="27" t="s">
+      <c r="AB41" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB41" t="s">
+      <c r="AC41" t="s">
         <v>978</v>
       </c>
-      <c r="AC41" s="112" t="s">
+      <c r="AD41" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD41" s="113" t="s">
+      <c r="AE41" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE41" s="25" t="s">
+      <c r="AF41" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="42" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="101">
         <v>40</v>
       </c>
@@ -53642,56 +53891,56 @@
       <c r="O42" s="107">
         <v>256</v>
       </c>
-      <c r="P42" s="107" t="s">
+      <c r="Q42" s="107" t="s">
         <v>1022</v>
       </c>
-      <c r="Q42" s="107" t="s">
+      <c r="R42" s="107" t="s">
         <v>1025</v>
       </c>
-      <c r="R42" s="107" t="s">
+      <c r="S42" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="S42" s="107" t="s">
+      <c r="T42" s="107" t="s">
         <v>1026</v>
       </c>
-      <c r="T42" s="126" t="s">
+      <c r="U42" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="U42" s="101" t="s">
+      <c r="V42" s="101" t="s">
         <v>943</v>
       </c>
-      <c r="V42" s="126" t="s">
+      <c r="W42" s="126" t="s">
         <v>789</v>
       </c>
-      <c r="W42" s="101" t="s">
+      <c r="X42" s="101" t="s">
         <v>792</v>
       </c>
-      <c r="X42" s="107" t="s">
+      <c r="Y42" s="107" t="s">
         <v>965</v>
       </c>
-      <c r="Y42" s="127" t="s">
+      <c r="Z42" s="127" t="s">
         <v>747</v>
       </c>
-      <c r="Z42" s="128" t="s">
+      <c r="AA42" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="AA42" s="129" t="s">
+      <c r="AB42" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="AB42" s="107" t="s">
+      <c r="AC42" s="107" t="s">
         <v>978</v>
       </c>
-      <c r="AC42" s="127" t="s">
+      <c r="AD42" s="127" t="s">
         <v>753</v>
       </c>
-      <c r="AD42" s="128" t="s">
+      <c r="AE42" s="128" t="s">
         <v>966</v>
       </c>
-      <c r="AE42" s="109" t="s">
+      <c r="AF42" s="109" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43" s="114">
         <v>41</v>
       </c>
@@ -53737,56 +53986,57 @@
       <c r="O43" s="95">
         <v>256</v>
       </c>
-      <c r="P43" t="s">
+      <c r="P43" s="95"/>
+      <c r="Q43" t="s">
         <v>1023</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>1025</v>
       </c>
-      <c r="R43" s="96" t="s">
+      <c r="S43" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S43" t="s">
+      <c r="T43" t="s">
         <v>1026</v>
       </c>
-      <c r="T43" s="20" t="s">
+      <c r="U43" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U43" s="6" t="s">
+      <c r="V43" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V43" s="20" t="s">
+      <c r="W43" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="W43" s="6" t="s">
+      <c r="X43" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X43" t="s">
+      <c r="Y43" t="s">
         <v>965</v>
       </c>
-      <c r="Y43" s="112" t="s">
+      <c r="Z43" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z43" s="113" t="s">
+      <c r="AA43" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA43" s="27" t="s">
+      <c r="AB43" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB43" t="s">
+      <c r="AC43" t="s">
         <v>978</v>
       </c>
-      <c r="AC43" s="112" t="s">
+      <c r="AD43" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD43" s="113" t="s">
+      <c r="AE43" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE43" s="25" t="s">
+      <c r="AF43" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44" s="114">
         <v>42</v>
       </c>
@@ -53832,56 +54082,57 @@
       <c r="O44" s="95">
         <v>256</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44" s="95"/>
+      <c r="Q44" t="s">
         <v>1024</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>1025</v>
       </c>
-      <c r="R44" s="96" t="s">
+      <c r="S44" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S44" t="s">
+      <c r="T44" t="s">
         <v>1026</v>
       </c>
-      <c r="T44" s="20" t="s">
+      <c r="U44" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="U44" s="6" t="s">
+      <c r="V44" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="V44" s="20" t="s">
+      <c r="W44" s="20" t="s">
         <v>789</v>
       </c>
-      <c r="W44" s="6" t="s">
+      <c r="X44" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="X44" t="s">
+      <c r="Y44" t="s">
         <v>965</v>
       </c>
-      <c r="Y44" s="112" t="s">
+      <c r="Z44" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z44" s="113" t="s">
+      <c r="AA44" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AA44" s="27" t="s">
+      <c r="AB44" s="27" t="s">
         <v>947</v>
       </c>
-      <c r="AB44" t="s">
+      <c r="AC44" t="s">
         <v>978</v>
       </c>
-      <c r="AC44" s="112" t="s">
+      <c r="AD44" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD44" s="113" t="s">
+      <c r="AE44" s="113" t="s">
         <v>966</v>
       </c>
-      <c r="AE44" s="25" t="s">
+      <c r="AF44" s="25" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="45" spans="1:31" s="107" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:32" s="107" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="114">
         <v>43</v>
       </c>
@@ -53927,56 +54178,56 @@
       <c r="O45" s="107">
         <v>256</v>
       </c>
-      <c r="P45" s="107" t="s">
+      <c r="Q45" s="107" t="s">
         <v>1027</v>
       </c>
-      <c r="Q45" s="107" t="s">
+      <c r="R45" s="107" t="s">
         <v>1030</v>
       </c>
-      <c r="R45" s="107" t="s">
+      <c r="S45" s="107" t="s">
         <v>914</v>
       </c>
-      <c r="S45" s="107" t="s">
+      <c r="T45" s="107" t="s">
         <v>1031</v>
       </c>
-      <c r="T45" s="126" t="s">
+      <c r="U45" s="126" t="s">
         <v>92</v>
       </c>
-      <c r="U45" s="101" t="s">
+      <c r="V45" s="101" t="s">
         <v>943</v>
       </c>
-      <c r="V45" s="126" t="s">
+      <c r="W45" s="126" t="s">
         <v>772</v>
       </c>
-      <c r="W45" s="101" t="s">
+      <c r="X45" s="101" t="s">
         <v>989</v>
       </c>
-      <c r="X45" s="107" t="s">
+      <c r="Y45" s="107" t="s">
         <v>990</v>
       </c>
-      <c r="Y45" s="127" t="s">
+      <c r="Z45" s="127" t="s">
         <v>747</v>
       </c>
-      <c r="Z45" s="128" t="s">
+      <c r="AA45" s="128" t="s">
         <v>946</v>
       </c>
-      <c r="AA45" s="129" t="s">
+      <c r="AB45" s="129" t="s">
         <v>947</v>
       </c>
-      <c r="AB45" s="107" t="s">
+      <c r="AC45" s="107" t="s">
         <v>991</v>
       </c>
-      <c r="AC45" s="127" t="s">
+      <c r="AD45" s="127" t="s">
         <v>753</v>
       </c>
-      <c r="AD45" s="128" t="s">
+      <c r="AE45" s="128" t="s">
         <v>946</v>
       </c>
-      <c r="AE45" s="109" t="s">
+      <c r="AF45" s="109" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="46" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="101">
         <v>44</v>
       </c>
@@ -54022,56 +54273,56 @@
       <c r="O46" s="96">
         <v>256</v>
       </c>
-      <c r="P46" s="96" t="s">
+      <c r="Q46" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="Q46" s="96" t="s">
+      <c r="R46" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R46" s="96" t="s">
+      <c r="S46" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S46" s="96" t="s">
+      <c r="T46" s="96" t="s">
         <v>1041</v>
       </c>
-      <c r="T46" s="133" t="s">
+      <c r="U46" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U46" s="114" t="s">
+      <c r="V46" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V46" s="133" t="s">
+      <c r="W46" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W46" s="114" t="s">
+      <c r="X46" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X46" s="96" t="s">
+      <c r="Y46" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y46" s="134" t="s">
+      <c r="Z46" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z46" s="135" t="s">
+      <c r="AA46" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA46" s="133" t="s">
+      <c r="AB46" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB46" s="96" t="s">
+      <c r="AC46" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC46" s="134" t="s">
+      <c r="AD46" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD46" s="135" t="s">
+      <c r="AE46" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE46" s="115" t="s">
+      <c r="AF46" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="47" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="114">
         <v>45</v>
       </c>
@@ -54117,56 +54368,56 @@
       <c r="O47" s="96">
         <v>256</v>
       </c>
-      <c r="P47" s="96" t="s">
+      <c r="Q47" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="Q47" s="96" t="s">
+      <c r="R47" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R47" s="96" t="s">
+      <c r="S47" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S47" s="96" t="s">
+      <c r="T47" s="96" t="s">
         <v>1060</v>
       </c>
-      <c r="T47" s="133" t="s">
+      <c r="U47" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U47" s="114" t="s">
+      <c r="V47" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V47" s="133" t="s">
+      <c r="W47" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W47" s="114" t="s">
+      <c r="X47" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X47" s="96" t="s">
+      <c r="Y47" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y47" s="134" t="s">
+      <c r="Z47" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z47" s="135" t="s">
+      <c r="AA47" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA47" s="133" t="s">
+      <c r="AB47" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB47" s="96" t="s">
+      <c r="AC47" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC47" s="134" t="s">
+      <c r="AD47" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD47" s="135" t="s">
+      <c r="AE47" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE47" s="115" t="s">
+      <c r="AF47" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="48" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="114">
         <v>46</v>
       </c>
@@ -54212,56 +54463,56 @@
       <c r="O48" s="96">
         <v>256</v>
       </c>
-      <c r="P48" s="96" t="s">
+      <c r="Q48" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="Q48" s="96" t="s">
+      <c r="R48" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R48" s="96" t="s">
+      <c r="S48" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S48" s="96" t="s">
+      <c r="T48" s="96" t="s">
         <v>1061</v>
       </c>
-      <c r="T48" s="133" t="s">
+      <c r="U48" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U48" s="114" t="s">
+      <c r="V48" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V48" s="133" t="s">
+      <c r="W48" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W48" s="114" t="s">
+      <c r="X48" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X48" s="96" t="s">
+      <c r="Y48" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y48" s="134" t="s">
+      <c r="Z48" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z48" s="135" t="s">
+      <c r="AA48" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA48" s="133" t="s">
+      <c r="AB48" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB48" s="96" t="s">
+      <c r="AC48" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC48" s="134" t="s">
+      <c r="AD48" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD48" s="135" t="s">
+      <c r="AE48" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE48" s="115" t="s">
+      <c r="AF48" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="49" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="114">
         <v>47</v>
       </c>
@@ -54307,56 +54558,56 @@
       <c r="O49" s="96">
         <v>256</v>
       </c>
-      <c r="P49" s="96" t="s">
+      <c r="Q49" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="Q49" s="96" t="s">
+      <c r="R49" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R49" s="96" t="s">
+      <c r="S49" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S49" s="96" t="s">
+      <c r="T49" s="96" t="s">
         <v>1064</v>
       </c>
-      <c r="T49" s="133" t="s">
+      <c r="U49" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U49" s="114" t="s">
+      <c r="V49" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V49" s="133" t="s">
+      <c r="W49" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W49" s="114" t="s">
+      <c r="X49" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X49" s="96" t="s">
+      <c r="Y49" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y49" s="134" t="s">
+      <c r="Z49" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z49" s="135" t="s">
+      <c r="AA49" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA49" s="133" t="s">
+      <c r="AB49" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB49" s="96" t="s">
+      <c r="AC49" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC49" s="134" t="s">
+      <c r="AD49" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD49" s="135" t="s">
+      <c r="AE49" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE49" s="115" t="s">
+      <c r="AF49" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="50" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="101">
         <v>48</v>
       </c>
@@ -54402,56 +54653,56 @@
       <c r="O50" s="96">
         <v>256</v>
       </c>
-      <c r="P50" s="96" t="s">
+      <c r="Q50" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="Q50" s="96" t="s">
+      <c r="R50" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R50" s="96" t="s">
+      <c r="S50" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S50" s="96" t="s">
+      <c r="T50" s="96" t="s">
         <v>1065</v>
       </c>
-      <c r="T50" s="133" t="s">
+      <c r="U50" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U50" s="114" t="s">
+      <c r="V50" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V50" s="133" t="s">
+      <c r="W50" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W50" s="114" t="s">
+      <c r="X50" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X50" s="96" t="s">
+      <c r="Y50" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y50" s="134" t="s">
+      <c r="Z50" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z50" s="135" t="s">
+      <c r="AA50" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA50" s="133" t="s">
+      <c r="AB50" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB50" s="96" t="s">
+      <c r="AC50" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC50" s="134" t="s">
+      <c r="AD50" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD50" s="135" t="s">
+      <c r="AE50" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE50" s="115" t="s">
+      <c r="AF50" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="51" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="114">
         <v>49</v>
       </c>
@@ -54497,56 +54748,56 @@
       <c r="O51" s="96">
         <v>256</v>
       </c>
-      <c r="P51" s="96" t="s">
+      <c r="Q51" s="96" t="s">
         <v>1027</v>
       </c>
-      <c r="Q51" s="96" t="s">
+      <c r="R51" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R51" s="96" t="s">
+      <c r="S51" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S51" s="96" t="s">
+      <c r="T51" s="96" t="s">
         <v>1079</v>
       </c>
-      <c r="T51" s="133" t="s">
+      <c r="U51" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U51" s="114" t="s">
+      <c r="V51" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V51" s="133" t="s">
+      <c r="W51" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W51" s="114" t="s">
+      <c r="X51" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X51" s="96" t="s">
+      <c r="Y51" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y51" s="134" t="s">
+      <c r="Z51" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z51" s="135" t="s">
+      <c r="AA51" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA51" s="133" t="s">
+      <c r="AB51" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB51" s="96" t="s">
+      <c r="AC51" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC51" s="134" t="s">
+      <c r="AD51" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD51" s="135" t="s">
+      <c r="AE51" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE51" s="115" t="s">
+      <c r="AF51" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="52" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="114">
         <v>50</v>
       </c>
@@ -54592,56 +54843,57 @@
       <c r="O52" s="95">
         <v>256</v>
       </c>
-      <c r="P52" s="96" t="s">
+      <c r="P52" s="95"/>
+      <c r="Q52" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="Q52" s="96" t="s">
+      <c r="R52" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R52" s="96" t="s">
+      <c r="S52" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S52" s="96" t="s">
+      <c r="T52" s="96" t="s">
         <v>1031</v>
       </c>
-      <c r="T52" s="133" t="s">
+      <c r="U52" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U52" s="114" t="s">
+      <c r="V52" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V52" s="133" t="s">
+      <c r="W52" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W52" s="114" t="s">
+      <c r="X52" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X52" s="96" t="s">
+      <c r="Y52" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y52" s="134" t="s">
+      <c r="Z52" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z52" s="135" t="s">
+      <c r="AA52" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA52" s="133" t="s">
+      <c r="AB52" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB52" s="96" t="s">
+      <c r="AC52" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC52" s="134" t="s">
+      <c r="AD52" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD52" s="135" t="s">
+      <c r="AE52" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE52" s="115" t="s">
+      <c r="AF52" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="53" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="114">
         <v>51</v>
       </c>
@@ -54687,56 +54939,57 @@
       <c r="O53" s="95">
         <v>256</v>
       </c>
-      <c r="P53" s="96" t="s">
+      <c r="P53" s="95"/>
+      <c r="Q53" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="Q53" s="96" t="s">
+      <c r="R53" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R53" s="96" t="s">
+      <c r="S53" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S53" s="96" t="s">
+      <c r="T53" s="96" t="s">
         <v>1041</v>
       </c>
-      <c r="T53" s="133" t="s">
+      <c r="U53" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U53" s="114" t="s">
+      <c r="V53" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V53" s="133" t="s">
+      <c r="W53" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W53" s="114" t="s">
+      <c r="X53" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X53" s="96" t="s">
+      <c r="Y53" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y53" s="134" t="s">
+      <c r="Z53" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z53" s="135" t="s">
+      <c r="AA53" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA53" s="133" t="s">
+      <c r="AB53" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB53" s="96" t="s">
+      <c r="AC53" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC53" s="134" t="s">
+      <c r="AD53" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD53" s="135" t="s">
+      <c r="AE53" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE53" s="115" t="s">
+      <c r="AF53" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="54" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="101">
         <v>52</v>
       </c>
@@ -54782,56 +55035,57 @@
       <c r="O54" s="95">
         <v>256</v>
       </c>
-      <c r="P54" s="96" t="s">
+      <c r="P54" s="95"/>
+      <c r="Q54" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="Q54" s="96" t="s">
+      <c r="R54" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R54" s="96" t="s">
+      <c r="S54" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S54" s="96" t="s">
+      <c r="T54" s="96" t="s">
         <v>1060</v>
       </c>
-      <c r="T54" s="133" t="s">
+      <c r="U54" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U54" s="114" t="s">
+      <c r="V54" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V54" s="133" t="s">
+      <c r="W54" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W54" s="114" t="s">
+      <c r="X54" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X54" s="96" t="s">
+      <c r="Y54" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y54" s="134" t="s">
+      <c r="Z54" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z54" s="135" t="s">
+      <c r="AA54" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA54" s="133" t="s">
+      <c r="AB54" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB54" s="96" t="s">
+      <c r="AC54" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC54" s="134" t="s">
+      <c r="AD54" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD54" s="135" t="s">
+      <c r="AE54" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE54" s="115" t="s">
+      <c r="AF54" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="55" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="114">
         <v>53</v>
       </c>
@@ -54877,56 +55131,57 @@
       <c r="O55" s="95">
         <v>256</v>
       </c>
-      <c r="P55" s="96" t="s">
+      <c r="P55" s="95"/>
+      <c r="Q55" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="Q55" s="96" t="s">
+      <c r="R55" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R55" s="96" t="s">
+      <c r="S55" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S55" s="96" t="s">
+      <c r="T55" s="96" t="s">
         <v>1061</v>
       </c>
-      <c r="T55" s="133" t="s">
+      <c r="U55" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U55" s="114" t="s">
+      <c r="V55" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V55" s="133" t="s">
+      <c r="W55" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W55" s="114" t="s">
+      <c r="X55" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X55" s="96" t="s">
+      <c r="Y55" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y55" s="134" t="s">
+      <c r="Z55" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z55" s="135" t="s">
+      <c r="AA55" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA55" s="133" t="s">
+      <c r="AB55" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB55" s="96" t="s">
+      <c r="AC55" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC55" s="134" t="s">
+      <c r="AD55" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD55" s="135" t="s">
+      <c r="AE55" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE55" s="115" t="s">
+      <c r="AF55" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="56" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="114">
         <v>54</v>
       </c>
@@ -54972,56 +55227,57 @@
       <c r="O56" s="95">
         <v>256</v>
       </c>
-      <c r="P56" s="96" t="s">
+      <c r="P56" s="95"/>
+      <c r="Q56" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="Q56" s="96" t="s">
+      <c r="R56" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R56" s="96" t="s">
+      <c r="S56" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S56" s="96" t="s">
+      <c r="T56" s="96" t="s">
         <v>1064</v>
       </c>
-      <c r="T56" s="133" t="s">
+      <c r="U56" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U56" s="114" t="s">
+      <c r="V56" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V56" s="133" t="s">
+      <c r="W56" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W56" s="114" t="s">
+      <c r="X56" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X56" s="96" t="s">
+      <c r="Y56" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y56" s="134" t="s">
+      <c r="Z56" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z56" s="135" t="s">
+      <c r="AA56" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA56" s="133" t="s">
+      <c r="AB56" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB56" s="96" t="s">
+      <c r="AC56" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC56" s="134" t="s">
+      <c r="AD56" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD56" s="135" t="s">
+      <c r="AE56" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE56" s="115" t="s">
+      <c r="AF56" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="57" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="114">
         <v>55</v>
       </c>
@@ -55067,56 +55323,57 @@
       <c r="O57" s="95">
         <v>256</v>
       </c>
-      <c r="P57" s="96" t="s">
+      <c r="P57" s="95"/>
+      <c r="Q57" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="Q57" s="96" t="s">
+      <c r="R57" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R57" s="96" t="s">
+      <c r="S57" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S57" s="96" t="s">
+      <c r="T57" s="96" t="s">
         <v>1065</v>
       </c>
-      <c r="T57" s="133" t="s">
+      <c r="U57" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U57" s="114" t="s">
+      <c r="V57" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V57" s="133" t="s">
+      <c r="W57" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W57" s="114" t="s">
+      <c r="X57" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X57" s="96" t="s">
+      <c r="Y57" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y57" s="134" t="s">
+      <c r="Z57" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z57" s="135" t="s">
+      <c r="AA57" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA57" s="133" t="s">
+      <c r="AB57" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB57" s="96" t="s">
+      <c r="AC57" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC57" s="134" t="s">
+      <c r="AD57" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD57" s="135" t="s">
+      <c r="AE57" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE57" s="115" t="s">
+      <c r="AF57" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="58" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="101">
         <v>56</v>
       </c>
@@ -55162,56 +55419,57 @@
       <c r="O58" s="95">
         <v>256</v>
       </c>
-      <c r="P58" s="96" t="s">
+      <c r="P58" s="95"/>
+      <c r="Q58" s="96" t="s">
         <v>1028</v>
       </c>
-      <c r="Q58" s="96" t="s">
+      <c r="R58" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R58" s="96" t="s">
+      <c r="S58" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S58" s="96" t="s">
+      <c r="T58" s="96" t="s">
         <v>1079</v>
       </c>
-      <c r="T58" s="133" t="s">
+      <c r="U58" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U58" s="114" t="s">
+      <c r="V58" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V58" s="133" t="s">
+      <c r="W58" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W58" s="114" t="s">
+      <c r="X58" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X58" s="96" t="s">
+      <c r="Y58" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y58" s="134" t="s">
+      <c r="Z58" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z58" s="135" t="s">
+      <c r="AA58" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA58" s="133" t="s">
+      <c r="AB58" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB58" s="96" t="s">
+      <c r="AC58" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC58" s="134" t="s">
+      <c r="AD58" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD58" s="135" t="s">
+      <c r="AE58" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE58" s="115" t="s">
+      <c r="AF58" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="59" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="114">
         <v>57</v>
       </c>
@@ -55257,56 +55515,56 @@
       <c r="O59" s="96">
         <v>256</v>
       </c>
-      <c r="P59" s="96" t="s">
+      <c r="Q59" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="Q59" s="96" t="s">
+      <c r="R59" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R59" s="96" t="s">
+      <c r="S59" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S59" s="96" t="s">
+      <c r="T59" s="96" t="s">
         <v>1031</v>
       </c>
-      <c r="T59" s="133" t="s">
+      <c r="U59" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U59" s="114" t="s">
+      <c r="V59" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V59" s="133" t="s">
+      <c r="W59" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W59" s="114" t="s">
+      <c r="X59" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X59" s="96" t="s">
+      <c r="Y59" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y59" s="134" t="s">
+      <c r="Z59" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z59" s="135" t="s">
+      <c r="AA59" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA59" s="133" t="s">
+      <c r="AB59" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB59" s="96" t="s">
+      <c r="AC59" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC59" s="134" t="s">
+      <c r="AD59" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD59" s="135" t="s">
+      <c r="AE59" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE59" s="115" t="s">
+      <c r="AF59" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="60" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="114">
         <v>58</v>
       </c>
@@ -55352,56 +55610,56 @@
       <c r="O60" s="96">
         <v>256</v>
       </c>
-      <c r="P60" s="96" t="s">
+      <c r="Q60" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="Q60" s="96" t="s">
+      <c r="R60" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R60" s="96" t="s">
+      <c r="S60" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S60" s="96" t="s">
+      <c r="T60" s="96" t="s">
         <v>1041</v>
       </c>
-      <c r="T60" s="20" t="s">
+      <c r="U60" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U60" s="114" t="s">
+      <c r="V60" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V60" s="20" t="s">
+      <c r="W60" s="20" t="s">
         <v>772</v>
       </c>
-      <c r="W60" s="114" t="s">
+      <c r="X60" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X60" s="96" t="s">
+      <c r="Y60" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y60" s="112" t="s">
+      <c r="Z60" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z60" s="113" t="s">
+      <c r="AA60" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA60" s="133" t="s">
+      <c r="AB60" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB60" s="96" t="s">
+      <c r="AC60" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC60" s="112" t="s">
+      <c r="AD60" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD60" s="113" t="s">
+      <c r="AE60" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE60" s="115" t="s">
+      <c r="AF60" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="61" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="114">
         <v>59</v>
       </c>
@@ -55447,56 +55705,56 @@
       <c r="O61" s="96">
         <v>256</v>
       </c>
-      <c r="P61" s="96" t="s">
+      <c r="Q61" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="Q61" s="96" t="s">
+      <c r="R61" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R61" s="96" t="s">
+      <c r="S61" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S61" s="96" t="s">
+      <c r="T61" s="96" t="s">
         <v>1060</v>
       </c>
-      <c r="T61" s="133" t="s">
+      <c r="U61" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U61" s="114" t="s">
+      <c r="V61" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V61" s="133" t="s">
+      <c r="W61" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W61" s="114" t="s">
+      <c r="X61" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X61" s="96" t="s">
+      <c r="Y61" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y61" s="134" t="s">
+      <c r="Z61" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z61" s="135" t="s">
+      <c r="AA61" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA61" s="133" t="s">
+      <c r="AB61" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB61" s="96" t="s">
+      <c r="AC61" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC61" s="134" t="s">
+      <c r="AD61" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD61" s="135" t="s">
+      <c r="AE61" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE61" s="115" t="s">
+      <c r="AF61" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="62" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="101">
         <v>60</v>
       </c>
@@ -55542,56 +55800,56 @@
       <c r="O62" s="96">
         <v>256</v>
       </c>
-      <c r="P62" s="96" t="s">
+      <c r="Q62" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="Q62" s="96" t="s">
+      <c r="R62" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R62" s="96" t="s">
+      <c r="S62" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S62" s="96" t="s">
+      <c r="T62" s="96" t="s">
         <v>1061</v>
       </c>
-      <c r="T62" s="20" t="s">
+      <c r="U62" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="U62" s="114" t="s">
+      <c r="V62" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V62" s="20" t="s">
+      <c r="W62" s="20" t="s">
         <v>772</v>
       </c>
-      <c r="W62" s="114" t="s">
+      <c r="X62" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X62" s="96" t="s">
+      <c r="Y62" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y62" s="112" t="s">
+      <c r="Z62" s="112" t="s">
         <v>747</v>
       </c>
-      <c r="Z62" s="113" t="s">
+      <c r="AA62" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AA62" s="133" t="s">
+      <c r="AB62" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB62" s="96" t="s">
+      <c r="AC62" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC62" s="112" t="s">
+      <c r="AD62" s="112" t="s">
         <v>753</v>
       </c>
-      <c r="AD62" s="113" t="s">
+      <c r="AE62" s="113" t="s">
         <v>946</v>
       </c>
-      <c r="AE62" s="115" t="s">
+      <c r="AF62" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="63" spans="1:31" s="96" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:32" s="96" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="114">
         <v>61</v>
       </c>
@@ -55637,56 +55895,56 @@
       <c r="O63" s="96">
         <v>256</v>
       </c>
-      <c r="P63" s="96" t="s">
+      <c r="Q63" s="96" t="s">
         <v>1029</v>
       </c>
-      <c r="Q63" s="96" t="s">
+      <c r="R63" s="96" t="s">
         <v>1030</v>
       </c>
-      <c r="R63" s="96" t="s">
+      <c r="S63" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S63" s="96" t="s">
+      <c r="T63" s="96" t="s">
         <v>1064</v>
       </c>
-      <c r="T63" s="133" t="s">
+      <c r="U63" s="133" t="s">
         <v>92</v>
       </c>
-      <c r="U63" s="114" t="s">
+      <c r="V63" s="114" t="s">
         <v>943</v>
       </c>
-      <c r="V63" s="133" t="s">
+      <c r="W63" s="133" t="s">
         <v>772</v>
       </c>
-      <c r="W63" s="114" t="s">
+      <c r="X63" s="114" t="s">
         <v>989</v>
       </c>
-      <c r="X63" s="96" t="s">
+      <c r="Y63" s="96" t="s">
         <v>990</v>
       </c>
-      <c r="Y63" s="134" t="s">
+      <c r="Z63" s="134" t="s">
         <v>747</v>
       </c>
-      <c r="Z63" s="135" t="s">
+      <c r="AA63" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AA63" s="133" t="s">
+      <c r="AB63" s="133" t="s">
         <v>947</v>
       </c>
-      <c r="AB63" s="96" t="s">
+      <c r="AC63" s="96" t="s">
         <v>991</v>
       </c>
-      <c r="AC63" s="134" t="s">
+      <c r="AD63" s="134" t="s">
         <v>753</v>
       </c>
-      <c r="AD63" s="135" t="s">
+      <c r="AE63" s="135" t="s">
         <v>946</v>
       </c>
-      <c r="AE63" s="115" t="s">
+      <c r="AF63" s="115" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="64" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:32" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="114">
         <v>62</v>
       </c>
@@ -55732,56 +55990,56 @@
       <c r="O64" s="73">
         <v>256</v>
       </c>
-      <c r="P64" s="73" t="s">
+      <c r="Q64" s="73" t="s">
         <v>1029</v>
       </c>
-      <c r="Q64" s="73" t="s">
+      <c r="R64" s="73" t="s">
         <v>1030</v>
       </c>
-      <c r="R64" s="73" t="s">
+      <c r="S64" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S64" s="73" t="s">
+      <c r="T64" s="73" t="s">
         <v>1065</v>
       </c>
-      <c r="T64" s="80" t="s">
+      <c r="U64" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="U64" s="74" t="s">
+      <c r="V64" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="V64" s="80" t="s">
+      <c r="W64" s="80" t="s">
         <v>772</v>
       </c>
-      <c r="W64" s="74" t="s">
+      <c r="X64" s="74" t="s">
         <v>989</v>
       </c>
-      <c r="X64" s="73" t="s">
+      <c r="Y64" s="73" t="s">
         <v>990</v>
       </c>
-      <c r="Y64" s="121" t="s">
+      <c r="Z64" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="Z64" s="124" t="s">
+      <c r="AA64" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AA64" s="85" t="s">
+      <c r="AB64" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="AB64" s="73" t="s">
+      <c r="AC64" s="73" t="s">
         <v>991</v>
       </c>
-      <c r="AC64" s="121" t="s">
+      <c r="AD64" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AD64" s="124" t="s">
+      <c r="AE64" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AE64" s="122" t="s">
+      <c r="AF64" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="65" spans="1:31" s="73" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:32" s="73" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="114">
         <v>63</v>
       </c>
@@ -55827,56 +56085,56 @@
       <c r="O65" s="73">
         <v>256</v>
       </c>
-      <c r="P65" s="73" t="s">
+      <c r="Q65" s="73" t="s">
         <v>1029</v>
       </c>
-      <c r="Q65" s="73" t="s">
+      <c r="R65" s="73" t="s">
         <v>1030</v>
       </c>
-      <c r="R65" s="73" t="s">
+      <c r="S65" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S65" s="73" t="s">
+      <c r="T65" s="73" t="s">
         <v>1079</v>
       </c>
-      <c r="T65" s="80" t="s">
+      <c r="U65" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="U65" s="74" t="s">
+      <c r="V65" s="74" t="s">
         <v>943</v>
       </c>
-      <c r="V65" s="80" t="s">
+      <c r="W65" s="80" t="s">
         <v>772</v>
       </c>
-      <c r="W65" s="74" t="s">
+      <c r="X65" s="74" t="s">
         <v>989</v>
       </c>
-      <c r="X65" s="73" t="s">
+      <c r="Y65" s="73" t="s">
         <v>990</v>
       </c>
-      <c r="Y65" s="121" t="s">
+      <c r="Z65" s="121" t="s">
         <v>747</v>
       </c>
-      <c r="Z65" s="124" t="s">
+      <c r="AA65" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AA65" s="85" t="s">
+      <c r="AB65" s="85" t="s">
         <v>947</v>
       </c>
-      <c r="AB65" s="73" t="s">
+      <c r="AC65" s="73" t="s">
         <v>991</v>
       </c>
-      <c r="AC65" s="121" t="s">
+      <c r="AD65" s="121" t="s">
         <v>753</v>
       </c>
-      <c r="AD65" s="124" t="s">
+      <c r="AE65" s="124" t="s">
         <v>946</v>
       </c>
-      <c r="AE65" s="122" t="s">
+      <c r="AF65" s="122" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A66" s="101">
         <v>64</v>
       </c>
@@ -55919,56 +56177,56 @@
       <c r="N66" s="95">
         <v>1</v>
       </c>
-      <c r="P66" t="s">
+      <c r="Q66" t="s">
         <v>1089</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="R66" t="s">
         <v>868</v>
       </c>
-      <c r="R66" s="73" t="s">
+      <c r="S66" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S66" t="s">
+      <c r="T66" t="s">
         <v>1090</v>
       </c>
-      <c r="T66" s="133" t="s">
+      <c r="U66" s="133" t="s">
         <v>95</v>
       </c>
-      <c r="U66" s="101" t="s">
+      <c r="V66" s="101" t="s">
         <v>840</v>
       </c>
-      <c r="V66" s="126" t="s">
+      <c r="W66" s="126" t="s">
         <v>775</v>
       </c>
-      <c r="W66" s="107" t="s">
+      <c r="X66" s="107" t="s">
         <v>841</v>
       </c>
-      <c r="X66" s="101" t="s">
+      <c r="Y66" s="101" t="s">
         <v>842</v>
       </c>
-      <c r="Y66" s="136" t="s">
+      <c r="Z66" s="136" t="s">
         <v>765</v>
       </c>
-      <c r="Z66" s="137" t="s">
+      <c r="AA66" s="137" t="s">
         <v>901</v>
       </c>
-      <c r="AA66" s="129" t="s">
+      <c r="AB66" s="129" t="s">
         <v>843</v>
       </c>
-      <c r="AB66" s="101" t="s">
+      <c r="AC66" s="101" t="s">
         <v>844</v>
       </c>
-      <c r="AC66" s="136" t="s">
+      <c r="AD66" s="136" t="s">
         <v>845</v>
       </c>
-      <c r="AD66" s="137" t="s">
+      <c r="AE66" s="137" t="s">
         <v>901</v>
       </c>
-      <c r="AE66" s="129" t="s">
+      <c r="AF66" s="129" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A67" s="114">
         <v>65</v>
       </c>
@@ -56011,56 +56269,56 @@
       <c r="N67" s="95">
         <v>1</v>
       </c>
-      <c r="P67" t="s">
+      <c r="Q67" t="s">
         <v>1095</v>
       </c>
-      <c r="Q67" t="s">
+      <c r="R67" t="s">
         <v>873</v>
       </c>
-      <c r="R67" s="73" t="s">
+      <c r="S67" s="73" t="s">
         <v>914</v>
       </c>
-      <c r="S67" t="s">
+      <c r="T67" t="s">
         <v>1098</v>
       </c>
-      <c r="T67" s="133" t="s">
+      <c r="U67" s="133" t="s">
         <v>95</v>
       </c>
-      <c r="U67" s="6" t="s">
+      <c r="V67" s="6" t="s">
         <v>840</v>
       </c>
-      <c r="V67" s="28" t="s">
+      <c r="W67" s="28" t="s">
         <v>848</v>
       </c>
-      <c r="W67" t="s">
+      <c r="X67" t="s">
         <v>849</v>
       </c>
-      <c r="X67" s="6" t="s">
+      <c r="Y67" s="6" t="s">
         <v>850</v>
       </c>
-      <c r="Y67" s="23" t="s">
+      <c r="Z67" s="23" t="s">
         <v>765</v>
       </c>
-      <c r="Z67" s="24" t="s">
+      <c r="AA67" s="24" t="s">
         <v>901</v>
       </c>
-      <c r="AA67" s="27" t="s">
+      <c r="AB67" s="27" t="s">
         <v>851</v>
       </c>
-      <c r="AB67" s="6" t="s">
+      <c r="AC67" s="6" t="s">
         <v>844</v>
       </c>
-      <c r="AC67" s="23" t="s">
+      <c r="AD67" s="23" t="s">
         <v>845</v>
       </c>
-      <c r="AD67" s="24" t="s">
+      <c r="AE67" s="24" t="s">
         <v>901</v>
       </c>
-      <c r="AE67" s="27" t="s">
+      <c r="AF67" s="27" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A68" s="114">
         <v>66</v>
       </c>
@@ -56103,56 +56361,56 @@
       <c r="N68" s="95">
         <v>1</v>
       </c>
-      <c r="P68" t="s">
+      <c r="Q68" t="s">
         <v>1096</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R68" t="s">
         <v>1097</v>
       </c>
-      <c r="R68" s="96" t="s">
+      <c r="S68" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S68" t="s">
+      <c r="T68" t="s">
         <v>1099</v>
       </c>
-      <c r="T68" s="133" t="s">
+      <c r="U68" s="133" t="s">
         <v>95</v>
       </c>
-      <c r="U68" s="6" t="s">
+      <c r="V68" s="6" t="s">
         <v>840</v>
       </c>
-      <c r="V68" s="133" t="s">
+      <c r="W68" s="133" t="s">
         <v>108</v>
       </c>
-      <c r="W68" s="114" t="s">
+      <c r="X68" s="114" t="s">
         <v>1091</v>
       </c>
-      <c r="X68" s="6" t="s">
+      <c r="Y68" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="Y68" s="23" t="s">
+      <c r="Z68" s="23" t="s">
         <v>765</v>
       </c>
-      <c r="Z68" s="24" t="s">
+      <c r="AA68" s="24" t="s">
         <v>901</v>
       </c>
-      <c r="AA68" s="27" t="s">
+      <c r="AB68" s="27" t="s">
         <v>851</v>
       </c>
-      <c r="AB68" s="95" t="s">
+      <c r="AC68" s="95" t="s">
         <v>996</v>
       </c>
-      <c r="AC68" s="23" t="s">
+      <c r="AD68" s="23" t="s">
         <v>845</v>
       </c>
-      <c r="AD68" s="24" t="s">
+      <c r="AE68" s="24" t="s">
         <v>901</v>
       </c>
-      <c r="AE68" s="27" t="s">
+      <c r="AF68" s="27" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="69" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="107">
         <v>67</v>
       </c>
@@ -56195,56 +56453,56 @@
       <c r="N69" s="107">
         <v>1</v>
       </c>
-      <c r="P69" s="107" t="s">
+      <c r="Q69" s="107" t="s">
         <v>1112</v>
       </c>
-      <c r="Q69" s="107" t="s">
+      <c r="R69" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R69" s="96" t="s">
+      <c r="S69" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S69" s="107" t="s">
+      <c r="T69" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T69" s="107" t="s">
+      <c r="U69" s="107" t="s">
         <v>1118</v>
       </c>
-      <c r="U69" s="107" t="s">
+      <c r="V69" s="107" t="s">
         <v>1119</v>
       </c>
-      <c r="V69" s="107" t="s">
+      <c r="W69" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W69" s="107" t="s">
+      <c r="X69" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X69" s="107" t="s">
+      <c r="Y69" s="107" t="s">
         <v>1122</v>
       </c>
-      <c r="Y69" s="107" t="s">
+      <c r="Z69" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z69" s="107" t="s">
+      <c r="AA69" s="107" t="s">
         <v>1121</v>
       </c>
-      <c r="AA69" s="107" t="s">
+      <c r="AB69" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB69" s="107" t="s">
+      <c r="AC69" s="107" t="s">
         <v>1122</v>
       </c>
-      <c r="AC69" s="107" t="s">
+      <c r="AD69" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD69" s="107" t="s">
+      <c r="AE69" s="107" t="s">
         <v>1121</v>
       </c>
-      <c r="AE69" s="107" t="s">
+      <c r="AF69" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A70" s="107">
         <v>68</v>
       </c>
@@ -56287,56 +56545,56 @@
       <c r="N70" s="107">
         <v>1</v>
       </c>
-      <c r="P70" t="s">
+      <c r="Q70" t="s">
         <v>1113</v>
       </c>
-      <c r="Q70" s="107" t="s">
+      <c r="R70" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R70" s="96" t="s">
+      <c r="S70" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S70" s="107" t="s">
+      <c r="T70" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T70" s="133" t="s">
+      <c r="U70" s="133" t="s">
         <v>1118</v>
       </c>
-      <c r="U70" t="s">
+      <c r="V70" t="s">
         <v>1119</v>
       </c>
-      <c r="V70" s="107" t="s">
+      <c r="W70" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W70" s="107" t="s">
+      <c r="X70" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X70" t="s">
+      <c r="Y70" t="s">
         <v>1122</v>
       </c>
-      <c r="Y70" s="107" t="s">
+      <c r="Z70" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z70" t="s">
+      <c r="AA70" t="s">
         <v>1121</v>
       </c>
-      <c r="AA70" s="107" t="s">
+      <c r="AB70" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB70" t="s">
+      <c r="AC70" t="s">
         <v>1122</v>
       </c>
-      <c r="AC70" s="107" t="s">
+      <c r="AD70" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD70" t="s">
+      <c r="AE70" t="s">
         <v>1121</v>
       </c>
-      <c r="AE70" s="107" t="s">
+      <c r="AF70" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A71" s="107">
         <v>69</v>
       </c>
@@ -56379,56 +56637,56 @@
       <c r="N71" s="107">
         <v>1</v>
       </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>1114</v>
       </c>
-      <c r="Q71" s="107" t="s">
+      <c r="R71" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R71" s="96" t="s">
+      <c r="S71" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S71" s="107" t="s">
+      <c r="T71" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T71" s="133" t="s">
+      <c r="U71" s="133" t="s">
         <v>1118</v>
       </c>
-      <c r="U71" t="s">
+      <c r="V71" t="s">
         <v>1119</v>
       </c>
-      <c r="V71" s="107" t="s">
+      <c r="W71" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W71" s="107" t="s">
+      <c r="X71" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X71" t="s">
+      <c r="Y71" t="s">
         <v>1122</v>
       </c>
-      <c r="Y71" s="107" t="s">
+      <c r="Z71" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z71" t="s">
+      <c r="AA71" t="s">
         <v>1121</v>
       </c>
-      <c r="AA71" s="107" t="s">
+      <c r="AB71" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB71" t="s">
+      <c r="AC71" t="s">
         <v>1122</v>
       </c>
-      <c r="AC71" s="107" t="s">
+      <c r="AD71" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD71" t="s">
+      <c r="AE71" t="s">
         <v>1121</v>
       </c>
-      <c r="AE71" s="107" t="s">
+      <c r="AF71" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A72" s="107">
         <v>70</v>
       </c>
@@ -56471,56 +56729,56 @@
       <c r="N72" s="107">
         <v>1</v>
       </c>
-      <c r="P72" t="s">
+      <c r="Q72" t="s">
         <v>1115</v>
       </c>
-      <c r="Q72" s="107" t="s">
+      <c r="R72" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R72" s="96" t="s">
+      <c r="S72" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S72" s="107" t="s">
+      <c r="T72" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T72" s="133" t="s">
+      <c r="U72" s="133" t="s">
         <v>1118</v>
       </c>
-      <c r="U72" t="s">
+      <c r="V72" t="s">
         <v>1119</v>
       </c>
-      <c r="V72" s="107" t="s">
+      <c r="W72" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W72" s="107" t="s">
+      <c r="X72" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X72" t="s">
+      <c r="Y72" t="s">
         <v>1122</v>
       </c>
-      <c r="Y72" s="107" t="s">
+      <c r="Z72" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z72" t="s">
+      <c r="AA72" t="s">
         <v>1121</v>
       </c>
-      <c r="AA72" s="107" t="s">
+      <c r="AB72" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB72" t="s">
+      <c r="AC72" t="s">
         <v>1122</v>
       </c>
-      <c r="AC72" s="107" t="s">
+      <c r="AD72" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD72" t="s">
+      <c r="AE72" t="s">
         <v>1121</v>
       </c>
-      <c r="AE72" s="107" t="s">
+      <c r="AF72" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="73" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="107">
         <v>71</v>
       </c>
@@ -56563,56 +56821,57 @@
       <c r="N73" s="107">
         <v>1</v>
       </c>
-      <c r="P73" t="s">
+      <c r="P73" s="96"/>
+      <c r="Q73" t="s">
         <v>1132</v>
       </c>
-      <c r="Q73" s="107" t="s">
+      <c r="R73" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R73" s="96" t="s">
+      <c r="S73" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S73" s="107" t="s">
+      <c r="T73" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T73" s="107" t="s">
+      <c r="U73" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U73" s="107" t="s">
+      <c r="V73" s="107" t="s">
         <v>1119</v>
       </c>
-      <c r="V73" s="107" t="s">
+      <c r="W73" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W73" s="107" t="s">
+      <c r="X73" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X73" s="107" t="s">
+      <c r="Y73" s="107" t="s">
         <v>1122</v>
       </c>
-      <c r="Y73" s="107" t="s">
+      <c r="Z73" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z73" s="107" t="s">
+      <c r="AA73" s="107" t="s">
         <v>1121</v>
       </c>
-      <c r="AA73" s="107" t="s">
+      <c r="AB73" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB73" s="107" t="s">
+      <c r="AC73" s="107" t="s">
         <v>1122</v>
       </c>
-      <c r="AC73" s="107" t="s">
+      <c r="AD73" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD73" s="107" t="s">
+      <c r="AE73" s="107" t="s">
         <v>1121</v>
       </c>
-      <c r="AE73" s="107" t="s">
+      <c r="AF73" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A74" s="107">
         <v>72</v>
       </c>
@@ -56655,56 +56914,56 @@
       <c r="N74" s="107">
         <v>1</v>
       </c>
-      <c r="P74" t="s">
+      <c r="Q74" t="s">
         <v>1133</v>
       </c>
-      <c r="Q74" s="107" t="s">
+      <c r="R74" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R74" s="96" t="s">
+      <c r="S74" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S74" s="107" t="s">
+      <c r="T74" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T74" s="107" t="s">
+      <c r="U74" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U74" t="s">
+      <c r="V74" t="s">
         <v>1119</v>
       </c>
-      <c r="V74" s="107" t="s">
+      <c r="W74" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W74" s="107" t="s">
+      <c r="X74" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X74" t="s">
+      <c r="Y74" t="s">
         <v>1122</v>
       </c>
-      <c r="Y74" s="107" t="s">
+      <c r="Z74" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z74" t="s">
+      <c r="AA74" t="s">
         <v>1121</v>
       </c>
-      <c r="AA74" s="107" t="s">
+      <c r="AB74" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB74" t="s">
+      <c r="AC74" t="s">
         <v>1122</v>
       </c>
-      <c r="AC74" s="107" t="s">
+      <c r="AD74" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD74" t="s">
+      <c r="AE74" t="s">
         <v>1121</v>
       </c>
-      <c r="AE74" s="107" t="s">
+      <c r="AF74" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A75" s="107">
         <v>73</v>
       </c>
@@ -56747,56 +57006,56 @@
       <c r="N75" s="107">
         <v>1</v>
       </c>
-      <c r="P75" t="s">
+      <c r="Q75" t="s">
         <v>1134</v>
       </c>
-      <c r="Q75" s="107" t="s">
+      <c r="R75" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R75" s="96" t="s">
+      <c r="S75" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S75" s="107" t="s">
+      <c r="T75" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T75" s="107" t="s">
+      <c r="U75" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U75" t="s">
+      <c r="V75" t="s">
         <v>1119</v>
       </c>
-      <c r="V75" s="107" t="s">
+      <c r="W75" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W75" s="107" t="s">
+      <c r="X75" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X75" t="s">
+      <c r="Y75" t="s">
         <v>1122</v>
       </c>
-      <c r="Y75" s="107" t="s">
+      <c r="Z75" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z75" t="s">
+      <c r="AA75" t="s">
         <v>1121</v>
       </c>
-      <c r="AA75" s="107" t="s">
+      <c r="AB75" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB75" t="s">
+      <c r="AC75" t="s">
         <v>1122</v>
       </c>
-      <c r="AC75" s="107" t="s">
+      <c r="AD75" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD75" t="s">
+      <c r="AE75" t="s">
         <v>1121</v>
       </c>
-      <c r="AE75" s="107" t="s">
+      <c r="AF75" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A76" s="107">
         <v>74</v>
       </c>
@@ -56839,56 +57098,56 @@
       <c r="N76" s="107">
         <v>1</v>
       </c>
-      <c r="P76" t="s">
+      <c r="Q76" t="s">
         <v>1135</v>
       </c>
-      <c r="Q76" s="107" t="s">
+      <c r="R76" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R76" s="96" t="s">
+      <c r="S76" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S76" s="107" t="s">
+      <c r="T76" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T76" s="107" t="s">
+      <c r="U76" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U76" t="s">
+      <c r="V76" t="s">
         <v>1119</v>
       </c>
-      <c r="V76" s="107" t="s">
+      <c r="W76" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W76" s="107" t="s">
+      <c r="X76" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X76" t="s">
+      <c r="Y76" t="s">
         <v>1122</v>
       </c>
-      <c r="Y76" s="107" t="s">
+      <c r="Z76" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z76" t="s">
+      <c r="AA76" t="s">
         <v>1121</v>
       </c>
-      <c r="AA76" s="107" t="s">
+      <c r="AB76" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB76" t="s">
+      <c r="AC76" t="s">
         <v>1122</v>
       </c>
-      <c r="AC76" s="107" t="s">
+      <c r="AD76" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD76" t="s">
+      <c r="AE76" t="s">
         <v>1121</v>
       </c>
-      <c r="AE76" s="107" t="s">
+      <c r="AF76" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="77" spans="1:31" s="107" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" s="107">
         <v>75</v>
       </c>
@@ -56931,56 +57190,56 @@
       <c r="N77" s="107">
         <v>1</v>
       </c>
-      <c r="P77" s="107" t="s">
+      <c r="Q77" s="107" t="s">
         <v>1112</v>
       </c>
-      <c r="Q77" s="107" t="s">
+      <c r="R77" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R77" s="96" t="s">
+      <c r="S77" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S77" s="107" t="s">
+      <c r="T77" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T77" s="107" t="s">
+      <c r="U77" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U77" s="107" t="s">
+      <c r="V77" s="107" t="s">
         <v>1119</v>
       </c>
-      <c r="V77" s="107" t="s">
+      <c r="W77" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W77" s="107" t="s">
+      <c r="X77" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X77" s="107" t="s">
+      <c r="Y77" s="107" t="s">
         <v>1122</v>
       </c>
-      <c r="Y77" s="107" t="s">
+      <c r="Z77" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z77" s="107" t="s">
+      <c r="AA77" s="107" t="s">
         <v>1121</v>
       </c>
-      <c r="AA77" s="107" t="s">
+      <c r="AB77" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB77" s="107" t="s">
+      <c r="AC77" s="107" t="s">
         <v>1122</v>
       </c>
-      <c r="AC77" s="107" t="s">
+      <c r="AD77" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD77" s="107" t="s">
+      <c r="AE77" s="107" t="s">
         <v>1121</v>
       </c>
-      <c r="AE77" s="107" t="s">
+      <c r="AF77" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A78" s="107">
         <v>76</v>
       </c>
@@ -57023,56 +57282,56 @@
       <c r="N78" s="107">
         <v>1</v>
       </c>
-      <c r="P78" t="s">
+      <c r="Q78" t="s">
         <v>1113</v>
       </c>
-      <c r="Q78" s="107" t="s">
+      <c r="R78" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R78" s="96" t="s">
+      <c r="S78" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S78" s="107" t="s">
+      <c r="T78" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T78" s="107" t="s">
+      <c r="U78" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U78" t="s">
+      <c r="V78" t="s">
         <v>1119</v>
       </c>
-      <c r="V78" s="107" t="s">
+      <c r="W78" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W78" s="107" t="s">
+      <c r="X78" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X78" t="s">
+      <c r="Y78" t="s">
         <v>1122</v>
       </c>
-      <c r="Y78" s="107" t="s">
+      <c r="Z78" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z78" t="s">
+      <c r="AA78" t="s">
         <v>1121</v>
       </c>
-      <c r="AA78" s="107" t="s">
+      <c r="AB78" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB78" t="s">
+      <c r="AC78" t="s">
         <v>1122</v>
       </c>
-      <c r="AC78" s="107" t="s">
+      <c r="AD78" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD78" t="s">
+      <c r="AE78" t="s">
         <v>1121</v>
       </c>
-      <c r="AE78" s="107" t="s">
+      <c r="AF78" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A79" s="107">
         <v>77</v>
       </c>
@@ -57115,56 +57374,56 @@
       <c r="N79" s="107">
         <v>1</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>1114</v>
       </c>
-      <c r="Q79" s="107" t="s">
+      <c r="R79" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R79" s="96" t="s">
+      <c r="S79" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S79" s="107" t="s">
+      <c r="T79" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T79" s="107" t="s">
+      <c r="U79" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U79" t="s">
+      <c r="V79" t="s">
         <v>1119</v>
       </c>
-      <c r="V79" s="107" t="s">
+      <c r="W79" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W79" s="107" t="s">
+      <c r="X79" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X79" t="s">
+      <c r="Y79" t="s">
         <v>1122</v>
       </c>
-      <c r="Y79" s="107" t="s">
+      <c r="Z79" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z79" t="s">
+      <c r="AA79" t="s">
         <v>1121</v>
       </c>
-      <c r="AA79" s="107" t="s">
+      <c r="AB79" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB79" t="s">
+      <c r="AC79" t="s">
         <v>1122</v>
       </c>
-      <c r="AC79" s="107" t="s">
+      <c r="AD79" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD79" t="s">
+      <c r="AE79" t="s">
         <v>1121</v>
       </c>
-      <c r="AE79" s="107" t="s">
+      <c r="AF79" s="107" t="s">
         <v>1123</v>
       </c>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A80" s="107">
         <v>78</v>
       </c>
@@ -57207,53 +57466,1763 @@
       <c r="N80" s="107">
         <v>1</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>1115</v>
       </c>
-      <c r="Q80" s="107" t="s">
+      <c r="R80" s="107" t="s">
         <v>1116</v>
       </c>
-      <c r="R80" s="96" t="s">
+      <c r="S80" s="96" t="s">
         <v>914</v>
       </c>
-      <c r="S80" s="107" t="s">
+      <c r="T80" s="107" t="s">
         <v>1117</v>
       </c>
-      <c r="T80" s="107" t="s">
+      <c r="U80" s="107" t="s">
         <v>96</v>
       </c>
-      <c r="U80" t="s">
+      <c r="V80" t="s">
         <v>1119</v>
       </c>
-      <c r="V80" s="107" t="s">
+      <c r="W80" s="107" t="s">
         <v>116</v>
       </c>
-      <c r="W80" s="107" t="s">
+      <c r="X80" s="107" t="s">
         <v>1120</v>
       </c>
-      <c r="X80" t="s">
+      <c r="Y80" t="s">
         <v>1122</v>
       </c>
-      <c r="Y80" s="107" t="s">
+      <c r="Z80" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="Z80" t="s">
+      <c r="AA80" t="s">
         <v>1121</v>
       </c>
-      <c r="AA80" s="107" t="s">
+      <c r="AB80" s="107" t="s">
         <v>1123</v>
       </c>
-      <c r="AB80" t="s">
+      <c r="AC80" t="s">
         <v>1122</v>
       </c>
-      <c r="AC80" s="107" t="s">
+      <c r="AD80" s="107" t="s">
         <v>759</v>
       </c>
-      <c r="AD80" t="s">
+      <c r="AE80" t="s">
         <v>1121</v>
       </c>
-      <c r="AE80" s="107" t="s">
+      <c r="AF80" s="107" t="s">
         <v>1123</v>
+      </c>
+    </row>
+    <row r="81" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A81" s="95">
+        <v>79</v>
+      </c>
+      <c r="B81" s="110" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C81" s="95" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D81" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E81" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F81" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G81">
+        <v>2</v>
+      </c>
+      <c r="H81" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I81" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J81" s="95">
+        <v>1</v>
+      </c>
+      <c r="K81" s="95">
+        <v>1</v>
+      </c>
+      <c r="L81" s="95">
+        <v>1</v>
+      </c>
+      <c r="M81" s="95">
+        <v>1</v>
+      </c>
+      <c r="N81" s="95">
+        <v>1</v>
+      </c>
+      <c r="P81">
+        <v>529</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>1140</v>
+      </c>
+      <c r="R81" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S81" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T81" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U81" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V81" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W81" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X81" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z81" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA81" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB81" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC81" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD81" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE81" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF81" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="82" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A82" s="107">
+        <v>80</v>
+      </c>
+      <c r="B82" s="110" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C82" s="95" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D82" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E82" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F82" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I82" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J82" s="95">
+        <v>1</v>
+      </c>
+      <c r="K82" s="95">
+        <v>1</v>
+      </c>
+      <c r="L82" s="95">
+        <v>1</v>
+      </c>
+      <c r="M82" s="95">
+        <v>1</v>
+      </c>
+      <c r="N82" s="95">
+        <v>1</v>
+      </c>
+      <c r="P82">
+        <v>529</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>1149</v>
+      </c>
+      <c r="R82" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S82" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T82" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U82" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V82" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W82" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X82" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y82" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z82" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA82" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB82" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC82" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD82" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE82" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF82" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A83" s="95">
+        <v>81</v>
+      </c>
+      <c r="B83" s="110" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C83" s="95" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D83" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E83" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F83" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="H83" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I83" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J83" s="95">
+        <v>1</v>
+      </c>
+      <c r="K83" s="95">
+        <v>1</v>
+      </c>
+      <c r="L83" s="95">
+        <v>1</v>
+      </c>
+      <c r="M83" s="95">
+        <v>1</v>
+      </c>
+      <c r="N83" s="95">
+        <v>1</v>
+      </c>
+      <c r="P83">
+        <v>529</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>1150</v>
+      </c>
+      <c r="R83" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S83" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T83" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U83" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V83" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W83" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X83" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z83" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA83" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB83" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC83" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD83" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE83" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF83" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="84" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A84" s="107">
+        <v>82</v>
+      </c>
+      <c r="B84" s="110" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C84" s="95" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D84" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E84" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F84" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I84" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J84" s="95">
+        <v>1</v>
+      </c>
+      <c r="K84" s="95">
+        <v>1</v>
+      </c>
+      <c r="L84" s="95">
+        <v>1</v>
+      </c>
+      <c r="M84" s="95">
+        <v>1</v>
+      </c>
+      <c r="N84" s="95">
+        <v>1</v>
+      </c>
+      <c r="P84">
+        <v>529</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>1151</v>
+      </c>
+      <c r="R84" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S84" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T84" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U84" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W84" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X84" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y84" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z84" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA84" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB84" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC84" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD84" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE84" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF84" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="85" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A85" s="95">
+        <v>83</v>
+      </c>
+      <c r="B85" s="110" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C85" s="95" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D85" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E85" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F85" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="H85" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I85" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J85" s="95">
+        <v>1</v>
+      </c>
+      <c r="K85" s="95">
+        <v>1</v>
+      </c>
+      <c r="L85" s="95">
+        <v>1</v>
+      </c>
+      <c r="M85" s="95">
+        <v>1</v>
+      </c>
+      <c r="N85" s="95">
+        <v>1</v>
+      </c>
+      <c r="P85">
+        <v>529</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>1152</v>
+      </c>
+      <c r="R85" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S85" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T85" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U85" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W85" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X85" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y85" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z85" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA85" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB85" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC85" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD85" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE85" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF85" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="86" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A86" s="107">
+        <v>84</v>
+      </c>
+      <c r="B86" s="110" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C86" s="95" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D86" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E86" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F86" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G86">
+        <v>2</v>
+      </c>
+      <c r="H86" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I86" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J86" s="95">
+        <v>1</v>
+      </c>
+      <c r="K86" s="95">
+        <v>1</v>
+      </c>
+      <c r="L86" s="95">
+        <v>1</v>
+      </c>
+      <c r="M86" s="95">
+        <v>1</v>
+      </c>
+      <c r="N86" s="95">
+        <v>1</v>
+      </c>
+      <c r="P86">
+        <v>529</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>1153</v>
+      </c>
+      <c r="R86" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S86" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T86" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U86" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W86" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X86" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y86" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z86" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA86" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB86" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC86" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD86" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE86" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF86" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="87" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A87" s="95">
+        <v>85</v>
+      </c>
+      <c r="B87" s="110" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C87" s="95" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D87" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E87" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F87" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G87">
+        <v>2</v>
+      </c>
+      <c r="H87" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I87" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J87" s="95">
+        <v>1</v>
+      </c>
+      <c r="K87" s="95">
+        <v>1</v>
+      </c>
+      <c r="L87" s="95">
+        <v>1</v>
+      </c>
+      <c r="M87" s="95">
+        <v>1</v>
+      </c>
+      <c r="N87" s="95">
+        <v>1</v>
+      </c>
+      <c r="P87">
+        <v>529</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>1154</v>
+      </c>
+      <c r="R87" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S87" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T87" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U87" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W87" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X87" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y87" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z87" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA87" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB87" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC87" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD87" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE87" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF87" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="88" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A88" s="107">
+        <v>86</v>
+      </c>
+      <c r="B88" s="110" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C88" s="95" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D88" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E88" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F88" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G88">
+        <v>2</v>
+      </c>
+      <c r="H88" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I88" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J88" s="95">
+        <v>1</v>
+      </c>
+      <c r="K88" s="95">
+        <v>1</v>
+      </c>
+      <c r="L88" s="95">
+        <v>1</v>
+      </c>
+      <c r="M88" s="95">
+        <v>1</v>
+      </c>
+      <c r="N88" s="95">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>529</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>1155</v>
+      </c>
+      <c r="R88" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S88" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T88" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U88" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W88" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X88" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y88" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z88" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA88" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB88" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC88" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD88" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE88" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF88" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="89" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A89" s="95">
+        <v>87</v>
+      </c>
+      <c r="B89" s="110" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C89" s="95" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D89" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E89" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F89" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89" s="130" t="s">
+        <v>104</v>
+      </c>
+      <c r="I89" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J89" s="95">
+        <v>1</v>
+      </c>
+      <c r="K89" s="95">
+        <v>1</v>
+      </c>
+      <c r="L89" s="95">
+        <v>1</v>
+      </c>
+      <c r="M89" s="95">
+        <v>1</v>
+      </c>
+      <c r="N89" s="95">
+        <v>1</v>
+      </c>
+      <c r="P89">
+        <v>529</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>1156</v>
+      </c>
+      <c r="R89" t="s">
+        <v>1139</v>
+      </c>
+      <c r="S89" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T89" t="s">
+        <v>1138</v>
+      </c>
+      <c r="U89" s="31" t="s">
+        <v>963</v>
+      </c>
+      <c r="V89" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="W89" s="20" t="s">
+        <v>789</v>
+      </c>
+      <c r="X89" s="50" t="s">
+        <v>792</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z89" s="18" t="s">
+        <v>747</v>
+      </c>
+      <c r="AA89" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="AB89" s="26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="AC89" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD89" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="AE89" s="14" t="s">
+        <v>881</v>
+      </c>
+      <c r="AF89" s="26" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="90" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A90" s="95">
+        <v>88</v>
+      </c>
+      <c r="B90" s="110" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D90" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E90" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F90" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G90">
+        <v>2</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I90" s="130" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="95">
+        <v>1</v>
+      </c>
+      <c r="K90" s="95">
+        <v>1</v>
+      </c>
+      <c r="L90" s="95">
+        <v>1</v>
+      </c>
+      <c r="M90" s="95">
+        <v>1</v>
+      </c>
+      <c r="N90" s="95">
+        <v>1</v>
+      </c>
+      <c r="P90">
+        <v>11932</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>380</v>
+      </c>
+      <c r="R90" t="s">
+        <v>381</v>
+      </c>
+      <c r="S90" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T90" t="s">
+        <v>1168</v>
+      </c>
+      <c r="U90" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="V90" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="W90" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="X90" s="50" t="s">
+        <v>793</v>
+      </c>
+      <c r="Y90" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="Z90" s="18" t="s">
+        <v>749</v>
+      </c>
+      <c r="AA90" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="AB90" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC90" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="AD90" s="17" t="s">
+        <v>749</v>
+      </c>
+      <c r="AE90" s="14" t="s">
+        <v>904</v>
+      </c>
+      <c r="AF90" s="26" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="91" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A91" s="95">
+        <v>89</v>
+      </c>
+      <c r="B91" s="110" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D91" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E91" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F91" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91" s="130" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I91" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J91" s="95">
+        <v>1</v>
+      </c>
+      <c r="K91" s="95">
+        <v>1</v>
+      </c>
+      <c r="L91" s="95">
+        <v>1</v>
+      </c>
+      <c r="M91" s="95">
+        <v>1</v>
+      </c>
+      <c r="N91" s="95">
+        <v>1</v>
+      </c>
+      <c r="P91">
+        <v>2958</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>1188</v>
+      </c>
+      <c r="R91" t="s">
+        <v>1190</v>
+      </c>
+      <c r="S91" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T91" t="s">
+        <v>1196</v>
+      </c>
+      <c r="U91" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V91" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W91" s="20" t="s">
+        <v>1178</v>
+      </c>
+      <c r="X91" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z91" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB91" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC91" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD91" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE91" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF91" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="92" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A92" s="95">
+        <v>90</v>
+      </c>
+      <c r="B92" s="110" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D92" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E92" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F92" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G92">
+        <v>2</v>
+      </c>
+      <c r="H92" s="130" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I92" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J92" s="95">
+        <v>1</v>
+      </c>
+      <c r="K92" s="95">
+        <v>1</v>
+      </c>
+      <c r="L92" s="95">
+        <v>1</v>
+      </c>
+      <c r="M92" s="95">
+        <v>1</v>
+      </c>
+      <c r="N92" s="95">
+        <v>1</v>
+      </c>
+      <c r="P92">
+        <v>725</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>1189</v>
+      </c>
+      <c r="R92" t="s">
+        <v>1191</v>
+      </c>
+      <c r="S92" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T92" t="s">
+        <v>1198</v>
+      </c>
+      <c r="U92" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V92" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W92" s="20" t="s">
+        <v>1178</v>
+      </c>
+      <c r="X92" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="Y92" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z92" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB92" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC92" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD92" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE92" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF92" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="93" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A93" s="95">
+        <v>91</v>
+      </c>
+      <c r="B93" s="110" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D93" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E93" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F93" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G93">
+        <v>2</v>
+      </c>
+      <c r="H93" s="130" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I93" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J93" s="95">
+        <v>1</v>
+      </c>
+      <c r="K93" s="95">
+        <v>1</v>
+      </c>
+      <c r="L93" s="95">
+        <v>1</v>
+      </c>
+      <c r="M93" s="95">
+        <v>1</v>
+      </c>
+      <c r="N93" s="95">
+        <v>1</v>
+      </c>
+      <c r="P93">
+        <v>2958</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>1192</v>
+      </c>
+      <c r="R93" t="s">
+        <v>1194</v>
+      </c>
+      <c r="S93" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T93" t="s">
+        <v>1196</v>
+      </c>
+      <c r="U93" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V93" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W93" s="20" t="s">
+        <v>1179</v>
+      </c>
+      <c r="X93" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y93" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z93" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB93" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC93" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD93" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE93" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF93" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="94" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A94" s="95">
+        <v>92</v>
+      </c>
+      <c r="B94" s="110" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D94" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E94" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F94" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G94">
+        <v>2</v>
+      </c>
+      <c r="H94" s="130" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I94" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J94" s="95">
+        <v>1</v>
+      </c>
+      <c r="K94" s="95">
+        <v>1</v>
+      </c>
+      <c r="L94" s="95">
+        <v>1</v>
+      </c>
+      <c r="M94" s="95">
+        <v>1</v>
+      </c>
+      <c r="N94" s="95">
+        <v>1</v>
+      </c>
+      <c r="P94">
+        <v>725</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>1193</v>
+      </c>
+      <c r="R94" t="s">
+        <v>1195</v>
+      </c>
+      <c r="S94" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T94" t="s">
+        <v>1198</v>
+      </c>
+      <c r="U94" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V94" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W94" s="20" t="s">
+        <v>1179</v>
+      </c>
+      <c r="X94" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z94" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB94" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC94" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD94" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE94" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF94" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="95" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A95" s="95">
+        <v>93</v>
+      </c>
+      <c r="B95" s="110" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D95" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E95" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F95" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G95">
+        <v>2</v>
+      </c>
+      <c r="H95" s="130" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I95" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J95" s="95">
+        <v>1</v>
+      </c>
+      <c r="K95" s="95">
+        <v>1</v>
+      </c>
+      <c r="L95" s="95">
+        <v>1</v>
+      </c>
+      <c r="M95" s="95">
+        <v>1</v>
+      </c>
+      <c r="N95" s="95">
+        <v>1</v>
+      </c>
+      <c r="P95">
+        <v>2958</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>1188</v>
+      </c>
+      <c r="R95" t="s">
+        <v>1190</v>
+      </c>
+      <c r="S95" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T95" t="s">
+        <v>1196</v>
+      </c>
+      <c r="U95" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V95" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W95" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="X95" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="Y95" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z95" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB95" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC95" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD95" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE95" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF95" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="96" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A96" s="95">
+        <v>94</v>
+      </c>
+      <c r="B96" s="110" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D96" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E96" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F96" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G96">
+        <v>2</v>
+      </c>
+      <c r="H96" s="130" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I96" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J96" s="95">
+        <v>1</v>
+      </c>
+      <c r="K96" s="95">
+        <v>1</v>
+      </c>
+      <c r="L96" s="95">
+        <v>1</v>
+      </c>
+      <c r="M96" s="95">
+        <v>1</v>
+      </c>
+      <c r="N96" s="95">
+        <v>1</v>
+      </c>
+      <c r="P96">
+        <v>725</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>1189</v>
+      </c>
+      <c r="R96" t="s">
+        <v>1191</v>
+      </c>
+      <c r="S96" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T96" t="s">
+        <v>1198</v>
+      </c>
+      <c r="U96" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V96" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W96" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="X96" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="Y96" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z96" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA96" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB96" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC96" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD96" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE96" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF96" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="97" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A97" s="95">
+        <v>95</v>
+      </c>
+      <c r="B97" s="110" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D97" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E97" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F97" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G97">
+        <v>2</v>
+      </c>
+      <c r="H97" s="130" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I97" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J97" s="95">
+        <v>1</v>
+      </c>
+      <c r="K97" s="95">
+        <v>1</v>
+      </c>
+      <c r="L97" s="95">
+        <v>1</v>
+      </c>
+      <c r="M97" s="95">
+        <v>1</v>
+      </c>
+      <c r="N97" s="95">
+        <v>1</v>
+      </c>
+      <c r="P97">
+        <v>2958</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>1192</v>
+      </c>
+      <c r="R97" t="s">
+        <v>1194</v>
+      </c>
+      <c r="S97" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T97" t="s">
+        <v>1196</v>
+      </c>
+      <c r="U97" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V97" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W97" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="X97" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y97" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z97" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB97" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC97" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD97" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE97" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF97" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="98" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A98" s="95">
+        <v>96</v>
+      </c>
+      <c r="B98" s="110" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D98" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E98" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F98" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G98">
+        <v>2</v>
+      </c>
+      <c r="H98" s="130" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I98" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J98" s="95">
+        <v>1</v>
+      </c>
+      <c r="K98" s="95">
+        <v>1</v>
+      </c>
+      <c r="L98" s="95">
+        <v>1</v>
+      </c>
+      <c r="M98" s="95">
+        <v>1</v>
+      </c>
+      <c r="N98" s="95">
+        <v>1</v>
+      </c>
+      <c r="P98">
+        <v>725</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>1193</v>
+      </c>
+      <c r="R98" t="s">
+        <v>1195</v>
+      </c>
+      <c r="S98" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T98" t="s">
+        <v>1198</v>
+      </c>
+      <c r="U98" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V98" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W98" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="X98" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y98" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z98" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA98" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB98" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC98" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD98" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE98" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF98" s="26" t="s">
+        <v>1186</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_train_transformer-v2.xlsx
+++ b/dataset_train_transformer-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2024 Foundation model\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ADDD848-CA56-49D1-A755-34CED7C49CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735D1E5F-7F68-403D-9E33-E86723C4F498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18375" yWindow="2625" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3705" yWindow="1530" windowWidth="16785" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="64x64" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12093" uniqueCount="1203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12231" uniqueCount="1234">
   <si>
     <t>path_lr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4021,6 +4021,113 @@
   <si>
     <t>synprot-channe-1-64-granule</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-0-64-reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-0-128-reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-1-64-reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>synprot-channe-1-128-reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\confocal_reg_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\confocal_reg_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\confocal_reg_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\confocal_reg_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\STED_reg_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_0\STED_reg_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\STED_reg_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test\channel_1\STED_reg_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test_p64_s64_2d_reg_1.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\Task-assisted-GAN\transformed\SynapticProteinsDataset\SynProt_loc\test_p128_s128_2d_reg_1.txt</t>
+  </si>
+  <si>
+    <t>DL-SMLM-MT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>super-resolution with a scale factor of 8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fixed COS-7 cell line</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>microtubule</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cy3B (yellow)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>with a high numerical aperture (N.A.) oil-immersion objective (Plan Apo 100 × , N.A. = 1.45)</t>
+  </si>
+  <si>
+    <t>130 x 130 nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16.25 x 16.25 nm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stochastic optical reconstruction microscopy (STORM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dl-smlm-microtubule-128</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dl-smlm-microtubule-64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\DL-SMLM\transformed\Microtubules\train\channel_0\WF_up8_crop_64_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\DL-SMLM\transformed\Microtubules\train\channel_0\WF_up8_crop_64_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\DL-SMLM\transformed\Microtubules\train\channel_0\SR_crop_64_p64_s64_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\DL-SMLM\transformed\Microtubules\train\channel_0\SR_crop_64_p128_s128_2d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\DL-SMLM\transformed\Microtubules\train_p64_s64_2d_1.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\DL-SMLM\transformed\Microtubules\train_p128_s128_2d_1.txt</t>
   </si>
 </sst>
 </file>
@@ -4209,7 +4316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -4374,6 +4481,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -49954,7 +50067,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A163AA7F-4DF5-48A0-AE09-D011016C5669}">
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AF104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -56177,6 +56290,9 @@
       <c r="N66" s="95">
         <v>1</v>
       </c>
+      <c r="P66">
+        <v>1440</v>
+      </c>
       <c r="Q66" t="s">
         <v>1089</v>
       </c>
@@ -56269,6 +56385,9 @@
       <c r="N67" s="95">
         <v>1</v>
       </c>
+      <c r="P67">
+        <v>1350</v>
+      </c>
       <c r="Q67" t="s">
         <v>1095</v>
       </c>
@@ -56361,6 +56480,9 @@
       <c r="N68" s="95">
         <v>1</v>
       </c>
+      <c r="P68">
+        <v>4096</v>
+      </c>
       <c r="Q68" t="s">
         <v>1096</v>
       </c>
@@ -56453,6 +56575,9 @@
       <c r="N69" s="107">
         <v>1</v>
       </c>
+      <c r="P69" s="107">
+        <v>80</v>
+      </c>
       <c r="Q69" s="107" t="s">
         <v>1112</v>
       </c>
@@ -56545,6 +56670,9 @@
       <c r="N70" s="107">
         <v>1</v>
       </c>
+      <c r="P70" s="107">
+        <v>80</v>
+      </c>
       <c r="Q70" t="s">
         <v>1113</v>
       </c>
@@ -56637,6 +56765,9 @@
       <c r="N71" s="107">
         <v>1</v>
       </c>
+      <c r="P71" s="107">
+        <v>80</v>
+      </c>
       <c r="Q71" t="s">
         <v>1114</v>
       </c>
@@ -56729,6 +56860,9 @@
       <c r="N72" s="107">
         <v>1</v>
       </c>
+      <c r="P72" s="107">
+        <v>80</v>
+      </c>
       <c r="Q72" t="s">
         <v>1115</v>
       </c>
@@ -56821,7 +56955,9 @@
       <c r="N73" s="107">
         <v>1</v>
       </c>
-      <c r="P73" s="96"/>
+      <c r="P73" s="107">
+        <v>80</v>
+      </c>
       <c r="Q73" t="s">
         <v>1132</v>
       </c>
@@ -56914,6 +57050,9 @@
       <c r="N74" s="107">
         <v>1</v>
       </c>
+      <c r="P74" s="107">
+        <v>80</v>
+      </c>
       <c r="Q74" t="s">
         <v>1133</v>
       </c>
@@ -57006,6 +57145,9 @@
       <c r="N75" s="107">
         <v>1</v>
       </c>
+      <c r="P75" s="107">
+        <v>80</v>
+      </c>
       <c r="Q75" t="s">
         <v>1134</v>
       </c>
@@ -57098,6 +57240,9 @@
       <c r="N76" s="107">
         <v>1</v>
       </c>
+      <c r="P76" s="107">
+        <v>80</v>
+      </c>
       <c r="Q76" t="s">
         <v>1135</v>
       </c>
@@ -57190,6 +57335,9 @@
       <c r="N77" s="107">
         <v>1</v>
       </c>
+      <c r="P77" s="107">
+        <v>80</v>
+      </c>
       <c r="Q77" s="107" t="s">
         <v>1112</v>
       </c>
@@ -57282,6 +57430,9 @@
       <c r="N78" s="107">
         <v>1</v>
       </c>
+      <c r="P78" s="107">
+        <v>80</v>
+      </c>
       <c r="Q78" t="s">
         <v>1113</v>
       </c>
@@ -57374,6 +57525,9 @@
       <c r="N79" s="107">
         <v>1</v>
       </c>
+      <c r="P79" s="107">
+        <v>80</v>
+      </c>
       <c r="Q79" t="s">
         <v>1114</v>
       </c>
@@ -57466,6 +57620,9 @@
       <c r="N80" s="107">
         <v>1</v>
       </c>
+      <c r="P80" s="107">
+        <v>80</v>
+      </c>
       <c r="Q80" t="s">
         <v>1115</v>
       </c>
@@ -59223,6 +59380,576 @@
       </c>
       <c r="AF98" s="26" t="s">
         <v>1186</v>
+      </c>
+    </row>
+    <row r="99" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="138">
+        <v>97</v>
+      </c>
+      <c r="B99" s="102" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C99" s="107" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D99" s="102" t="s">
+        <v>941</v>
+      </c>
+      <c r="E99" s="102" t="s">
+        <v>976</v>
+      </c>
+      <c r="F99" s="102" t="s">
+        <v>942</v>
+      </c>
+      <c r="G99" s="107">
+        <v>2</v>
+      </c>
+      <c r="H99" s="102" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I99" s="102" t="s">
+        <v>11</v>
+      </c>
+      <c r="J99" s="138">
+        <v>1</v>
+      </c>
+      <c r="K99" s="138">
+        <v>1</v>
+      </c>
+      <c r="L99" s="138">
+        <v>1</v>
+      </c>
+      <c r="M99" s="138">
+        <v>1</v>
+      </c>
+      <c r="N99" s="138">
+        <v>1</v>
+      </c>
+      <c r="P99" s="107">
+        <v>2744</v>
+      </c>
+      <c r="Q99" s="107" t="s">
+        <v>1207</v>
+      </c>
+      <c r="R99" s="107" t="s">
+        <v>1211</v>
+      </c>
+      <c r="S99" s="138" t="s">
+        <v>914</v>
+      </c>
+      <c r="T99" s="107" t="s">
+        <v>1215</v>
+      </c>
+      <c r="U99" s="139" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V99" s="138" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W99" s="126" t="s">
+        <v>1178</v>
+      </c>
+      <c r="X99" s="140" t="s">
+        <v>849</v>
+      </c>
+      <c r="Y99" s="141" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z99" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA99" s="107" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB99" s="142" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC99" s="143" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD99" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE99" s="107" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF99" s="142" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="100" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A100" s="95">
+        <v>98</v>
+      </c>
+      <c r="B100" s="110" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D100" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E100" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F100" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100" s="130" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I100" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J100" s="95">
+        <v>1</v>
+      </c>
+      <c r="K100" s="95">
+        <v>1</v>
+      </c>
+      <c r="L100" s="95">
+        <v>1</v>
+      </c>
+      <c r="M100" s="95">
+        <v>1</v>
+      </c>
+      <c r="N100" s="95">
+        <v>1</v>
+      </c>
+      <c r="P100">
+        <v>672</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>1208</v>
+      </c>
+      <c r="R100" t="s">
+        <v>1212</v>
+      </c>
+      <c r="S100" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T100" t="s">
+        <v>1216</v>
+      </c>
+      <c r="U100" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V100" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W100" s="20" t="s">
+        <v>1178</v>
+      </c>
+      <c r="X100" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z100" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB100" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC100" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD100" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE100" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF100" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="101" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A101" s="95">
+        <v>99</v>
+      </c>
+      <c r="B101" s="110" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D101" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E101" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F101" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G101">
+        <v>2</v>
+      </c>
+      <c r="H101" s="130" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I101" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J101" s="95">
+        <v>1</v>
+      </c>
+      <c r="K101" s="95">
+        <v>1</v>
+      </c>
+      <c r="L101" s="95">
+        <v>1</v>
+      </c>
+      <c r="M101" s="95">
+        <v>1</v>
+      </c>
+      <c r="N101" s="95">
+        <v>1</v>
+      </c>
+      <c r="P101">
+        <v>2744</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>1209</v>
+      </c>
+      <c r="R101" t="s">
+        <v>1213</v>
+      </c>
+      <c r="S101" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T101" t="s">
+        <v>1215</v>
+      </c>
+      <c r="U101" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V101" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W101" s="20" t="s">
+        <v>1179</v>
+      </c>
+      <c r="X101" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z101" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB101" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC101" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD101" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE101" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF101" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="102" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A102" s="95">
+        <v>100</v>
+      </c>
+      <c r="B102" s="110" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D102" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E102" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F102" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G102">
+        <v>2</v>
+      </c>
+      <c r="H102" s="130" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I102" s="130" t="s">
+        <v>11</v>
+      </c>
+      <c r="J102" s="95">
+        <v>1</v>
+      </c>
+      <c r="K102" s="95">
+        <v>1</v>
+      </c>
+      <c r="L102" s="95">
+        <v>1</v>
+      </c>
+      <c r="M102" s="95">
+        <v>1</v>
+      </c>
+      <c r="N102" s="95">
+        <v>1</v>
+      </c>
+      <c r="P102">
+        <v>672</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>1210</v>
+      </c>
+      <c r="R102" t="s">
+        <v>1214</v>
+      </c>
+      <c r="S102" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T102" t="s">
+        <v>1216</v>
+      </c>
+      <c r="U102" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="V102" s="4" t="s">
+        <v>1181</v>
+      </c>
+      <c r="W102" s="20" t="s">
+        <v>1179</v>
+      </c>
+      <c r="X102" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z102" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA102" t="s">
+        <v>1183</v>
+      </c>
+      <c r="AB102" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="AC102" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD102" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE102" t="s">
+        <v>1185</v>
+      </c>
+      <c r="AF102" s="26" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="103" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="95">
+        <v>101</v>
+      </c>
+      <c r="B103" s="107" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C103" s="107" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D103" s="107" t="s">
+        <v>941</v>
+      </c>
+      <c r="E103" s="107" t="s">
+        <v>976</v>
+      </c>
+      <c r="F103" s="107" t="s">
+        <v>942</v>
+      </c>
+      <c r="G103" s="107">
+        <v>2</v>
+      </c>
+      <c r="H103" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="I103" s="107" t="s">
+        <v>11</v>
+      </c>
+      <c r="J103" s="107">
+        <v>1</v>
+      </c>
+      <c r="K103" s="107">
+        <v>1</v>
+      </c>
+      <c r="L103" s="107">
+        <v>1</v>
+      </c>
+      <c r="M103" s="107">
+        <v>1</v>
+      </c>
+      <c r="N103" s="107">
+        <v>1</v>
+      </c>
+      <c r="P103" s="107">
+        <v>900</v>
+      </c>
+      <c r="Q103" s="107" t="s">
+        <v>1228</v>
+      </c>
+      <c r="R103" s="107" t="s">
+        <v>1230</v>
+      </c>
+      <c r="S103" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T103" s="107" t="s">
+        <v>1232</v>
+      </c>
+      <c r="U103" s="107" t="s">
+        <v>1218</v>
+      </c>
+      <c r="V103" s="107" t="s">
+        <v>1219</v>
+      </c>
+      <c r="W103" s="107" t="s">
+        <v>1220</v>
+      </c>
+      <c r="X103" s="107" t="s">
+        <v>1221</v>
+      </c>
+      <c r="Y103" s="107" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z103" s="107" t="s">
+        <v>761</v>
+      </c>
+      <c r="AA103" s="107" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AB103" s="107" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AC103" s="107" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD103" s="107" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AE103" s="107" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AF103" s="107" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="104" spans="1:32" s="107" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="95">
+        <v>102</v>
+      </c>
+      <c r="B104" s="107" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C104" s="107" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D104" s="107" t="s">
+        <v>941</v>
+      </c>
+      <c r="E104" s="107" t="s">
+        <v>976</v>
+      </c>
+      <c r="F104" s="107" t="s">
+        <v>942</v>
+      </c>
+      <c r="G104" s="107">
+        <v>2</v>
+      </c>
+      <c r="H104" s="107" t="s">
+        <v>105</v>
+      </c>
+      <c r="I104" s="107" t="s">
+        <v>11</v>
+      </c>
+      <c r="J104" s="107">
+        <v>1</v>
+      </c>
+      <c r="K104" s="107">
+        <v>1</v>
+      </c>
+      <c r="L104" s="107">
+        <v>1</v>
+      </c>
+      <c r="M104" s="107">
+        <v>1</v>
+      </c>
+      <c r="N104" s="107">
+        <v>1</v>
+      </c>
+      <c r="P104" s="107">
+        <v>225</v>
+      </c>
+      <c r="Q104" s="107" t="s">
+        <v>1229</v>
+      </c>
+      <c r="R104" s="107" t="s">
+        <v>1231</v>
+      </c>
+      <c r="S104" s="95" t="s">
+        <v>914</v>
+      </c>
+      <c r="T104" s="107" t="s">
+        <v>1233</v>
+      </c>
+      <c r="U104" s="107" t="s">
+        <v>1218</v>
+      </c>
+      <c r="V104" s="107" t="s">
+        <v>1219</v>
+      </c>
+      <c r="W104" s="107" t="s">
+        <v>1220</v>
+      </c>
+      <c r="X104" s="107" t="s">
+        <v>1221</v>
+      </c>
+      <c r="Y104" s="107" t="s">
+        <v>996</v>
+      </c>
+      <c r="Z104" s="107" t="s">
+        <v>761</v>
+      </c>
+      <c r="AA104" s="107" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AB104" s="107" t="s">
+        <v>1223</v>
+      </c>
+      <c r="AC104" s="107" t="s">
+        <v>996</v>
+      </c>
+      <c r="AD104" s="107" t="s">
+        <v>1225</v>
+      </c>
+      <c r="AE104" s="107" t="s">
+        <v>1222</v>
+      </c>
+      <c r="AF104" s="107" t="s">
+        <v>1224</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_train_transformer-v2.xlsx
+++ b/dataset_train_transformer-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2024 Foundation model\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735D1E5F-7F68-403D-9E33-E86723C4F498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DBAB27-BE6B-4694-91D3-1DA0E4F64695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3705" yWindow="1530" windowWidth="16785" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1335" yWindow="2370" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="64x64" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12231" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12254" uniqueCount="1238">
   <si>
     <t>path_lr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4128,6 +4128,19 @@
   </si>
   <si>
     <t>E:\qiqilu\datasets\DL-SMLM\transformed\Microtubules\train_p128_s128_2d_1.txt</t>
+  </si>
+  <si>
+    <t>rcan3d-c2s-mt-dcv-mc-3d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_MT\train_p64_s64_3d_1.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_MT\train\channel_0\confocal_p64_s64_3d</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets\RCAN3D\transformed\C2S_MT\train\channel_0\STED_p64_s64_3d</t>
   </si>
 </sst>
 </file>
@@ -4491,7 +4504,35 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="469">
+  <dxfs count="473">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -43367,122 +43408,122 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F480:F1048576 F1:F478">
-    <cfRule type="containsText" dxfId="468" priority="121" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="472" priority="121" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="467" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="471" priority="124" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="466" priority="125" operator="equal">
+    <cfRule type="cellIs" dxfId="470" priority="125" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="465" priority="126" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="469" priority="126" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F195">
-    <cfRule type="containsText" dxfId="464" priority="61" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="468" priority="61" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F195)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="463" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="467" priority="62" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="462" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="466" priority="63" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="461" priority="64" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="465" priority="64" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F195)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F200">
-    <cfRule type="containsText" dxfId="460" priority="57" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="464" priority="57" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F200)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="459" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="463" priority="58" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="458" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="462" priority="59" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="457" priority="60" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="461" priority="60" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F200)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F205">
-    <cfRule type="containsText" dxfId="456" priority="53" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="460" priority="53" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F205)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="455" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="459" priority="54" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="454" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="458" priority="55" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="453" priority="56" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="457" priority="56" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F205)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F210">
-    <cfRule type="containsText" dxfId="452" priority="45" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="456" priority="45" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F210)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="451" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="455" priority="46" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="450" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="454" priority="47" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="449" priority="48" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="453" priority="48" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F210)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F215">
-    <cfRule type="containsText" dxfId="448" priority="41" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="452" priority="41" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F215)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="447" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="451" priority="42" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="446" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="450" priority="43" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="445" priority="44" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="449" priority="44" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F215)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F220">
-    <cfRule type="containsText" dxfId="444" priority="33" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="448" priority="33" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F220)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="443" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="447" priority="34" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="442" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="446" priority="35" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="441" priority="36" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="445" priority="36" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F220)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C473:C479">
-    <cfRule type="cellIs" dxfId="440" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="444" priority="7" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="439" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="443" priority="8" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F479">
-    <cfRule type="containsText" dxfId="438" priority="9" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="442" priority="9" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F479)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="437" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="441" priority="10" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="436" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="440" priority="11" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="435" priority="12" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="439" priority="12" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F479)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49900,164 +49941,164 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F1:F67">
-    <cfRule type="containsText" dxfId="434" priority="93" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="438" priority="93" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="433" priority="94" operator="equal">
+    <cfRule type="cellIs" dxfId="437" priority="94" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="432" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="436" priority="95" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="431" priority="96" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="435" priority="96" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="containsText" dxfId="430" priority="43" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="434" priority="43" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F54)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="429" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="433" priority="44" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="428" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="432" priority="45" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="427" priority="46" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="431" priority="46" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F54)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="containsText" dxfId="426" priority="39" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="430" priority="39" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F59)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="425" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="429" priority="40" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="424" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="428" priority="41" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="423" priority="42" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="427" priority="42" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="containsText" dxfId="422" priority="35" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="426" priority="35" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F64)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="421" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="425" priority="36" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="420" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="424" priority="37" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="419" priority="38" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="423" priority="38" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C65:C67">
-    <cfRule type="cellIs" dxfId="418" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="422" priority="33" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="417" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="421" priority="34" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F68:F70">
-    <cfRule type="containsText" dxfId="416" priority="25" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="420" priority="25" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F68)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="415" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="419" priority="26" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="414" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="418" priority="27" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="413" priority="28" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="417" priority="28" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F68)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F71:F75">
-    <cfRule type="containsText" dxfId="412" priority="21" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="416" priority="21" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F71)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="411" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="415" priority="22" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="410" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="414" priority="23" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="409" priority="24" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="413" priority="24" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F71)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F75">
-    <cfRule type="containsText" dxfId="408" priority="17" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="412" priority="17" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F75)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="407" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="411" priority="18" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="406" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="410" priority="19" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="405" priority="20" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="409" priority="20" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F75)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F76:F83">
-    <cfRule type="containsText" dxfId="404" priority="13" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="408" priority="13" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F76)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="403" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="407" priority="14" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="402" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="406" priority="15" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="401" priority="16" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="405" priority="16" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84:F85">
-    <cfRule type="containsText" dxfId="400" priority="9" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="404" priority="9" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F84)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="399" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="403" priority="10" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="398" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="402" priority="11" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="397" priority="12" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="401" priority="12" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F84)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F86:F87">
-    <cfRule type="containsText" dxfId="396" priority="5" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="400" priority="5" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F86)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="395" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="399" priority="6" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="394" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="398" priority="7" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="393" priority="8" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="397" priority="8" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F86)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88:F89">
-    <cfRule type="containsText" dxfId="392" priority="1" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="396" priority="1" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",F88)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="391" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="395" priority="2" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="390" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="394" priority="3" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="389" priority="4" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="393" priority="4" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",F88)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -50067,7 +50108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A163AA7F-4DF5-48A0-AE09-D011016C5669}">
-  <dimension ref="A1:AF104"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.625" customWidth="1"/>
@@ -59952,1292 +59993,1401 @@
         <v>1224</v>
       </c>
     </row>
+    <row r="105" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A105" s="101">
+        <v>103</v>
+      </c>
+      <c r="B105" s="102" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C105" s="102" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D105" s="130" t="s">
+        <v>941</v>
+      </c>
+      <c r="E105" s="130" t="s">
+        <v>976</v>
+      </c>
+      <c r="F105" s="130" t="s">
+        <v>942</v>
+      </c>
+      <c r="G105" s="95">
+        <v>2</v>
+      </c>
+      <c r="H105" s="114" t="s">
+        <v>105</v>
+      </c>
+      <c r="I105" s="130" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105" s="101">
+        <v>6</v>
+      </c>
+      <c r="K105" s="101">
+        <v>6</v>
+      </c>
+      <c r="L105" s="131">
+        <v>1</v>
+      </c>
+      <c r="M105" s="132">
+        <v>1</v>
+      </c>
+      <c r="N105" s="95">
+        <v>1</v>
+      </c>
+      <c r="P105">
+        <v>1440</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>1236</v>
+      </c>
+      <c r="R105" t="s">
+        <v>1237</v>
+      </c>
+      <c r="S105" s="73" t="s">
+        <v>914</v>
+      </c>
+      <c r="T105" t="s">
+        <v>1235</v>
+      </c>
+      <c r="U105" s="133" t="s">
+        <v>95</v>
+      </c>
+      <c r="V105" s="101" t="s">
+        <v>840</v>
+      </c>
+      <c r="W105" s="126" t="s">
+        <v>775</v>
+      </c>
+      <c r="X105" s="107" t="s">
+        <v>841</v>
+      </c>
+      <c r="Y105" s="101" t="s">
+        <v>842</v>
+      </c>
+      <c r="Z105" s="136" t="s">
+        <v>765</v>
+      </c>
+      <c r="AA105" s="137" t="s">
+        <v>901</v>
+      </c>
+      <c r="AB105" s="129" t="s">
+        <v>843</v>
+      </c>
+      <c r="AC105" s="101" t="s">
+        <v>844</v>
+      </c>
+      <c r="AD105" s="136" t="s">
+        <v>845</v>
+      </c>
+      <c r="AE105" s="137" t="s">
+        <v>901</v>
+      </c>
+      <c r="AF105" s="129" t="s">
+        <v>843</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I21 I28 I35 I42:I45 I52 I59 I2:K2 I3:I5 J3:K68">
-    <cfRule type="containsText" dxfId="388" priority="464" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="392" priority="468" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I2)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="387" priority="465" operator="equal">
+    <cfRule type="cellIs" dxfId="391" priority="469" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="386" priority="466" operator="equal">
+    <cfRule type="cellIs" dxfId="390" priority="470" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="385" priority="467" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="389" priority="471" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:F2 F3:F5 E3:E6 E8 E10 E12 E52 E59 E14 E16 E18:E22 E28:E29 E35 E38 E42:E45">
-    <cfRule type="cellIs" dxfId="384" priority="462" operator="equal">
+    <cfRule type="cellIs" dxfId="388" priority="466" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="383" priority="463" operator="equal">
+    <cfRule type="cellIs" dxfId="387" priority="467" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1:K1">
-    <cfRule type="containsText" dxfId="382" priority="458" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="386" priority="462" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I1)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="381" priority="459" operator="equal">
+    <cfRule type="cellIs" dxfId="385" priority="463" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="380" priority="460" operator="equal">
+    <cfRule type="cellIs" dxfId="384" priority="464" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="379" priority="461" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="383" priority="465" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:F1">
-    <cfRule type="cellIs" dxfId="378" priority="456" operator="equal">
+    <cfRule type="cellIs" dxfId="382" priority="460" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="377" priority="457" operator="equal">
+    <cfRule type="cellIs" dxfId="381" priority="461" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6 I8 I10 I12 I14 I16">
-    <cfRule type="containsText" dxfId="376" priority="452" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="380" priority="456" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I6)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="375" priority="453" operator="equal">
+    <cfRule type="cellIs" dxfId="379" priority="457" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="374" priority="454" operator="equal">
+    <cfRule type="cellIs" dxfId="378" priority="458" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="373" priority="455" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="377" priority="459" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6 F8 F10 F12 F14 F16">
-    <cfRule type="cellIs" dxfId="372" priority="450" operator="equal">
+    <cfRule type="cellIs" dxfId="376" priority="454" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="371" priority="451" operator="equal">
+    <cfRule type="cellIs" dxfId="375" priority="455" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F6 F8 F10 F12 F14 F16">
-    <cfRule type="cellIs" dxfId="370" priority="449" operator="equal">
+    <cfRule type="cellIs" dxfId="374" priority="453" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I18:I20">
-    <cfRule type="containsText" dxfId="369" priority="445" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="373" priority="449" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I18)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="368" priority="446" operator="equal">
+    <cfRule type="cellIs" dxfId="372" priority="450" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="447" operator="equal">
+    <cfRule type="cellIs" dxfId="371" priority="451" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="366" priority="448" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="370" priority="452" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F22 F52 F59 F28:F29 F35 F38 F42:F45">
-    <cfRule type="cellIs" dxfId="365" priority="443" operator="equal">
+    <cfRule type="cellIs" dxfId="369" priority="447" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="364" priority="444" operator="equal">
+    <cfRule type="cellIs" dxfId="368" priority="448" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18:F22 F52 F59 F28:F29 F35 F38 F42:F45">
-    <cfRule type="cellIs" dxfId="363" priority="442" operator="equal">
+    <cfRule type="cellIs" dxfId="367" priority="446" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I22">
-    <cfRule type="containsText" dxfId="362" priority="429" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="366" priority="433" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I22)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="361" priority="430" operator="equal">
+    <cfRule type="cellIs" dxfId="365" priority="434" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="360" priority="431" operator="equal">
+    <cfRule type="cellIs" dxfId="364" priority="435" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="359" priority="432" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="363" priority="436" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29">
-    <cfRule type="containsText" dxfId="358" priority="420" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="362" priority="424" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I29)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="357" priority="421" operator="equal">
+    <cfRule type="cellIs" dxfId="361" priority="425" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="356" priority="422" operator="equal">
+    <cfRule type="cellIs" dxfId="360" priority="426" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="355" priority="423" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="359" priority="427" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I38">
-    <cfRule type="containsText" dxfId="354" priority="411" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="358" priority="415" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I38)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="353" priority="412" operator="equal">
+    <cfRule type="cellIs" dxfId="357" priority="416" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="352" priority="413" operator="equal">
+    <cfRule type="cellIs" dxfId="356" priority="417" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="351" priority="414" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="355" priority="418" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="cellIs" dxfId="350" priority="404" operator="equal">
+    <cfRule type="cellIs" dxfId="354" priority="408" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="349" priority="405" operator="equal">
+    <cfRule type="cellIs" dxfId="353" priority="409" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7">
-    <cfRule type="containsText" dxfId="348" priority="400" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="352" priority="404" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I7)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="347" priority="401" operator="equal">
+    <cfRule type="cellIs" dxfId="351" priority="405" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="346" priority="402" operator="equal">
+    <cfRule type="cellIs" dxfId="350" priority="406" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="345" priority="403" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="349" priority="407" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="344" priority="398" operator="equal">
+    <cfRule type="cellIs" dxfId="348" priority="402" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="343" priority="399" operator="equal">
+    <cfRule type="cellIs" dxfId="347" priority="403" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="cellIs" dxfId="342" priority="397" operator="equal">
+    <cfRule type="cellIs" dxfId="346" priority="401" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E9">
-    <cfRule type="cellIs" dxfId="341" priority="395" operator="equal">
+    <cfRule type="cellIs" dxfId="345" priority="399" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="340" priority="396" operator="equal">
+    <cfRule type="cellIs" dxfId="344" priority="400" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9">
-    <cfRule type="containsText" dxfId="339" priority="391" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="343" priority="395" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I9)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="338" priority="392" operator="equal">
+    <cfRule type="cellIs" dxfId="342" priority="396" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="337" priority="393" operator="equal">
+    <cfRule type="cellIs" dxfId="341" priority="397" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="336" priority="394" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="340" priority="398" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="335" priority="389" operator="equal">
+    <cfRule type="cellIs" dxfId="339" priority="393" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="334" priority="390" operator="equal">
+    <cfRule type="cellIs" dxfId="338" priority="394" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" dxfId="333" priority="388" operator="equal">
+    <cfRule type="cellIs" dxfId="337" priority="392" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="cellIs" dxfId="332" priority="386" operator="equal">
+    <cfRule type="cellIs" dxfId="336" priority="390" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="331" priority="387" operator="equal">
+    <cfRule type="cellIs" dxfId="335" priority="391" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11">
-    <cfRule type="containsText" dxfId="330" priority="382" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="334" priority="386" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I11)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="329" priority="383" operator="equal">
+    <cfRule type="cellIs" dxfId="333" priority="387" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="328" priority="384" operator="equal">
+    <cfRule type="cellIs" dxfId="332" priority="388" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="327" priority="385" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="331" priority="389" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="cellIs" dxfId="326" priority="380" operator="equal">
+    <cfRule type="cellIs" dxfId="330" priority="384" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="325" priority="381" operator="equal">
+    <cfRule type="cellIs" dxfId="329" priority="385" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="cellIs" dxfId="324" priority="379" operator="equal">
+    <cfRule type="cellIs" dxfId="328" priority="383" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I46">
-    <cfRule type="containsText" dxfId="323" priority="375" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="327" priority="379" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I46)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="376" operator="equal">
+    <cfRule type="cellIs" dxfId="326" priority="380" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="321" priority="377" operator="equal">
+    <cfRule type="cellIs" dxfId="325" priority="381" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="320" priority="378" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="324" priority="382" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I46)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E46">
-    <cfRule type="cellIs" dxfId="319" priority="373" operator="equal">
+    <cfRule type="cellIs" dxfId="323" priority="377" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="374" operator="equal">
+    <cfRule type="cellIs" dxfId="322" priority="378" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="cellIs" dxfId="317" priority="371" operator="equal">
+    <cfRule type="cellIs" dxfId="321" priority="375" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="372" operator="equal">
+    <cfRule type="cellIs" dxfId="320" priority="376" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="cellIs" dxfId="315" priority="370" operator="equal">
+    <cfRule type="cellIs" dxfId="319" priority="374" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I53">
-    <cfRule type="containsText" dxfId="314" priority="366" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="318" priority="370" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I53)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="313" priority="367" operator="equal">
+    <cfRule type="cellIs" dxfId="317" priority="371" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="368" operator="equal">
+    <cfRule type="cellIs" dxfId="316" priority="372" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="311" priority="369" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="315" priority="373" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I53)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E53">
-    <cfRule type="cellIs" dxfId="310" priority="364" operator="equal">
+    <cfRule type="cellIs" dxfId="314" priority="368" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="309" priority="365" operator="equal">
+    <cfRule type="cellIs" dxfId="313" priority="369" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="cellIs" dxfId="308" priority="362" operator="equal">
+    <cfRule type="cellIs" dxfId="312" priority="366" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="307" priority="363" operator="equal">
+    <cfRule type="cellIs" dxfId="311" priority="367" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53">
-    <cfRule type="cellIs" dxfId="306" priority="361" operator="equal">
+    <cfRule type="cellIs" dxfId="310" priority="365" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I60">
-    <cfRule type="containsText" dxfId="305" priority="357" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="309" priority="361" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I60)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="358" operator="equal">
+    <cfRule type="cellIs" dxfId="308" priority="362" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="359" operator="equal">
+    <cfRule type="cellIs" dxfId="307" priority="363" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="302" priority="360" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="306" priority="364" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I60)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E60">
-    <cfRule type="cellIs" dxfId="301" priority="355" operator="equal">
+    <cfRule type="cellIs" dxfId="305" priority="359" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="356" operator="equal">
+    <cfRule type="cellIs" dxfId="304" priority="360" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60">
-    <cfRule type="cellIs" dxfId="299" priority="353" operator="equal">
+    <cfRule type="cellIs" dxfId="303" priority="357" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="354" operator="equal">
+    <cfRule type="cellIs" dxfId="302" priority="358" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F60">
-    <cfRule type="cellIs" dxfId="297" priority="352" operator="equal">
+    <cfRule type="cellIs" dxfId="301" priority="356" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E13">
-    <cfRule type="cellIs" dxfId="296" priority="350" operator="equal">
+    <cfRule type="cellIs" dxfId="300" priority="354" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="295" priority="351" operator="equal">
+    <cfRule type="cellIs" dxfId="299" priority="355" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I13">
-    <cfRule type="containsText" dxfId="294" priority="346" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="298" priority="350" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I13)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="293" priority="347" operator="equal">
+    <cfRule type="cellIs" dxfId="297" priority="351" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="348" operator="equal">
+    <cfRule type="cellIs" dxfId="296" priority="352" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="291" priority="349" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="295" priority="353" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" dxfId="290" priority="344" operator="equal">
+    <cfRule type="cellIs" dxfId="294" priority="348" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="345" operator="equal">
+    <cfRule type="cellIs" dxfId="293" priority="349" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="cellIs" dxfId="288" priority="343" operator="equal">
+    <cfRule type="cellIs" dxfId="292" priority="347" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E15">
-    <cfRule type="cellIs" dxfId="287" priority="341" operator="equal">
+    <cfRule type="cellIs" dxfId="291" priority="345" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="286" priority="342" operator="equal">
+    <cfRule type="cellIs" dxfId="290" priority="346" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I15">
-    <cfRule type="containsText" dxfId="285" priority="337" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="289" priority="341" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I15)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="284" priority="338" operator="equal">
+    <cfRule type="cellIs" dxfId="288" priority="342" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="283" priority="339" operator="equal">
+    <cfRule type="cellIs" dxfId="287" priority="343" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="282" priority="340" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="286" priority="344" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="cellIs" dxfId="281" priority="335" operator="equal">
+    <cfRule type="cellIs" dxfId="285" priority="339" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="336" operator="equal">
+    <cfRule type="cellIs" dxfId="284" priority="340" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="cellIs" dxfId="279" priority="334" operator="equal">
+    <cfRule type="cellIs" dxfId="283" priority="338" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E17">
-    <cfRule type="cellIs" dxfId="278" priority="332" operator="equal">
+    <cfRule type="cellIs" dxfId="282" priority="336" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="277" priority="333" operator="equal">
+    <cfRule type="cellIs" dxfId="281" priority="337" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I17">
-    <cfRule type="containsText" dxfId="276" priority="328" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="280" priority="332" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I17)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="275" priority="329" operator="equal">
+    <cfRule type="cellIs" dxfId="279" priority="333" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="330" operator="equal">
+    <cfRule type="cellIs" dxfId="278" priority="334" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="273" priority="331" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="277" priority="335" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="cellIs" dxfId="272" priority="326" operator="equal">
+    <cfRule type="cellIs" dxfId="276" priority="330" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="271" priority="327" operator="equal">
+    <cfRule type="cellIs" dxfId="275" priority="331" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="cellIs" dxfId="270" priority="325" operator="equal">
+    <cfRule type="cellIs" dxfId="274" priority="329" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E23">
-    <cfRule type="cellIs" dxfId="269" priority="323" operator="equal">
+    <cfRule type="cellIs" dxfId="273" priority="327" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="324" operator="equal">
+    <cfRule type="cellIs" dxfId="272" priority="328" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="cellIs" dxfId="267" priority="321" operator="equal">
+    <cfRule type="cellIs" dxfId="271" priority="325" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="266" priority="322" operator="equal">
+    <cfRule type="cellIs" dxfId="270" priority="326" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23">
-    <cfRule type="cellIs" dxfId="265" priority="320" operator="equal">
+    <cfRule type="cellIs" dxfId="269" priority="324" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="264" priority="316" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="268" priority="320" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I23)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="263" priority="317" operator="equal">
+    <cfRule type="cellIs" dxfId="267" priority="321" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="318" operator="equal">
+    <cfRule type="cellIs" dxfId="266" priority="322" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="261" priority="319" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="265" priority="323" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="cellIs" dxfId="260" priority="314" operator="equal">
+    <cfRule type="cellIs" dxfId="264" priority="318" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="259" priority="315" operator="equal">
+    <cfRule type="cellIs" dxfId="263" priority="319" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="cellIs" dxfId="258" priority="312" operator="equal">
+    <cfRule type="cellIs" dxfId="262" priority="316" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="257" priority="313" operator="equal">
+    <cfRule type="cellIs" dxfId="261" priority="317" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="cellIs" dxfId="256" priority="311" operator="equal">
+    <cfRule type="cellIs" dxfId="260" priority="315" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24">
-    <cfRule type="containsText" dxfId="255" priority="307" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="259" priority="311" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I24)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="254" priority="308" operator="equal">
+    <cfRule type="cellIs" dxfId="258" priority="312" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="253" priority="309" operator="equal">
+    <cfRule type="cellIs" dxfId="257" priority="313" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="252" priority="310" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="256" priority="314" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I24)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
-    <cfRule type="cellIs" dxfId="251" priority="305" operator="equal">
+    <cfRule type="cellIs" dxfId="255" priority="309" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="306" operator="equal">
+    <cfRule type="cellIs" dxfId="254" priority="310" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30">
-    <cfRule type="cellIs" dxfId="249" priority="303" operator="equal">
+    <cfRule type="cellIs" dxfId="253" priority="307" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="248" priority="304" operator="equal">
+    <cfRule type="cellIs" dxfId="252" priority="308" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30">
-    <cfRule type="cellIs" dxfId="247" priority="302" operator="equal">
+    <cfRule type="cellIs" dxfId="251" priority="306" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I30">
-    <cfRule type="containsText" dxfId="246" priority="298" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="250" priority="302" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I30)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="245" priority="299" operator="equal">
+    <cfRule type="cellIs" dxfId="249" priority="303" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="244" priority="300" operator="equal">
+    <cfRule type="cellIs" dxfId="248" priority="304" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="243" priority="301" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="247" priority="305" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="cellIs" dxfId="242" priority="296" operator="equal">
+    <cfRule type="cellIs" dxfId="246" priority="300" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="297" operator="equal">
+    <cfRule type="cellIs" dxfId="245" priority="301" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="cellIs" dxfId="240" priority="294" operator="equal">
+    <cfRule type="cellIs" dxfId="244" priority="298" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="239" priority="295" operator="equal">
+    <cfRule type="cellIs" dxfId="243" priority="299" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F31">
-    <cfRule type="cellIs" dxfId="238" priority="293" operator="equal">
+    <cfRule type="cellIs" dxfId="242" priority="297" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="237" priority="289" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="241" priority="293" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I31)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="236" priority="290" operator="equal">
+    <cfRule type="cellIs" dxfId="240" priority="294" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="291" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="295" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="234" priority="292" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="238" priority="296" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I37">
-    <cfRule type="containsText" dxfId="233" priority="271" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="237" priority="275" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I37)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="272" operator="equal">
+    <cfRule type="cellIs" dxfId="236" priority="276" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="273" operator="equal">
+    <cfRule type="cellIs" dxfId="235" priority="277" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="230" priority="274" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="234" priority="278" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="cellIs" dxfId="229" priority="199" operator="equal">
+    <cfRule type="cellIs" dxfId="233" priority="203" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E36">
-    <cfRule type="cellIs" dxfId="228" priority="287" operator="equal">
+    <cfRule type="cellIs" dxfId="232" priority="291" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="227" priority="288" operator="equal">
+    <cfRule type="cellIs" dxfId="231" priority="292" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="cellIs" dxfId="226" priority="285" operator="equal">
+    <cfRule type="cellIs" dxfId="230" priority="289" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="225" priority="286" operator="equal">
+    <cfRule type="cellIs" dxfId="229" priority="290" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36">
-    <cfRule type="cellIs" dxfId="224" priority="284" operator="equal">
+    <cfRule type="cellIs" dxfId="228" priority="288" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I36">
-    <cfRule type="containsText" dxfId="223" priority="280" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="227" priority="284" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I36)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="281" operator="equal">
+    <cfRule type="cellIs" dxfId="226" priority="285" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="221" priority="282" operator="equal">
+    <cfRule type="cellIs" dxfId="225" priority="286" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="220" priority="283" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="224" priority="287" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37">
-    <cfRule type="cellIs" dxfId="219" priority="278" operator="equal">
+    <cfRule type="cellIs" dxfId="223" priority="282" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="218" priority="279" operator="equal">
+    <cfRule type="cellIs" dxfId="222" priority="283" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="cellIs" dxfId="217" priority="276" operator="equal">
+    <cfRule type="cellIs" dxfId="221" priority="280" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="216" priority="277" operator="equal">
+    <cfRule type="cellIs" dxfId="220" priority="281" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F37">
-    <cfRule type="cellIs" dxfId="215" priority="275" operator="equal">
+    <cfRule type="cellIs" dxfId="219" priority="279" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I47">
-    <cfRule type="containsText" dxfId="214" priority="213" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="218" priority="217" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I47)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="213" priority="214" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="218" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="212" priority="215" operator="equal">
+    <cfRule type="cellIs" dxfId="216" priority="219" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="211" priority="216" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="215" priority="220" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I47)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47">
-    <cfRule type="cellIs" dxfId="210" priority="211" operator="equal">
+    <cfRule type="cellIs" dxfId="214" priority="215" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="209" priority="212" operator="equal">
+    <cfRule type="cellIs" dxfId="213" priority="216" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47">
-    <cfRule type="cellIs" dxfId="208" priority="209" operator="equal">
+    <cfRule type="cellIs" dxfId="212" priority="213" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="210" operator="equal">
+    <cfRule type="cellIs" dxfId="211" priority="214" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F47">
-    <cfRule type="cellIs" dxfId="206" priority="208" operator="equal">
+    <cfRule type="cellIs" dxfId="210" priority="212" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48">
-    <cfRule type="containsText" dxfId="205" priority="204" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="209" priority="208" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I48)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="205" operator="equal">
+    <cfRule type="cellIs" dxfId="208" priority="209" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="203" priority="206" operator="equal">
+    <cfRule type="cellIs" dxfId="207" priority="210" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="202" priority="207" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="206" priority="211" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I48)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E48">
-    <cfRule type="cellIs" dxfId="201" priority="202" operator="equal">
+    <cfRule type="cellIs" dxfId="205" priority="206" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="200" priority="203" operator="equal">
+    <cfRule type="cellIs" dxfId="204" priority="207" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="cellIs" dxfId="199" priority="200" operator="equal">
+    <cfRule type="cellIs" dxfId="203" priority="204" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="201" operator="equal">
+    <cfRule type="cellIs" dxfId="202" priority="205" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I54">
-    <cfRule type="containsText" dxfId="197" priority="195" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="201" priority="199" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I54)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="196" operator="equal">
+    <cfRule type="cellIs" dxfId="200" priority="200" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="197" operator="equal">
+    <cfRule type="cellIs" dxfId="199" priority="201" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="194" priority="198" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="198" priority="202" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I54)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E54">
-    <cfRule type="cellIs" dxfId="193" priority="193" operator="equal">
+    <cfRule type="cellIs" dxfId="197" priority="197" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="194" operator="equal">
+    <cfRule type="cellIs" dxfId="196" priority="198" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="cellIs" dxfId="191" priority="191" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="195" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="190" priority="192" operator="equal">
+    <cfRule type="cellIs" dxfId="194" priority="196" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F54">
-    <cfRule type="cellIs" dxfId="189" priority="190" operator="equal">
+    <cfRule type="cellIs" dxfId="193" priority="194" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I55">
-    <cfRule type="containsText" dxfId="188" priority="186" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="192" priority="190" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I55)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="187" operator="equal">
+    <cfRule type="cellIs" dxfId="191" priority="191" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="186" priority="188" operator="equal">
+    <cfRule type="cellIs" dxfId="190" priority="192" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="185" priority="189" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="189" priority="193" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E55">
-    <cfRule type="cellIs" dxfId="184" priority="184" operator="equal">
+    <cfRule type="cellIs" dxfId="188" priority="188" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="185" operator="equal">
+    <cfRule type="cellIs" dxfId="187" priority="189" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="cellIs" dxfId="182" priority="182" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="186" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="183" operator="equal">
+    <cfRule type="cellIs" dxfId="185" priority="187" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55">
-    <cfRule type="cellIs" dxfId="180" priority="181" operator="equal">
+    <cfRule type="cellIs" dxfId="184" priority="185" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I61">
-    <cfRule type="containsText" dxfId="179" priority="177" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="183" priority="181" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I61)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="178" priority="178" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="182" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="179" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="183" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="176" priority="180" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="180" priority="184" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I61)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E61">
-    <cfRule type="cellIs" dxfId="175" priority="175" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="179" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="176" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="180" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F61">
-    <cfRule type="cellIs" dxfId="173" priority="173" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="177" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="174" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="178" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F61">
-    <cfRule type="cellIs" dxfId="171" priority="172" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="176" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I62">
-    <cfRule type="containsText" dxfId="170" priority="168" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="174" priority="172" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I62)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="169" operator="equal">
+    <cfRule type="cellIs" dxfId="173" priority="173" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="170" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="174" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="167" priority="171" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="171" priority="175" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I62)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62">
-    <cfRule type="cellIs" dxfId="166" priority="166" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="170" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="167" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="171" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="cellIs" dxfId="164" priority="164" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="168" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="165" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="169" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="cellIs" dxfId="162" priority="163" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="167" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49">
-    <cfRule type="cellIs" dxfId="161" priority="154" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="158" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I49">
-    <cfRule type="containsText" dxfId="160" priority="159" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="164" priority="163" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I49)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="159" priority="160" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="164" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="161" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="165" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="157" priority="162" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="161" priority="166" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I49)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E49">
-    <cfRule type="cellIs" dxfId="156" priority="157" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="161" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="155" priority="158" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="162" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49">
-    <cfRule type="cellIs" dxfId="154" priority="155" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="159" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="156" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="160" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="cellIs" dxfId="152" priority="145" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="149" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I50">
-    <cfRule type="containsText" dxfId="151" priority="150" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="155" priority="154" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I50)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="151" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="155" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="152" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="156" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="148" priority="153" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="152" priority="157" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I50)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E50">
-    <cfRule type="cellIs" dxfId="147" priority="148" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="152" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="149" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="153" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F50">
-    <cfRule type="cellIs" dxfId="145" priority="146" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="150" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="147" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="151" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I56">
-    <cfRule type="containsText" dxfId="143" priority="141" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="147" priority="145" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I56)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="142" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="146" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="143" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="147" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="140" priority="144" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="144" priority="148" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I56)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E56">
-    <cfRule type="cellIs" dxfId="139" priority="139" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="143" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="140" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="144" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="cellIs" dxfId="137" priority="137" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="141" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="138" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="142" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F56">
-    <cfRule type="cellIs" dxfId="135" priority="136" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="140" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I57">
-    <cfRule type="containsText" dxfId="134" priority="132" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="138" priority="136" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I57)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="133" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="137" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="134" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="138" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="131" priority="135" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="135" priority="139" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I57)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E57">
-    <cfRule type="cellIs" dxfId="130" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="134" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="131" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="135" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57">
-    <cfRule type="cellIs" dxfId="128" priority="128" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="132" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="129" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="133" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F57">
-    <cfRule type="cellIs" dxfId="126" priority="127" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="131" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I63">
-    <cfRule type="containsText" dxfId="125" priority="123" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="129" priority="127" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I63)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="128" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="125" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="129" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="122" priority="126" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="126" priority="130" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E63">
-    <cfRule type="cellIs" dxfId="121" priority="121" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="125" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="122" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="126" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="cellIs" dxfId="119" priority="119" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="123" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="120" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="124" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63">
-    <cfRule type="cellIs" dxfId="117" priority="118" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="122" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I64">
-    <cfRule type="containsText" dxfId="116" priority="114" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="120" priority="118" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I64)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="115" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="119" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="116" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="120" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="113" priority="117" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="117" priority="121" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I64)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E64">
-    <cfRule type="cellIs" dxfId="112" priority="112" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="116" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="113" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="117" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="cellIs" dxfId="110" priority="110" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="114" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="111" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="115" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F64">
-    <cfRule type="cellIs" dxfId="108" priority="109" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="113" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E25">
-    <cfRule type="cellIs" dxfId="107" priority="107" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="111" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="108" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="112" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="cellIs" dxfId="105" priority="105" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="109" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="106" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="110" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="cellIs" dxfId="103" priority="104" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="108" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="containsText" dxfId="102" priority="100" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="106" priority="104" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I25)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="101" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="105" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="102" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="106" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="99" priority="103" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="103" priority="107" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I25)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E26">
-    <cfRule type="cellIs" dxfId="98" priority="98" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="102" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="99" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="103" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="cellIs" dxfId="96" priority="96" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="100" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="97" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="101" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="cellIs" dxfId="94" priority="95" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="99" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26">
-    <cfRule type="containsText" dxfId="93" priority="91" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="97" priority="95" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I26)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="92" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="96" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="93" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="97" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="94" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="94" priority="98" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32">
-    <cfRule type="cellIs" dxfId="89" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="93" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="94" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="cellIs" dxfId="87" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="91" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="88" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="92" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="cellIs" dxfId="85" priority="86" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="90" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I32">
-    <cfRule type="containsText" dxfId="84" priority="82" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="88" priority="86" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I32)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="83" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="87" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="82" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="88" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="81" priority="85" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="85" priority="89" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="cellIs" dxfId="80" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="84" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="81" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="85" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33">
-    <cfRule type="cellIs" dxfId="78" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="82" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="81" priority="83" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33">
-    <cfRule type="cellIs" dxfId="76" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="81" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I33">
-    <cfRule type="containsText" dxfId="75" priority="73" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="79" priority="77" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I33)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="74" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="78" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="75" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="79" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="76" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="76" priority="80" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E39">
-    <cfRule type="cellIs" dxfId="71" priority="71" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="75" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="76" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="cellIs" dxfId="69" priority="69" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="73" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="74" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F39">
-    <cfRule type="cellIs" dxfId="67" priority="68" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="72" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I39">
-    <cfRule type="containsText" dxfId="66" priority="64" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="70" priority="68" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I39)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="65" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="69" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="66" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="70" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="63" priority="67" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="67" priority="71" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E40">
-    <cfRule type="cellIs" dxfId="62" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="66" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="67" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F40">
-    <cfRule type="cellIs" dxfId="60" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="64" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="61" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="65" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F40">
-    <cfRule type="cellIs" dxfId="58" priority="59" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="63" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I40">
+    <cfRule type="containsText" dxfId="61" priority="59" operator="containsText" text="iso">
+      <formula>NOT(ISERROR(SEARCH("iso",I40)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="60" operator="equal">
+      <formula>"dn"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="59" priority="61" operator="equal">
+      <formula>"dcv"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="58" priority="62" operator="containsText" text="sr">
+      <formula>NOT(ISERROR(SEARCH("sr",I40)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I65">
     <cfRule type="containsText" dxfId="57" priority="55" operator="containsText" text="iso">
-      <formula>NOT(ISERROR(SEARCH("iso",I40)))</formula>
+      <formula>NOT(ISERROR(SEARCH("iso",I65)))</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="56" priority="56" operator="equal">
       <formula>"dn"</formula>
@@ -61246,217 +61396,217 @@
       <formula>"dcv"</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="54" priority="58" operator="containsText" text="sr">
-      <formula>NOT(ISERROR(SEARCH("sr",I40)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I65">
-    <cfRule type="containsText" dxfId="53" priority="51" operator="containsText" text="iso">
-      <formula>NOT(ISERROR(SEARCH("iso",I65)))</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="52" operator="equal">
-      <formula>"dn"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="53" operator="equal">
-      <formula>"dcv"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="54" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I65)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65">
-    <cfRule type="cellIs" dxfId="49" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="53" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="50" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="54" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="cellIs" dxfId="47" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="51" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="52" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F65">
-    <cfRule type="cellIs" dxfId="45" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="50" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E41">
-    <cfRule type="cellIs" dxfId="44" priority="44" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="48" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="49" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41">
-    <cfRule type="cellIs" dxfId="42" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="46" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="47" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F41">
-    <cfRule type="cellIs" dxfId="40" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="45" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I41">
-    <cfRule type="containsText" dxfId="39" priority="37" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="43" priority="41" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I41)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="42" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="43" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="40" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="40" priority="44" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E27">
-    <cfRule type="cellIs" dxfId="35" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="39" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="40" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="cellIs" dxfId="33" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="37" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="38" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F27">
-    <cfRule type="cellIs" dxfId="31" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="36" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I27">
-    <cfRule type="containsText" dxfId="30" priority="28" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="34" priority="32" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I27)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="33" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="31" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="31" priority="35" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E34">
-    <cfRule type="cellIs" dxfId="26" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="30" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="31" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="28" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="29" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="cellIs" dxfId="22" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I34">
-    <cfRule type="containsText" dxfId="21" priority="19" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I34)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="24" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="25" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="22" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="22" priority="26" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="cellIs" dxfId="17" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="14" operator="equal">
       <formula>"ft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I51">
-    <cfRule type="containsText" dxfId="16" priority="15" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="20" priority="19" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I51)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="21" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="18" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="17" priority="22" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E51">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F51">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I58">
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="iso">
+    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="iso">
       <formula>NOT(ISERROR(SEARCH("iso",I58)))</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>"dn"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"dcv"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="sr">
+    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="sr">
       <formula>NOT(ISERROR(SEARCH("sr",I58)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E58">
-    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"ex"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"in"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"ft"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J105:K105">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="iso">
+      <formula>NOT(ISERROR(SEARCH("iso",J105)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"dn"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"dcv"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="sr">
+      <formula>NOT(ISERROR(SEARCH("sr",J105)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataset_train_transformer-v2.xlsx
+++ b/dataset_train_transformer-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2024 Foundation model\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DBAB27-BE6B-4694-91D3-1DA0E4F64695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EABCB9-4AEA-4FE6-ACB5-913005D7515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="2370" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20415" yWindow="2460" windowWidth="16785" windowHeight="17190" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="64x64" sheetId="1" r:id="rId1"/>
